--- a/docs/videos/video_import_file.xlsx
+++ b/docs/videos/video_import_file.xlsx
@@ -558,7 +558,17 @@
   - "Register. Verify. Sell."
 DEMO DATA: A fresh email address for signup.
 CTA: Try free + subscribe
-RELATED: [03-sales-pos.md](./03-sales-pos.md) (first sale)</t>
+RELATED: [03-sales-pos.md](./03-sales-pos.md) (first sale)
+PUBLISHED TITLE: Create your shop in 5 minutes.
+SHORT-FORM VARIANT: Create your shop
+PUBLISHED DESCRIPTION: Get your shop live on Custosell - register, set up your business, and complete onboarding in about five minutes. Start selling today. Try free + subscribe #custosell #account #signup #Custosell #SmallBusiness
+TAGS: custosell, account, sign up, signup, register, login, security, two factor, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Live in 5 minutes" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D2" s="5" t="n"/>
@@ -611,7 +621,17 @@
 DEMO DATA: A fresh email address for signup.
 CTA: Try free + subscribe
 RELATED: [08-expenses-budgets-income.md](./08-expenses-budgets-income.md),
-[18-quick-notes.md](./18-quick-notes.md)</t>
+[18-quick-notes.md](./18-quick-notes.md)
+PUBLISHED TITLE: No shop? No problem - get a personal account.
+SHORT-FORM VARIANT: No shop? No problem
+PUBLISHED DESCRIPTION: Create a personal Custosell account in minutes - for tracking expenses, budgets, and income without a business. Pick the modules you want, use them on your own terms. Try free + subscribe #custosell #account #signup #Custosell #SmallBusiness
+TAGS: custosell, account, sign up, signup, register, login, security, two factor, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "For personal use" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D3" s="5" t="n"/>
@@ -665,7 +685,17 @@
 DEMO DATA: A fresh email address for signup + a published storefront
 with products.
 CTA: Try free + subscribe
-RELATED: [14-storefront.md](./14-storefront.md)</t>
+RELATED: [14-storefront.md](./14-storefront.md)
+PUBLISHED TITLE: Buy from the storefront in minutes - no shop needed.
+SHORT-FORM VARIANT: Buy from the storefront in minutes
+PUBLISHED DESCRIPTION: Create a free shopping account on Custosell to browse and buy from storefronts and the marketplace. A Discover-only account that keeps you shopping without a business setup. Try free + subscribe #custosell #account #signup #Custosell #SmallBusiness
+TAGS: custosell, account, sign up, signup, register, login, security, two factor, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Online shopping" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D4" s="5" t="n"/>
@@ -726,7 +756,17 @@
 DEMO DATA: A verified account with an active subscription and a few
 modules enabled.
 CTA: Try free + subscribe
-RELATED: [02-common-start.md](./02-common-start.md)</t>
+RELATED: [02-common-start.md](./02-common-start.md)
+PUBLISHED TITLE: Every tool Custosell gives you, one card away.
+SHORT-FORM VARIANT: Every tool Custosell gives you
+PUBLISHED DESCRIPTION: After you sign in, Your Tools is the launchpad - a card grid of every module you can access, starting with the six most used and a Show more row for the rest. Each card jumps straight into that module, with personalised descriptions for personal or business accounts, plus plan status and locked-tool warnings when access lapses. Try free + subscribe #custosell #account #signup #Custosell #SmallBusiness
+TAGS: custosell, account, sign up, signup, register, login, security, two factor, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Your Tools" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D5" s="5" t="n"/>
@@ -780,7 +820,17 @@
 account's inbox for the code.
 CTA: Try free + subscribe
 RELATED: [02-dashboard-reports.md](./02-dashboard-reports.md),
-[01-account-auth-security.md](./01-account-auth-security.md) (switch)</t>
+[01-account-auth-security.md](./01-account-auth-security.md) (switch)
+PUBLISHED TITLE: Run two shops with one login.
+SHORT-FORM VARIANT: Run two shops with one login.
+PUBLISHED DESCRIPTION: Link multiple shops to one Custosell account so you can switch between them without logging out. Linking is confirmed with a security code sent to the account being linked - so it stays safe. Try free + subscribe #custosell #account #signup #Custosell #SmallBusiness
+TAGS: custosell, account, sign up, signup, register, login, security, two factor, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "One login. Many shops." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D6" s="5" t="n"/>
@@ -828,7 +878,17 @@
 DEMO DATA: Two linked accounts.
 CTA: Try free + subscribe
 RELATED: [01-account-auth-security.md](./01-account-auth-security.md)
-(link), [02-dashboard-reports.md](./02-dashboard-reports.md)</t>
+(link), [02-dashboard-reports.md](./02-dashboard-reports.md)
+PUBLISHED TITLE: Switch shops in one tap - no logging out.
+SHORT-FORM VARIANT: Switch shops in one tap
+PUBLISHED DESCRIPTION: Jump between your linked shops on Custosell without signing out and signing back in. Switching keeps each shop's data separate. Try free + subscribe #custosell #account #signup #Custosell #SmallBusiness
+TAGS: custosell, account, sign up, signup, register, login, security, two factor, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Switch in a tap" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D7" s="5" t="n"/>
@@ -876,7 +936,17 @@
 DEMO DATA: Two linked accounts.
 CTA: Try free
 RELATED: [01-account-auth-security.md](./01-account-auth-security.md)
-(link), [20-referrals-credits.md](./20-referrals-credits.md)</t>
+(link), [20-referrals-credits.md](./20-referrals-credits.md)
+PUBLISHED TITLE: Pick which shop you land in by default.
+SHORT-FORM VARIANT: Pick which shop you land
+PUBLISHED DESCRIPTION: Choose the default account on Custosell - the one you land in at sign-in and which acts as your primary for billing and referrals. Try free #custosell #account #signup #Custosell #SmallBusiness
+TAGS: custosell, account, sign up, signup, register, login, security, two factor, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Set. Primary. Done." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D8" s="5" t="n"/>
@@ -927,7 +997,17 @@
 CTA: Try free
 RELATED: [01-account-auth-security.md](./01-account-auth-security.md)
 (link), [01-account-auth-security.md](./01-account-auth-security.md)
-(set default)</t>
+(set default)
+PUBLISHED TITLE: Remove an account from your login - safely.
+SHORT-FORM VARIANT: Remove an account from your login
+PUBLISHED DESCRIPTION: Unlink an account on Custosell when you no longer want it under your login. Unlinking is confirmed with a security code and does not delete the account itself. Try free #custosell #account #signup #Custosell #SmallBusiness
+TAGS: custosell, account, sign up, signup, register, login, security, two factor, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Unlinked. Not deleted." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D9" s="5" t="n"/>
@@ -977,7 +1057,17 @@
 CTA: Try free + subscribe
 RELATED: [01-account-auth-security.md](./01-account-auth-security.md)
 (lost password), [01-account-auth-security.md](./01-account-auth-security.md)
-(activity)</t>
+(activity)
+PUBLISHED TITLE: Change your password in two steps - safely.
+SHORT-FORM VARIANT: Change your password in two steps
+PUBLISHED DESCRIPTION: Change your Custosell password with a security code sent to your email. Your password only changes once you confirm with the code. Try free + subscribe #custosell #account #signup #Custosell #SmallBusiness
+TAGS: custosell, account, sign up, signup, register, login, security, two factor, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Code confirms every change" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D10" s="5" t="n"/>
@@ -1024,7 +1114,17 @@
 DEMO DATA: A demo account to reset.
 CTA: Try free
 RELATED: [01-account-auth-security.md](./01-account-auth-security.md)
-(change password)</t>
+(change password)
+PUBLISHED TITLE: Locked out? Back in within a minute.
+SHORT-FORM VARIANT: Locked out? Back
+PUBLISHED DESCRIPTION: The forgotten-password flow on Custosell - reset it safely and keep access to your shop. The number one support question, answered. Try free #custosell #account #signup #Custosell #SmallBusiness
+TAGS: custosell, account, sign up, signup, register, login, security, two factor, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Reset in 60 seconds" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D11" s="5" t="n"/>
@@ -1074,7 +1174,17 @@
 CTA: Try free
 RELATED: [01-account-auth-security.md](./01-account-auth-security.md)
 (2FA), [01-account-auth-security.md](./01-account-auth-security.md)
-(change email)</t>
+(change email)
+PUBLISHED TITLE: Verify your email to secure your account.
+SHORT-FORM VARIANT: Verify your email to secure your account.
+PUBLISHED DESCRIPTION: Confirm your email address on Custosell - send the code, enter the 6-digit code, and get the Verified badge. Required for full access and account security. Try free #custosell #account #signup #Custosell #SmallBusiness
+TAGS: custosell, account, sign up, signup, register, login, security, two factor, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Verified" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D12" s="5" t="n"/>
@@ -1123,7 +1233,17 @@
 CTA: Try free + subscribe
 RELATED: [01-account-auth-security.md](./01-account-auth-security.md)
 (verify email), [01-account-auth-security.md](./01-account-auth-security.md)
-(activity)</t>
+(activity)
+PUBLISHED TITLE: Lock your account. Sleep easy.
+SHORT-FORM VARIANT: Lock your account. Sleep easy.
+PUBLISHED DESCRIPTION: Turn on two-factor authentication on Custosell. From now on, every sign-in needs your password plus a code sent to your email. Try free + subscribe #custosell #account #signup #Custosell #SmallBusiness
+TAGS: custosell, account, sign up, signup, register, login, security, two factor, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "2FA: on" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D13" s="5" t="n"/>
@@ -1170,7 +1290,17 @@
 DEMO DATA: A demo account with 2FA on.
 CTA: Try free
 RELATED: [01-account-auth-security.md](./01-account-auth-security.md)
-(2FA on)</t>
+(2FA on)
+PUBLISHED TITLE: Got a new phone? Turn 2FA off - and back on.
+SHORT-FORM VARIANT: Got a new phone? Turn 2FA off
+PUBLISHED DESCRIPTION: Disable two-factor authentication on Custosell when you no longer need the extra step - and how to switch it back on later. Try free #custosell #account #signup #Custosell #SmallBusiness
+TAGS: custosell, account, sign up, signup, register, login, security, two factor, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "2FA: off (you control it)" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D14" s="5" t="n"/>
@@ -1217,7 +1347,17 @@
 DEMO DATA: A demo account and access to the new inbox.
 CTA: Try free
 RELATED: [01-account-auth-security.md](./01-account-auth-security.md)
-(verify email)</t>
+(verify email)
+PUBLISHED TITLE: New email, same account, same data.
+SHORT-FORM VARIANT: New email
+PUBLISHED DESCRIPTION: Change the email on your Custosell account with a security code - safe, confirmed, and nothing else changes. Try free #custosell #account #signup #Custosell #SmallBusiness
+TAGS: custosell, account, sign up, signup, register, login, security, two factor, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Verified change" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D15" s="5" t="n"/>
@@ -1264,7 +1404,17 @@
 DEMO DATA: A demo account + an image file for the avatar.
 CTA: Try free
 RELATED: [01-account-auth-security.md](./01-account-auth-security.md)
-(switch), [15-hr.md](./15-hr.md) (team recognition)</t>
+(switch), [15-hr.md](./15-hr.md) (team recognition)
+PUBLISHED TITLE: Your face on the till - update your profile.
+SHORT-FORM VARIANT: Your face on the till
+PUBLISHED DESCRIPTION: Update your profile photo, name, and phone on Custosell. Your photo follows you across linked accounts, so your team recognises you. Try free #custosell #account #signup #Custosell #SmallBusiness
+TAGS: custosell, account, sign up, signup, register, login, security, two factor, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Photo follows you" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D16" s="5" t="n"/>
@@ -1353,7 +1503,17 @@
 `plan_features` + `getAccessibleModules` (business slugs only), status line
 and gating via `hasSubscriptionAccess` + `STATUS_CONFIG` (trial / active /
 past_due / cancelled / suspended / expired + grace period), card targets are
-`MODULE_DEFAULT_ROUTES` / each group's first sub-route.</t>
+`MODULE_DEFAULT_ROUTES` / each group's first sub-route.
+PUBLISHED TITLE: See every sign-in, every change - in one feed.
+SHORT-FORM VARIANT: See every sign-in, every change
+PUBLISHED DESCRIPTION: Review your account activity on Custosell - sign-ins, sign-outs, email verification, 2FA events, password changes, and profile updates, each with the device and IP address. Try free + subscribe #custosell #account #signup #Custosell #SmallBusiness
+TAGS: custosell, account, sign up, signup, register, login, security, two factor, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Every event, tracked" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D17" s="5" t="n"/>
@@ -1400,7 +1560,17 @@
   - "Your brand, everywhere"
 DEMO DATA: A logo image.
 CTA: Try free + subscribe
-RELATED: [16-subscriptions-billing.md](./16-subscriptions-billing.md)</t>
+RELATED: [16-subscriptions-billing.md](./16-subscriptions-billing.md)
+PUBLISHED TITLE: Your shop's identity - name, logo, contacts, done.
+SHORT-FORM VARIANT: Your shop's identity
+PUBLISHED DESCRIPTION: Complete your business profile on Custosell - business name, website, business email and phone, description, and logo - so your app header and customer-facing pages carry your brand. Try free + subscribe #custosell #settings #businessprofile #tax #Custosell #SmallBusiness
+TAGS: custosell, settings, business profile, tax, currency, receipts, branches, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Your brand, everywhere" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D18" s="5" t="n"/>
@@ -1448,7 +1618,17 @@
   - "Tax right, everywhere"
 DEMO DATA: A business profile; tax jurisdiction list.
 CTA: Try free + subscribe
-RELATED: [17-settings.md](./17-settings.md)</t>
+RELATED: [17-settings.md](./17-settings.md)
+PUBLISHED TITLE: Country, currency, VAT rate - set once, correct everywhere.
+SHORT-FORM VARIANT: Country, currency, VAT rate - set once, correct
+PUBLISHED DESCRIPTION: Configure where your business operates - country, city, address - plus your currency, tax jurisdiction, TIN, VAT registration, default VAT rate, and whether prices include tax. Every price and report then uses them. Try free + subscribe #custosell #settings #businessprofile #tax #Custosell #SmallBusiness
+TAGS: custosell, settings, business profile, tax, currency, receipts, branches, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Tax right, everywhere" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D19" s="5" t="n"/>
@@ -1495,7 +1675,17 @@
   - "Pay your way"
 DEMO DATA: A business with invoice data.
 CTA: Try free + subscribe
-RELATED: [03-sales-pos.md](./03-sales-pos.md)</t>
+RELATED: [03-sales-pos.md](./03-sales-pos.md)
+PUBLISHED TITLE: Show customers exactly where to pay.
+SHORT-FORM VARIANT: Show customers exactly where to pay.
+PUBLISHED DESCRIPTION: Add your bank account and mobile money details once - they print on every invoice and order so customers know exactly where and how to pay. Try free + subscribe #custosell #settings #businessprofile #tax #Custosell #SmallBusiness
+TAGS: custosell, settings, business profile, tax, currency, receipts, branches, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Pay your way" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D20" s="5" t="n"/>
@@ -1541,7 +1731,17 @@
   - "Branded receipts"
 DEMO DATA: A business profile.
 CTA: Try free
-RELATED: [03-sales-pos.md](./03-sales-pos.md)</t>
+RELATED: [03-sales-pos.md](./03-sales-pos.md)
+PUBLISHED TITLE: A thank-you that prints on every receipt.
+SHORT-FORM VARIANT: A thank-you that prints on every receipt.
+PUBLISHED DESCRIPTION: Add a receipt footer message on Custosell so every customer receipt carries your branding, phone number, or a simple thank you. Try free #custosell #settings #businessprofile #tax #Custosell #SmallBusiness
+TAGS: custosell, settings, business profile, tax, currency, receipts, branches, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Branded receipts" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D21" s="5" t="n"/>
@@ -1587,7 +1787,17 @@
   - "Follow the shop"
 DEMO DATA: A storefront-enabled business.
 CTA: Try free
-RELATED: [14-storefront.md](./14-storefront.md)</t>
+RELATED: [14-storefront.md](./14-storefront.md)
+PUBLISHED TITLE: Link your socials, grow your reach.
+SHORT-FORM VARIANT: Link your socials
+PUBLISHED DESCRIPTION: Add your social media links on Custosell so customers browsing your online storefront can follow you on the platforms you actually use. Try free #custosell #settings #businessprofile #tax #Custosell #SmallBusiness
+TAGS: custosell, settings, business profile, tax, currency, receipts, branches, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Follow the shop" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D22" s="5" t="n"/>
@@ -1634,7 +1844,17 @@
   - "VAT, filed faster"
 DEMO DATA: A VAT-registered business with sales and expenses.
 CTA: Try free + subscribe
-RELATED: [02-dashboard-reports.md](./02-dashboard-reports.md)</t>
+RELATED: [02-dashboard-reports.md](./02-dashboard-reports.md)
+PUBLISHED TITLE: Your VAT workbook, ready in one click.
+SHORT-FORM VARIANT: Your VAT workbook
+PUBLISHED DESCRIPTION: Use the Tax &amp; VAT page to see net output VAT, claimable input VAT, and estimated VAT payable for any period, review claimable purchase VAT line by line, and download the workbook as PDF or CSV for filing. Try free + subscribe #custosell #settings #businessprofile #tax #Custosell #SmallBusiness
+TAGS: custosell, settings, business profile, tax, currency, receipts, branches, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "VAT, filed faster" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D23" s="5" t="n"/>
@@ -1681,7 +1901,17 @@
   - "No lock-in"
 DEMO DATA: Business data present.
 CTA: Try free
-RELATED: [10-documents.md](./10-documents.md)</t>
+RELATED: [10-documents.md](./10-documents.md)
+PUBLISHED TITLE: Your data is yours - take it anytime.
+SHORT-FORM VARIANT: Your data is yours
+PUBLISHED DESCRIPTION: Export your full Custosell data - products, customers, sales, invoices, expenses, accounting, pipeline, documents and more - as JSON, CSV, or Excel, whenever you need a backup or to hand records to an accountant. Try free #custosell #settings #businessprofile #tax #Custosell #SmallBusiness
+TAGS: custosell, settings, business profile, tax, currency, receipts, branches, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "No lock-in" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D24" s="5" t="n"/>
@@ -1728,7 +1958,17 @@
   - "Team ready"
 DEMO DATA: Roles and branches already set up.
 CTA: Try free + subscribe
-RELATED: [17-settings.md](./17-settings.md)</t>
+RELATED: [17-settings.md](./17-settings.md)
+PUBLISHED TITLE: Your team, logged in and working in minutes.
+SHORT-FORM VARIANT: Your team
+PUBLISHED DESCRIPTION: Add staff on Custosell - name, email, phone, role, branch, and modules - then edit them, move them between branches, and keep an eye on branch staffing with one team list. Try free + subscribe #custosell #settings #businessprofile #tax #Custosell #SmallBusiness
+TAGS: custosell, settings, business profile, tax, currency, receipts, branches, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Team ready" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D25" s="5" t="n"/>
@@ -1775,7 +2015,17 @@
   - "Clear roles"
 DEMO DATA: Staff data.
 CTA: Try free + subscribe
-RELATED: [17-settings.md](./17-settings.md)</t>
+RELATED: [17-settings.md](./17-settings.md)
+PUBLISHED TITLE: Give everyone a job title that makes sense.
+SHORT-FORM VARIANT: Give everyone a job title that makes sense.
+PUBLISHED DESCRIPTION: Create custom roles on Custosell to organize staff by job title - cashier, salesperson, manager - while module access stays controlled per staff member. Try free + subscribe #custosell #settings #businessprofile #tax #Custosell #SmallBusiness
+TAGS: custosell, settings, business profile, tax, currency, receipts, branches, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Clear roles" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D26" s="5" t="n"/>
@@ -1821,7 +2071,17 @@
   - "Branch by branch"
 DEMO DATA: A business profile.
 CTA: Try free + subscribe
-RELATED: [17-settings.md](./17-settings.md)</t>
+RELATED: [17-settings.md](./17-settings.md)
+PUBLISHED TITLE: One Custosell, every branch you run.
+SHORT-FORM VARIANT: One Custosell
+PUBLISHED DESCRIPTION: Add branches on Custosell, pick a default, and keep inventory, expenses, and staff organized per branch across the whole app. Try free + subscribe #custosell #settings #businessprofile #tax #Custosell #SmallBusiness
+TAGS: custosell, settings, business profile, tax, currency, receipts, branches, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Branch by branch" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D27" s="5" t="n"/>
@@ -1908,7 +2168,17 @@
 **Notable behavior:** business settings, staff, and roles updates can complete
 locally and sync when back online (pending-sync badges); export and delete flows
 are owner-only; personal accounts keep only Profile + Location tabs and skip the
-Danger Zone.</t>
+Danger Zone.
+PUBLISHED TITLE: Your app, your workspaces.
+SHORT-FORM VARIANT: Your app
+PUBLISHED DESCRIPTION: Pick which workspaces the business owner sees on Custosell - hide the modules you don't use and go deeper on Estimates or HR with full access toggles, all from one screen. Try free + subscribe #custosell #settings #businessprofile #tax #Custosell #SmallBusiness
+TAGS: custosell, settings, business profile, tax, currency, receipts, branches, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Your workspaces" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D28" s="5" t="n"/>
@@ -1956,7 +2226,17 @@
   - "Add. Price. Save. Sell."
 DEMO DATA: An existing category and a default branch.
 CTA: Try free + subscribe
-RELATED: [03-sales-pos.md](./03-sales-pos.md)</t>
+RELATED: [03-sales-pos.md](./03-sales-pos.md)
+PUBLISHED TITLE: Add a product once - sell it forever.
+SHORT-FORM VARIANT: Add a product once
+PUBLISHED DESCRIPTION: Learn how to add a product to Custosell inventory - name, price, cost, stock, and category. Everything you need to start selling in minutes. Try free + subscribe #custosell #inventory #products #categories #Custosell #SmallBusiness
+TAGS: custosell, inventory, products, categories, sku, barcode, stock, low stock, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Add. Price. Save. Sell." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D29" s="5" t="n"/>
@@ -2004,7 +2284,17 @@
   - "Services sell. Stock doesn't move."
 DEMO DATA: A service like "Installation" or "Delivery fee".
 CTA: Try free
-RELATED: [03-sales-pos.md](./03-sales-pos.md)</t>
+RELATED: [03-sales-pos.md](./03-sales-pos.md)
+PUBLISHED TITLE: Sell services with no stock to count.
+SHORT-FORM VARIANT: Sell services with no stock to count.
+PUBLISHED DESCRIPTION: Services in Custosell sell any quantity from the till without stock gates and post to service revenue. Add one in seconds. Try free #custosell #inventory #products #categories #Custosell #SmallBusiness
+TAGS: custosell, inventory, products, categories, sku, barcode, stock, low stock, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Services sell. Stock doesn't move." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D30" s="5" t="n"/>
@@ -2052,7 +2342,17 @@
   - "Group it. Find it. Sell it."
 DEMO DATA: Several uncategorized products.
 CTA: Try free
-RELATED: [05-inventory-products.md](./05-inventory-products.md)</t>
+RELATED: [05-inventory-products.md](./05-inventory-products.md)
+PUBLISHED TITLE: A tidy catalog is a faster till.
+SHORT-FORM VARIANT: A tidy catalog is a faster till.
+PUBLISHED DESCRIPTION: Create and manage categories in Custosell - group products, rename, and keep the POS fast to use. Try free #custosell #inventory #products #categories #Custosell #SmallBusiness
+TAGS: custosell, inventory, products, categories, sku, barcode, stock, low stock, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Group it. Find it. Sell it." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D31" s="5" t="n"/>
@@ -2100,7 +2400,17 @@
   - "Create it. Selected. Done."
 DEMO DATA: No categories yet, or a product with no category chosen.
 CTA: Try free
-RELATED: [05-inventory-products.md](./05-inventory-products.md)</t>
+RELATED: [05-inventory-products.md](./05-inventory-products.md)
+PUBLISHED TITLE: No category yet? Make one without leaving the form.
+SHORT-FORM VARIANT: No category yet? Make one without leaving the form.
+PUBLISHED DESCRIPTION: Add a category on the fly while creating a product - it gets created and auto-selected so you never break flow. Try free #custosell #inventory #products #categories #Custosell #SmallBusiness
+TAGS: custosell, inventory, products, categories, sku, barcode, stock, low stock, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Create it. Selected. Done." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D32" s="5" t="n"/>
@@ -2147,7 +2457,17 @@
   - "Edit once. Sell right."
 DEMO DATA: A product with a price that has changed.
 CTA: Try free
-RELATED: [05-inventory-products.md](./05-inventory-products.md)</t>
+RELATED: [05-inventory-products.md](./05-inventory-products.md)
+PUBLISHED TITLE: Prices change. Keep your catalog current.
+SHORT-FORM VARIANT: Prices change. Keep your catalog current.
+PUBLISHED DESCRIPTION: Update any product detail in Custosell - price, category, description, tax - and see the change reflect across the business. Try free #custosell #inventory #products #categories #Custosell #SmallBusiness
+TAGS: custosell, inventory, products, categories, sku, barcode, stock, low stock, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Edit once. Sell right." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D33" s="5" t="n"/>
@@ -2195,7 +2515,17 @@
   - "Retail. Wholesale. Cost. Tax."
 DEMO DATA: A supplier price for a stocked product.
 CTA: Try free
-RELATED: [09-accounting.md](./09-accounting.md)</t>
+RELATED: [09-accounting.md](./09-accounting.md)
+PUBLISHED TITLE: Price it right. Tax it right.
+SHORT-FORM VARIANT: Price it right. Tax it right.
+PUBLISHED DESCRIPTION: Set unit, wholesale, and cost prices plus tax class and tax percentage on a product so sales and reports stay accurate. Try free #custosell #inventory #products #categories #Custosell #SmallBusiness
+TAGS: custosell, inventory, products, categories, sku, barcode, stock, low stock, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Retail. Wholesale. Cost. Tax." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D34" s="5" t="n"/>
@@ -2243,7 +2573,17 @@
   - "Was. Now. Done."
 DEMO DATA: A product on the public shop.
 CTA: Try free
-RELATED: [14-storefront.md](./14-storefront.md)</t>
+RELATED: [14-storefront.md](./14-storefront.md)
+PUBLISHED TITLE: Put a product on sale without touching the till price.
+SHORT-FORM VARIANT: Put a product on sale without touching the till price.
+PUBLISHED DESCRIPTION: Set a sale discount percentage on a product with a live "Was X to Now Y" preview. The POS till keeps using the regular price. Try free #custosell #inventory #products #categories #Custosell #SmallBusiness
+TAGS: custosell, inventory, products, categories, sku, barcode, stock, low stock, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Was. Now. Done." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D35" s="5" t="n"/>
@@ -2291,7 +2631,17 @@
   - "SKU. Barcode. Found."
 DEMO DATA: A product with a barcode.
 CTA: Try free
-RELATED: [03-sales-pos.md](./03-sales-pos.md)</t>
+RELATED: [03-sales-pos.md](./03-sales-pos.md)
+PUBLISHED TITLE: Find any product in a second.
+SHORT-FORM VARIANT: Find any product
+PUBLISHED DESCRIPTION: Add a SKU and barcode to products so you can search and scan them fast at the till and in the catalog. Try free #custosell #inventory #products #categories #Custosell #SmallBusiness
+TAGS: custosell, inventory, products, categories, sku, barcode, stock, low stock, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "SKU. Barcode. Found." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D36" s="5" t="n"/>
@@ -2339,7 +2689,17 @@
   - "Open right. Reorder on time."
 DEMO DATA: A branch and a target stock level.
 CTA: Try free
-RELATED: [06-marketplace-purchase-orders.md](./06-marketplace-purchase-orders.md)</t>
+RELATED: [06-marketplace-purchase-orders.md](./06-marketplace-purchase-orders.md)
+PUBLISHED TITLE: Start with real stock numbers.
+SHORT-FORM VARIANT: Start with real stock numbers.
+PUBLISHED DESCRIPTION: Enter opening stock for a branch and a low-stock threshold so Custosell flags items that need reordering before you run out. Try free #custosell #inventory #products #categories #Custosell #SmallBusiness
+TAGS: custosell, inventory, products, categories, sku, barcode, stock, low stock, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Open right. Reorder on time." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D37" s="5" t="n"/>
@@ -2387,7 +2747,17 @@
   - "Recurring. Tracked. Forecast."
 DEMO DATA: A subscription-style product.
 CTA: Try free
-RELATED: [13-forecasting.md](./13-forecasting.md)</t>
+RELATED: [13-forecasting.md](./13-forecasting.md)
+PUBLISHED TITLE: Track subscriptions as real products.
+SHORT-FORM VARIANT: Track subscriptions as real products.
+PUBLISHED DESCRIPTION: Flag a product as recurring and pick a billing interval so subscription revenue is visible in forecasting KPIs. Try free #custosell #inventory #products #categories #Custosell #SmallBusiness
+TAGS: custosell, inventory, products, categories, sku, barcode, stock, low stock, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Recurring. Tracked. Forecast." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D38" s="5" t="n"/>
@@ -2434,7 +2804,17 @@
   - "Gone from the till. Kept in the books."
 DEMO DATA: A product with past sales.
 CTA: Try free
-RELATED: [09-accounting.md](./09-accounting.md)</t>
+RELATED: [09-accounting.md](./09-accounting.md)
+PUBLISHED TITLE: Stop selling a product without deleting its history.
+SHORT-FORM VARIANT: Stop selling a product without deleting its history.
+PUBLISHED DESCRIPTION: Deactivate a discontinued product on Custosell - it leaves your POS but keeps its sales history and reports intact. Try free #custosell #inventory #products #categories #Custosell #SmallBusiness
+TAGS: custosell, inventory, products, categories, sku, barcode, stock, low stock, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Gone from the till. Kept in the books." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D39" s="5" t="n"/>
@@ -2481,7 +2861,17 @@
   - "Confirm. Delete. Clean."
 DEMO DATA: A product created only for testing.
 CTA: Try free
-RELATED: [05-inventory-products.md](./05-inventory-products.md)</t>
+RELATED: [05-inventory-products.md](./05-inventory-products.md)
+PUBLISHED TITLE: Remove a product for good - with a safety check.
+SHORT-FORM VARIANT: Remove a product for good
+PUBLISHED DESCRIPTION: Permanently delete a product (or several) with an explicit confirmation so mistakes don't happen. Try free #custosell #inventory #products #categories #Custosell #SmallBusiness
+TAGS: custosell, inventory, products, categories, sku, barcode, stock, low stock, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Confirm. Delete. Clean." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D40" s="5" t="n"/>
@@ -2530,7 +2920,17 @@
 DEMO DATA: A catalog with many products across branches and listing
 states.
 CTA: Try free
-RELATED: [05-inventory-products.md](./05-inventory-products.md)</t>
+RELATED: [05-inventory-products.md](./05-inventory-products.md)
+PUBLISHED TITLE: Find any product in seconds.
+SHORT-FORM VARIANT: Find any product
+PUBLISHED DESCRIPTION: Search your catalog by name, SKU, or barcode and filter by branch, public shop listing, or supply listing. Try free #custosell #inventory #products #categories #Custosell #SmallBusiness
+TAGS: custosell, inventory, products, categories, sku, barcode, stock, low stock, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Search. Filter. Found." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D41" s="5" t="n"/>
@@ -2578,7 +2978,17 @@
   - "Select. Batch. Done."
 DEMO DATA: A dozen products ready to be listed or removed.
 CTA: Try free
-RELATED: [06-marketplace-purchase-orders.md](./06-marketplace-purchase-orders.md)</t>
+RELATED: [06-marketplace-purchase-orders.md](./06-marketplace-purchase-orders.md)
+PUBLISHED TITLE: Manage dozens of products at once.
+SHORT-FORM VARIANT: Manage dozens of products at once.
+PUBLISHED DESCRIPTION: Select many products and list or unlist them on the public shop or supply marketplace, or delete them in one action. Try free #custosell #inventory #products #categories #Custosell #SmallBusiness
+TAGS: custosell, inventory, products, categories, sku, barcode, stock, low stock, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Select. Batch. Done." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D42" s="5" t="n"/>
@@ -2626,7 +3036,17 @@
   - "Add. Reason. Traceable."
 DEMO DATA: A product at a known stock level.
 CTA: Try free
-RELATED: [06-marketplace-purchase-orders.md](./06-marketplace-purchase-orders.md)</t>
+RELATED: [06-marketplace-purchase-orders.md](./06-marketplace-purchase-orders.md)
+PUBLISHED TITLE: Stock in? Add it with a reason.
+SHORT-FORM VARIANT: Stock in? Add it with a reason.
+PUBLISHED DESCRIPTION: Add stock to a product from the Adjust Stock flow - choose a reason (purchase, return, correction, initial) and a branch. Try free #custosell #inventory #products #categories #Custosell #SmallBusiness
+TAGS: custosell, inventory, products, categories, sku, barcode, stock, low stock, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Add. Reason. Traceable." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D43" s="5" t="n"/>
@@ -2674,7 +3094,17 @@
   - "Remove. Reason. Logged."
 DEMO DATA: A product with stock to remove.
 CTA: Try free
-RELATED: [05-inventory-products.md](./05-inventory-products.md)</t>
+RELATED: [05-inventory-products.md](./05-inventory-products.md)
+PUBLISHED TITLE: Stock wrong? Correct it safely.
+SHORT-FORM VARIANT: Stock wrong? Correct it safely.
+PUBLISHED DESCRIPTION: Remove stock for damage, loss, write-off, or supplier returns - Custosell blocks going below zero and logs the reason. Try free #custosell #inventory #products #categories #Custosell #SmallBusiness
+TAGS: custosell, inventory, products, categories, sku, barcode, stock, low stock, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Remove. Reason. Logged." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D44" s="5" t="n"/>
@@ -2721,7 +3151,17 @@
   - "Low. Out. Order now."
 DEMO DATA: Products at various stock levels including low and out.
 CTA: Try free
-RELATED: [06-marketplace-purchase-orders.md](./06-marketplace-purchase-orders.md)</t>
+RELATED: [06-marketplace-purchase-orders.md](./06-marketplace-purchase-orders.md)
+PUBLISHED TITLE: Out of stock before you run out of stock.
+SHORT-FORM VARIANT: Out of stock before you run out of stock.
+PUBLISHED DESCRIPTION: Read your stock level indicator on Custosell - see what's low, what's out, and what needs restocking at a glance. Try free #custosell #inventory #products #categories #Custosell #SmallBusiness
+TAGS: custosell, inventory, products, categories, sku, barcode, stock, low stock, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Low. Out. Order now." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D45" s="5" t="n"/>
@@ -2768,7 +3208,17 @@
   - "History. Balance. Proof."
 DEMO DATA: A product with a few stock movements.
 CTA: Try free
-RELATED: [05-inventory-products.md](./05-inventory-products.md)</t>
+RELATED: [05-inventory-products.md](./05-inventory-products.md)
+PUBLISHED TITLE: Every move a product made, in one timeline.
+SHORT-FORM VARIANT: Every move a product made
+PUBLISHED DESCRIPTION: Open the stock history for any product and see every purchase, sale, adjustment, return, and initial entry with the running balance. Try free #custosell #inventory #products #categories #Custosell #SmallBusiness
+TAGS: custosell, inventory, products, categories, sku, barcode, stock, low stock, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "History. Balance. Proof." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D46" s="5" t="n"/>
@@ -2815,7 +3265,17 @@
   - "Filter. Inspect. Reconstruct."
 DEMO DATA: Several stock movements across products and types.
 CTA: Try free
-RELATED: [05-inventory-products.md](./05-inventory-products.md)</t>
+RELATED: [05-inventory-products.md](./05-inventory-products.md)
+PUBLISHED TITLE: Every stock movement, one clean ledger.
+SHORT-FORM VARIANT: Every stock movement
+PUBLISHED DESCRIPTION: Browse the full stock ledger - filter by product and type, see before/after balances, and clean up records in bulk if needed. Try free #custosell #inventory #products #categories #Custosell #SmallBusiness
+TAGS: custosell, inventory, products, categories, sku, barcode, stock, low stock, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Filter. Inspect. Reconstruct." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D47" s="5" t="n"/>
@@ -2863,7 +3323,17 @@
   - "From. To. Moved."
 DEMO DATA: Two branches with stocked products.
 CTA: Try free
-RELATED: [17-settings.md](./17-settings.md)</t>
+RELATED: [17-settings.md](./17-settings.md)
+PUBLISHED TITLE: Move stock where it sells.
+SHORT-FORM VARIANT: Move stock where it sells.
+PUBLISHED DESCRIPTION: Transfer stock from one branch to another for one product or a whole selection, with available-quantity checks built in. Try free #custosell #inventory #products #categories #Custosell #SmallBusiness
+TAGS: custosell, inventory, products, categories, sku, barcode, stock, low stock, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "From. To. Moved." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D48" s="5" t="n"/>
@@ -2911,7 +3381,18 @@
   - "Template. Upload. Imported."
 DEMO DATA: A filled product template file with one bad row.
 CTA: Try free + subscribe
-RELATED: [05-inventory-products.md](./05-inventory-products.md)</t>
+RELATED: [05-inventory-products.md](./05-inventory-products.md)
+PUBLISHED TITLE: Skip the typing. Upload your whole catalog.
+SHORT-FORM VARIANT: Skip the typing. Upload your whole catalog.
+PUBLISHED DESCRIPTION: Import products from an .xlsx, .xls, or .csv file - download the template, map products to a branch, upload, and review per-row errors. Try free + subscribe #custosell #inventory #products #categories #Custosell #SmallBusiness
+TAGS: custosell, inventory, products, categories, sku, barcode, stock, low stock, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Template. Upload. Imported." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover
+  - Intro / outro: 2s animated logo intro + end screen with subscribe</t>
         </is>
       </c>
       <c r="D49" s="5" t="n"/>
@@ -2958,7 +3439,17 @@
   - "CSV. Excel. Downloaded."
 DEMO DATA: A populated catalog.
 CTA: Try free
-RELATED: [05-inventory-products.md](./05-inventory-products.md)</t>
+RELATED: [05-inventory-products.md](./05-inventory-products.md)
+PUBLISHED TITLE: Take your catalog anywhere.
+SHORT-FORM VARIANT: Take your catalog anywhere.
+PUBLISHED DESCRIPTION: Download your full product list as CSV or Excel for backups, spreadsheets, or sharing with a supplier. Try free #custosell #inventory #products #categories #Custosell #SmallBusiness
+TAGS: custosell, inventory, products, categories, sku, barcode, stock, low stock, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "CSV. Excel. Downloaded." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D50" s="5" t="n"/>
@@ -3006,7 +3497,17 @@
   - "Upload. Preview. Listed."
 DEMO DATA: A product image file.
 CTA: Try free
-RELATED: [14-storefront.md](./14-storefront.md)</t>
+RELATED: [14-storefront.md](./14-storefront.md)
+PUBLISHED TITLE: Give your shop products a face.
+SHORT-FORM VARIANT: Give your shop products a face.
+PUBLISHED DESCRIPTION: Upload a product photo so your public shop looks real and trustworthy to customers. Try free #custosell #inventory #products #categories #Custosell #SmallBusiness
+TAGS: custosell, inventory, products, categories, sku, barcode, stock, low stock, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Upload. Preview. Listed." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D51" s="5" t="n"/>
@@ -3056,7 +3557,18 @@
 DEMO DATA: A catalog with costed stock, low/out/dead items, and
 multi-branch data.
 CTA: Try free + subscribe
-RELATED: [02-dashboard-reports.md](./02-dashboard-reports.md)</t>
+RELATED: [02-dashboard-reports.md](./02-dashboard-reports.md)
+PUBLISHED TITLE: Know the money sitting in your stock.
+SHORT-FORM VARIANT: Know the money sitting
+PUBLISHED DESCRIPTION: The inventory overview shows stock value at cost, projected profit, units on hand, and alerts - plus trends, category and branch breakdowns, and margin rankings. Try free + subscribe #custosell #inventory #products #categories #Custosell #SmallBusiness
+TAGS: custosell, inventory, products, categories, sku, barcode, stock, low stock, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Value. Profit. Alerts." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover
+  - Intro / outro: 2s animated logo intro + end screen with subscribe</t>
         </is>
       </c>
       <c r="D52" s="5" t="n"/>
@@ -3124,7 +3636,17 @@
 `/products/{id}/supply-listing` · `/products/{id}/storefront-listing` ·
 `/products/{id}/image` · `/categories` CRUD · `/stock-movements` CRUD +
 `/stock-movements/bulk-delete` + `/stock-movements/transfer` ·
-`/inventory/overview`</t>
+`/inventory/overview`
+PUBLISHED TITLE: Keep building your catalog without internet.
+SHORT-FORM VARIANT: Keep building your catalog without internet.
+PUBLISHED DESCRIPTION: Create, edit, and adjust products even when offline - Custosell queues the changes and syncs them when you're back online. Try free #custosell #inventory #products #categories #Custosell #SmallBusiness
+TAGS: custosell, inventory, products, categories, sku, barcode, stock, low stock, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Offline. Queued. Synced." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D53" s="5" t="n"/>
@@ -3178,7 +3700,17 @@
 a customer, at least 2 payment methods configured.
 CTA: Subscribe + try free (https://custosell.com?utm=wave1-firstsale)
 RELATED: [04-shifts.md](./04-shifts.md) (shift close),
-[21-offline-sync.md](./21-offline-sync.md)</t>
+[21-offline-sync.md](./21-offline-sync.md)
+PUBLISHED TITLE: Make your first sale in under a minute on Custosell.
+SHORT-FORM VARIANT: Make your first sale
+PUBLISHED DESCRIPTION: Learn how to make your first sale on Custosell POS. Add items to the cart, take payment, and print or email the receipt. Perfect for new shop owners getting started. Try Custosell free - link below. Subscribe + try free (https://custosell.com?utm=wave1-firstsale) #custosell #pos #pointofsale #sell #Custosell #SmallBusiness
+TAGS: custosell, pos, point of sale, sell, checkout, retail, payments, receipt, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Sell your first item" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D54" s="5" t="n"/>
@@ -3226,7 +3758,17 @@
   - "Stock + price inline"
 DEMO DATA: A catalog of 10+ products with SKUs, a couple with barcodes.
 CTA: Try free
-RELATED: [03-sales-pos.md](./03-sales-pos.md) (first sale)</t>
+RELATED: [03-sales-pos.md](./03-sales-pos.md) (first sale)
+PUBLISHED TITLE: Search by name, SKU, or barcode - the till never waits.
+SHORT-FORM VARIANT: Search by name, SKU, or barcode
+PUBLISHED DESCRIPTION: Find any product on Custosell POS in seconds. The search bar matches product name, SKU, and barcode as you type, and shows stock and price right in the results. Try free #custosell #pos #pointofsale #sell #Custosell #SmallBusiness
+TAGS: custosell, pos, point of sale, sell, checkout, retail, payments, receipt, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Search: name, SKU, or barcode" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D55" s="5" t="n"/>
@@ -3273,7 +3815,17 @@
   - "No typing needed"
 DEMO DATA: Products with real barcodes and a working scanner.
 CTA: Try free
-RELATED: [03-sales-pos.md](./03-sales-pos.md) (search products)</t>
+RELATED: [03-sales-pos.md](./03-sales-pos.md) (search products)
+PUBLISHED TITLE: Beep. In the cart. That fast.
+SHORT-FORM VARIANT: Beep. In the cart. That fast.
+PUBLISHED DESCRIPTION: Attach a barcode scanner to Custosell POS and add products the moment they are scanned - no clicking, no typing, no queue. Try free #custosell #pos #pointofsale #sell #Custosell #SmallBusiness
+TAGS: custosell, pos, point of sale, sell, checkout, retail, payments, receipt, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Scan = add" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D56" s="5" t="n"/>
@@ -3322,7 +3874,17 @@
   - "Stock limit enforced"
 DEMO DATA: A product with stock, a service item (no stock limit).
 CTA: Try free
-RELATED: [03-sales-pos.md](./03-sales-pos.md) (first sale)</t>
+RELATED: [03-sales-pos.md](./03-sales-pos.md) (first sale)
+PUBLISHED TITLE: Two of these, three of those - in two taps.
+SHORT-FORM VARIANT: Two of these, three of those
+PUBLISHED DESCRIPTION: Adjust how many of an item you are selling right in the Custosell cart - plus/minus steppers or a quick quantity editor - with stock limits enforced automatically. Try free #custosell #pos #pointofsale #sell #Custosell #SmallBusiness
+TAGS: custosell, pos, point of sale, sell, checkout, retail, payments, receipt, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Steppers or type it" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D57" s="5" t="n"/>
@@ -3371,7 +3933,17 @@
   - "Mixed carts, priced right"
 DEMO DATA: Products with both retail and wholesale prices set.
 CTA: Try free + subscribe
-RELATED: [07-customers.md](./07-customers.md) (B2B customers)</t>
+RELATED: [07-customers.md](./07-customers.md) (B2B customers)
+PUBLISHED TITLE: One cart, two prices - retail or wholesale.
+SHORT-FORM VARIANT: One cart, two prices
+PUBLISHED DESCRIPTION: Charge wholesale prices on Custosell POS. Flip the whole cart to wholesale with one tap, or switch a single line - ideal for bulk and B2B buyers. Try free + subscribe #custosell #pos #pointofsale #sell #Custosell #SmallBusiness
+TAGS: custosell, pos, point of sale, sell, checkout, retail, payments, receipt, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Retail all / Wholesale all" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D58" s="5" t="n"/>
@@ -3419,7 +3991,17 @@
   - "Rest of cart untouched"
 DEMO DATA: A cart with 3+ items, one needing a line discount.
 CTA: Try free
-RELATED: [03-sales-pos.md](./03-sales-pos.md) (whole-cart discount)</t>
+RELATED: [03-sales-pos.md](./03-sales-pos.md) (whole-cart discount)
+PUBLISHED TITLE: Price it down on one line - not the whole cart.
+SHORT-FORM VARIANT: Price it down on one line
+PUBLISHED DESCRIPTION: Give a discount on a single item in the Custosell cart - a scratched tin, a promo line, a favour - without touching the rest of the sale. Try free #custosell #pos #pointofsale #sell #Custosell #SmallBusiness
+TAGS: custosell, pos, point of sale, sell, checkout, retail, payments, receipt, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Line-level discount" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D59" s="5" t="n"/>
@@ -3467,7 +4049,17 @@
   - "Amount off shown live"
 DEMO DATA: A cart of 3+ items and a discount to apply.
 CTA: Try free
-RELATED: [03-sales-pos.md](./03-sales-pos.md) (line discount)</t>
+RELATED: [03-sales-pos.md](./03-sales-pos.md) (line discount)
+PUBLISHED TITLE: 10% off everything - one field, done.
+SHORT-FORM VARIANT: 10% off everything
+PUBLISHED DESCRIPTION: Apply a whole-cart discount on Custosell POS as a fixed amount or a percentage. See exactly how much comes off before you take payment. Try free #custosell #pos #pointofsale #sell #Custosell #SmallBusiness
+TAGS: custosell, pos, point of sale, sell, checkout, retail, payments, receipt, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Fixed or % - your choice" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D60" s="5" t="n"/>
@@ -3515,7 +4107,17 @@
   - "Receipts carry the name"
 DEMO DATA: No customer yet; type one during the take.
 CTA: Try free
-RELATED: [07-customers.md](./07-customers.md)</t>
+RELATED: [07-customers.md](./07-customers.md)
+PUBLISHED TITLE: No profile needed - type the name and sell.
+SHORT-FORM VARIANT: No profile needed
+PUBLISHED DESCRIPTION: Attach a customer to a sale on Custosell POS without leaving the till - type a name, phone, or email and the sale is linked for receipts, invoices, and history. Try free #custosell #pos #pointofsale #sell #Custosell #SmallBusiness
+TAGS: custosell, pos, point of sale, sell, checkout, retail, payments, receipt, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Type. Link. Done." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D61" s="5" t="n"/>
@@ -3564,7 +4166,17 @@
   - "Full amount = one tap"
 DEMO DATA: A cart total that isn't a round number (e.g. 45,500 UGX).
 CTA: Try free + subscribe
-RELATED: [03-sales-pos.md](./03-sales-pos.md) (first sale)</t>
+RELATED: [03-sales-pos.md](./03-sales-pos.md) (first sale)
+PUBLISHED TITLE: The till tells you the change - every time.
+SHORT-FORM VARIANT: The till tells you the change
+PUBLISHED DESCRIPTION: Take cash on Custosell POS and let it calculate change. Enter what the customer hands you (or tap 'Full amount') and the exact change is shown before you complete the sale. Try free + subscribe #custosell #pos #pointofsale #sell #Custosell #SmallBusiness
+TAGS: custosell, pos, point of sale, sell, checkout, retail, payments, receipt, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Enter tendered. Change shown." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D62" s="5" t="n"/>
@@ -3613,7 +4225,17 @@
 DEMO DATA: A cart and a business with mobile money configured.
 CTA: Try free
 RELATED: [04-shifts.md](./04-shifts.md) (method totals),
-[03-sales-pos.md](./03-sales-pos.md) (cash change)</t>
+[03-sales-pos.md](./03-sales-pos.md) (cash change)
+PUBLISHED TITLE: Cash, Mobile Money, card, or other - one tap to switch.
+SHORT-FORM VARIANT: Cash, Mobile Money, card, or other
+PUBLISHED DESCRIPTION: Accept any payment method on Custosell POS - cash, Mobile Money, card, or other - and see collections tracked by method on your shift and reports. Try free #custosell #pos #pointofsale #sell #Custosell #SmallBusiness
+TAGS: custosell, pos, point of sale, sell, checkout, retail, payments, receipt, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Cash / Mobile / Card / Other" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D63" s="5" t="n"/>
@@ -3663,7 +4285,17 @@
 DEMO DATA: A cart of 2+ items where the customer pays part now.
 CTA: Try free
 RELATED: [03-sales-pos.md](./03-sales-pos.md) (collect balance),
-[09-accounting.md](./09-accounting.md)</t>
+[09-accounting.md](./09-accounting.md)
+PUBLISHED TITLE: They pay part now, the rest later - recorded cleanly.
+SHORT-FORM VARIANT: They pay part now, the rest later
+PUBLISHED DESCRIPTION: Let a customer pay part of a sale now on Custosell POS. Enable installments, record the first payment, and the balance stays tracked until it is settled. Try free #custosell #pos #pointofsale #sell #Custosell #SmallBusiness
+TAGS: custosell, pos, point of sale, sell, checkout, retail, payments, receipt, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Part now, rest later" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D64" s="5" t="n"/>
@@ -3711,7 +4343,17 @@
 DEMO DATA: A VAT-registered business with a cart of 2+ items.
 CTA: Try free
 RELATED: [17-settings.md](./17-settings.md) (VAT),
-[09-accounting.md](./09-accounting.md)</t>
+[09-accounting.md](./09-accounting.md)
+PUBLISHED TITLE: Subtotal, discount, VAT, total - all before you take payment.
+SHORT-FORM VARIANT: Subtotal, discount, VAT, total - all before you take
+PUBLISHED DESCRIPTION: Understand the numbers on the Custosell checkout - subtotal before tax, discount, VAT, and the final total - so you can answer the customer's questions and never misquote a price. Try free #custosell #pos #pointofsale #sell #Custosell #SmallBusiness
+TAGS: custosell, pos, point of sale, sell, checkout, retail, payments, receipt, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Subtotal - discount + VAT = total" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D65" s="5" t="n"/>
@@ -3759,7 +4401,17 @@
   - "Stock + books + dashboard updated"
 DEMO DATA: A ready cart at the payment step.
 CTA: Try free
-RELATED: [03-sales-pos.md](./03-sales-pos.md) (print/PDF/email receipt)</t>
+RELATED: [03-sales-pos.md](./03-sales-pos.md) (print/PDF/email receipt)
+PUBLISHED TITLE: One tap and the sale is done - receipt ready.
+SHORT-FORM VARIANT: One tap and the sale is done
+PUBLISHED DESCRIPTION: Finalize a sale on Custosell POS, see the confirmation, and get the receipt - ready to print, download, or email in seconds. Try free #custosell #pos #pointofsale #sell #Custosell #SmallBusiness
+TAGS: custosell, pos, point of sale, sell, checkout, retail, payments, receipt, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Complete Sale" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D66" s="5" t="n"/>
@@ -3806,7 +4458,17 @@
   - "Refresh = fresh stock"
 DEMO DATA: A product added in Inventory just before filming.
 CTA: Try free
-RELATED: [05-inventory-products.md](./05-inventory-products.md)</t>
+RELATED: [05-inventory-products.md](./05-inventory-products.md)
+PUBLISHED TITLE: New stock just arrived? Pull it into the till.
+SHORT-FORM VARIANT: New stock just arrived? Pull it into the till.
+PUBLISHED DESCRIPTION: Refresh the product list inside Custosell POS so a product added or restocked in Inventory appears at the till without restarting the app. Try free #custosell #pos #pointofsale #sell #Custosell #SmallBusiness
+TAGS: custosell, pos, point of sale, sell, checkout, retail, payments, receipt, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Refresh = fresh stock" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D67" s="5" t="n"/>
@@ -3855,7 +4517,17 @@
   - "Auto-syncs when connected"
 DEMO DATA: A device with offline mode (or network disabled) and a cart.
 CTA: Try free + subscribe
-RELATED: [21-offline-sync.md](./21-offline-sync.md)</t>
+RELATED: [21-offline-sync.md](./21-offline-sync.md)
+PUBLISHED TITLE: No internet? Keep selling - Custosell syncs when you're back.
+SHORT-FORM VARIANT: No internet? Keep selling - Custosell syncs when
+PUBLISHED DESCRIPTION: Sell normally on Custosell POS with no internet. Sales save locally, the till keeps working, and everything auto-syncs when the connection returns - stock, books, and dashboard included. Try free + subscribe #custosell #pos #pointofsale #sell #Custosell #SmallBusiness
+TAGS: custosell, pos, point of sale, sell, checkout, retail, payments, receipt, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Offline sale saved" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D68" s="5" t="n"/>
@@ -3904,7 +4576,17 @@
 order.
 CTA: Try free + subscribe
 RELATED: [03-sales-pos.md](./03-sales-pos.md) (first sale),
-[21-offline-sync.md](./21-offline-sync.md)</t>
+[21-offline-sync.md](./21-offline-sync.md)
+PUBLISHED TITLE: Customer stepped out? Hold their order - don't lose the sale.
+SHORT-FORM VARIANT: Customer stepped out? Hold their order - don't lose
+PUBLISHED DESCRIPTION: Use hold/draft orders on Custosell POS to pause a sale and come back to it later. Never lose a customer mid-purchase again. Try free + subscribe #custosell #pos #pointofsale #sell #Custosell #SmallBusiness
+TAGS: custosell, pos, point of sale, sell, checkout, retail, payments, receipt, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Hold. Not lost." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D69" s="5" t="n"/>
@@ -3952,7 +4634,17 @@
   - "Nothing re-typed"
 DEMO DATA: An existing open/held order with several items.
 CTA: Try free
-RELATED: [03-sales-pos.md](./03-sales-pos.md) (hold an order)</t>
+RELATED: [03-sales-pos.md](./03-sales-pos.md) (hold an order)
+PUBLISHED TITLE: They're back. Their cart is still here.
+SHORT-FORM VARIANT: They're back. Their cart is still here.
+PUBLISHED DESCRIPTION: Resume a held order on Custosell POS - the exact items and customer come back to the till and you complete the sale where you left off. Try free #custosell #pos #pointofsale #sell #Custosell #SmallBusiness
+TAGS: custosell, pos, point of sale, sell, checkout, retail, payments, receipt, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Resume = exact cart back" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D70" s="5" t="n"/>
@@ -3999,7 +4691,17 @@
   - "Rename = findable"
 DEMO DATA: Two or more held orders to distinguish.
 CTA: Try free
-RELATED: [03-sales-pos.md](./03-sales-pos.md) (take an order)</t>
+RELATED: [03-sales-pos.md](./03-sales-pos.md) (take an order)
+PUBLISHED TITLE: Name it 'Table 5' or 'John's order' - find it in seconds.
+SHORT-FORM VARIANT: Name it 'Table 5' or 'John's order' - find it in
+PUBLISHED DESCRIPTION: Rename a held order or add notes on Custosell POS so you can find the right cart fast - by customer name, table number, or any note. Try free #custosell #pos #pointofsale #sell #Custosell #SmallBusiness
+TAGS: custosell, pos, point of sale, sell, checkout, retail, payments, receipt, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Rename = findable" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D71" s="5" t="n"/>
@@ -4047,7 +4749,17 @@
   - "Update, not rebuild"
 DEMO DATA: An open order that needs an item added and one removed.
 CTA: Try free
-RELATED: [03-sales-pos.md](./03-sales-pos.md) (hold/take orders)</t>
+RELATED: [03-sales-pos.md](./03-sales-pos.md) (hold/take orders)
+PUBLISHED TITLE: Change a held order - items, quantity, customer - and save.
+SHORT-FORM VARIANT: Change a held order - items, quantity, customer - and
+PUBLISHED DESCRIPTION: Edit an existing open order on Custosell POS - add or remove items, change quantities, fix the customer - then save the changes back to the order. Try free #custosell #pos #pointofsale #sell #Custosell #SmallBusiness
+TAGS: custosell, pos, point of sale, sell, checkout, retail, payments, receipt, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Update, not rebuild" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D72" s="5" t="n"/>
@@ -4093,7 +4805,17 @@
   - "Cancel = clean list"
 DEMO DATA: An open order you are willing to cancel.
 CTA: Try free
-RELATED: [03-sales-pos.md](./03-sales-pos.md) (hold an order)</t>
+RELATED: [03-sales-pos.md](./03-sales-pos.md) (hold an order)
+PUBLISHED TITLE: Customer walked? Cancel the order - cleanly.
+SHORT-FORM VARIANT: Customer walked? Cancel the order
+PUBLISHED DESCRIPTION: Cancel a held order on Custosell POS when the customer is gone for good - it leaves Take Order and no stock is touched. Try free #custosell #pos #pointofsale #sell #Custosell #SmallBusiness
+TAGS: custosell, pos, point of sale, sell, checkout, retail, payments, receipt, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Cancel = clean list" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D73" s="5" t="n"/>
@@ -4141,7 +4863,17 @@
   - "Held, sold, invoiced, cancelled"
 DEMO DATA: Orders in more than one status, from two branches.
 CTA: Try free
-RELATED: [03-sales-pos.md](./03-sales-pos.md) (take/update/cancel)</t>
+RELATED: [03-sales-pos.md](./03-sales-pos.md) (take/update/cancel)
+PUBLISHED TITLE: Open, completed, invoiced, cancelled - every order in one view.
+SHORT-FORM VARIANT: Open, completed, invoiced, cancelled - every order in
+PUBLISHED DESCRIPTION: Use the Orders page on Custosell to track every order - held, completed, invoiced, or cancelled - with tabs, search, branch filter, and quick actions. Try free #custosell #pos #pointofsale #sell #Custosell #SmallBusiness
+TAGS: custosell, pos, point of sale, sell, checkout, retail, payments, receipt, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Held, sold, invoiced, cancelled" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D74" s="5" t="n"/>
@@ -4192,7 +4924,17 @@
 DEMO DATA: At least one order with source 'storefront' and a delivery
 address.
 CTA: Try free + subscribe
-RELATED: [14-storefront.md](./14-storefront.md)</t>
+RELATED: [14-storefront.md](./14-storefront.md)
+PUBLISHED TITLE: Orders placed online, fulfilled at your till.
+SHORT-FORM VARIANT: Orders placed online
+PUBLISHED DESCRIPTION: See orders placed through your online storefront right inside Custosell - spot them with the Online filter, view the delivery address, and reach the customer by phone or WhatsApp. Try free + subscribe #custosell #pos #pointofsale #sell #Custosell #SmallBusiness
+TAGS: custosell, pos, point of sale, sell, checkout, retail, payments, receipt, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Online = storefront orders" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D75" s="5" t="n"/>
@@ -4239,7 +4981,17 @@
   - "Net + refunds summary live"
 DEMO DATA: Sales across several days, branches, and statuses.
 CTA: Try free
-RELATED: [02-dashboard-reports.md](./02-dashboard-reports.md)</t>
+RELATED: [02-dashboard-reports.md](./02-dashboard-reports.md)
+PUBLISHED TITLE: Every receipt, every day - searchable in seconds.
+SHORT-FORM VARIANT: Every receipt, every day
+PUBLISHED DESCRIPTION: Find any sale on Custosell by receipt number, branch, or status, with net revenue and total refunds for the current view shown up top. Try free #custosell #pos #pointofsale #sell #Custosell #SmallBusiness
+TAGS: custosell, pos, point of sale, sell, checkout, retail, payments, receipt, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Search by receipt number" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D76" s="5" t="n"/>
@@ -4287,7 +5039,17 @@
   - "Badge = sale health"
 DEMO DATA: Sales in all four payment statuses.
 CTA: Try free
-RELATED: [03-sales-pos.md](./03-sales-pos.md) (refund a sale)</t>
+RELATED: [03-sales-pos.md](./03-sales-pos.md) (refund a sale)
+PUBLISHED TITLE: Paid, partial, refunded - the badge tells the story.
+SHORT-FORM VARIANT: Paid, partial, refunded
+PUBLISHED DESCRIPTION: Read the payment status badges on Custosell sales - Paid, Partially Paid, Partially Refunded, and Full Refund - plus fiscal status, so the health of any sale is obvious at a glance. Try free #custosell #pos #pointofsale #sell #Custosell #SmallBusiness
+TAGS: custosell, pos, point of sale, sell, checkout, retail, payments, receipt, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Badge = sale health" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D77" s="5" t="n"/>
@@ -4333,7 +5095,17 @@
   - "Select. Delete. Confirm."
 DEMO DATA: A few clearly disposable sales to delete.
 CTA: Try free
-RELATED: [03-sales-pos.md](./03-sales-pos.md) (sales history)</t>
+RELATED: [03-sales-pos.md](./03-sales-pos.md) (sales history)
+PUBLISHED TITLE: Clean out test or duplicate sales - in bulk, with a warning.
+SHORT-FORM VARIANT: Clean out test or duplicate sales - in bulk, with a
+PUBLISHED DESCRIPTION: Delete multiple sales at once on Custosell - select rows (or Select All), confirm, and remove them. Use sparingly; deletion is permanent. Try free #custosell #pos #pointofsale #sell #Custosell #SmallBusiness
+TAGS: custosell, pos, point of sale, sell, checkout, retail, payments, receipt, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Select. Delete. Confirm." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D78" s="5" t="n"/>
@@ -4383,7 +5155,17 @@
   - "Balance collected, tracked"
 DEMO DATA: A partially paid sale with a balance due.
 CTA: Try free
-RELATED: [03-sales-pos.md](./03-sales-pos.md) (installments)</t>
+RELATED: [03-sales-pos.md](./03-sales-pos.md) (installments)
+PUBLISHED TITLE: Paid part, paid more, still owed - see every payment.
+SHORT-FORM VARIANT: Paid part, paid more, still owed
+PUBLISHED DESCRIPTION: Open a sale's payment history on Custosell and record the remaining balance when the customer settles up - each payment stays on the receipt trail. Try free #custosell #pos #pointofsale #sell #Custosell #SmallBusiness
+TAGS: custosell, pos, point of sale, sell, checkout, retail, payments, receipt, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Payment trail per sale" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D79" s="5" t="n"/>
@@ -4430,7 +5212,17 @@
   - "Branded, clean, consistent"
 DEMO DATA: A completed sale.
 CTA: Try free
-RELATED: [03-sales-pos.md](./03-sales-pos.md) (email receipt)</t>
+RELATED: [03-sales-pos.md](./03-sales-pos.md) (email receipt)
+PUBLISHED TITLE: Print it, or save the receipt as a PDF - your call.
+SHORT-FORM VARIANT: Print it, or save the receipt as a PDF
+PUBLISHED DESCRIPTION: Print a sale receipt from Custosell or save it as a PDF file - from the sale's payment view, ready for the customer or your records. Try free #custosell #pos #pointofsale #sell #Custosell #SmallBusiness
+TAGS: custosell, pos, point of sale, sell, checkout, retail, payments, receipt, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "PDF or print" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D80" s="5" t="n"/>
@@ -4477,7 +5269,17 @@
   - "Receipt sent"
 DEMO DATA: A completed sale with a customer email.
 CTA: Try free
-RELATED: [03-sales-pos.md](./03-sales-pos.md) (print/PDF receipt)</t>
+RELATED: [03-sales-pos.md](./03-sales-pos.md) (print/PDF receipt)
+PUBLISHED TITLE: Email the receipt before the customer reaches the door.
+SHORT-FORM VARIANT: Email the receipt before the customer reaches the door.
+PUBLISHED DESCRIPTION: Send a digital receipt from Custosell POS in one tap - no printer needed. Customers get a clean copy by email. Try free #custosell #pos #pointofsale #sell #Custosell #SmallBusiness
+TAGS: custosell, pos, point of sale, sell, checkout, retail, payments, receipt, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "No printer needed" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D81" s="5" t="n"/>
@@ -4526,7 +5328,17 @@
   - "No double-counted revenue"
 DEMO DATA: A completed sale with line items and a customer.
 CTA: Try free
-RELATED: [03-sales-pos.md](./03-sales-pos.md) (B2B invoices)</t>
+RELATED: [03-sales-pos.md](./03-sales-pos.md) (B2B invoices)
+PUBLISHED TITLE: A sale already made - now bill it properly.
+SHORT-FORM VARIANT: A sale already made
+PUBLISHED DESCRIPTION: Turn a completed sale on Custosell into a proper invoice with the line items already filled in - no double-posting, balance carried automatically. Try free #custosell #pos #pointofsale #sell #Custosell #SmallBusiness
+TAGS: custosell, pos, point of sale, sell, checkout, retail, payments, receipt, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Sale to invoice in one tap" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D82" s="5" t="n"/>
@@ -4572,7 +5384,17 @@
   - "Cart -&gt; invoice"
 DEMO DATA: A cart with 2+ items and a discount set.
 CTA: Try free
-RELATED: [03-sales-pos.md](./03-sales-pos.md) (invoice from sale)</t>
+RELATED: [03-sales-pos.md](./03-sales-pos.md) (invoice from sale)
+PUBLISHED TITLE: Cart ready, customer wants a bill - make it an invoice.
+SHORT-FORM VARIANT: Cart ready, customer wants a bill
+PUBLISHED DESCRIPTION: Turn the current POS cart into a draft invoice on Custosell before completing the sale - adjust items, then save or send. Try free #custosell #pos #pointofsale #sell #Custosell #SmallBusiness
+TAGS: custosell, pos, point of sale, sell, checkout, retail, payments, receipt, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Cart -&gt; invoice" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D83" s="5" t="n"/>
@@ -4623,7 +5445,18 @@
 DEMO DATA: A B2B customer, a product/service catalog.
 CTA: Try free + subscribe
 RELATED: [08-expenses-budgets-income.md](./08-expenses-budgets-income.md),
-[09-accounting.md](./09-accounting.md)</t>
+[09-accounting.md](./09-accounting.md)
+PUBLISHED TITLE: Invoices that look like you - send, track, and get paid.
+SHORT-FORM VARIANT: Invoices that look like you - send, track, and get
+PUBLISHED DESCRIPTION: Full walkthrough of Custosell invoicing - create an invoice, send it to a customer, record their payment, and keep every PDF on file. Great for B2B and wholesale shops. Try free + subscribe #custosell #pos #pointofsale #sell #Custosell #SmallBusiness
+TAGS: custosell, pos, point of sale, sell, checkout, retail, payments, receipt, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Send. Track. Get paid." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover
+  - Intro / outro: 2s animated logo intro + end screen with subscribe</t>
         </is>
       </c>
       <c r="D84" s="5" t="n"/>
@@ -4672,7 +5505,17 @@
   - "Stock + books fix themselves"
 DEMO DATA: A sale from earlier today with a paid payment.
 CTA: Try free + subscribe
-RELATED: [09-accounting.md](./09-accounting.md)</t>
+RELATED: [09-accounting.md](./09-accounting.md)
+PUBLISHED TITLE: Refunds that don't wreck your books.
+SHORT-FORM VARIANT: Refunds that don't wreck your books.
+PUBLISHED DESCRIPTION: Process a refund on Custosell POS the right way - full or partial, item by item. Refunds update stock, accounting, and reports automatically so your numbers stay honest. Try free + subscribe #custosell #pos #pointofsale #sell #Custosell #SmallBusiness
+TAGS: custosell, pos, point of sale, sell, checkout, retail, payments, receipt, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Refund in 3 taps" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D85" s="5" t="n"/>
@@ -4721,7 +5564,17 @@
   - "Refund capped at what was paid"
 DEMO DATA: A sale that was partially refunded before.
 CTA: Try free
-RELATED: [03-sales-pos.md](./03-sales-pos.md) (refund a sale)</t>
+RELATED: [03-sales-pos.md](./03-sales-pos.md) (refund a sale)
+PUBLISHED TITLE: How much can you refund? The app guards it.
+SHORT-FORM VARIANT: How much can you refund? The app guards it.
+PUBLISHED DESCRIPTION: Learn how Custosell computes refund amounts - what was paid vs the total, previously refunded lines, and the net remaining - so a refund can never exceed what the customer actually paid. Try free #custosell #pos #pointofsale #sell #Custosell #SmallBusiness
+TAGS: custosell, pos, point of sale, sell, checkout, retail, payments, receipt, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Refund capped at what was paid" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D86" s="5" t="n"/>
@@ -4795,7 +5648,17 @@
 · `/sales/batch` (offline sync) · `/sales/bulk-delete` · `/sales/{id}/refund` ·
 `/sales/{id}/payment` · `/sales/{id}/customer` · `/sales/{id}/pdf` ·
 `/sales/{id}/email` · `/orders` (index/store) · `/orders/{id}` (show/update) ·
-`/orders/{id}/cancel` · `/invoices` CRUD + `/send` `/payment` `/email` `/pdf`</t>
+`/orders/{id}/cancel` · `/invoices` CRUD + `/send` `/payment` `/email` `/pdf`
+PUBLISHED TITLE: Refund offline? Saved - and synced when you're back.
+SHORT-FORM VARIANT: Refund offline? Saved
+PUBLISHED DESCRIPTION: Process a refund with no internet on Custosell. It saves locally and syncs when you reconnect; sales that haven't synced yet are protected from being refunded early. Try free #custosell #pos #pointofsale #sell #Custosell #SmallBusiness
+TAGS: custosell, pos, point of sale, sell, checkout, retail, payments, receipt, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Saved locally, syncs later" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D87" s="5" t="n"/>
@@ -4842,7 +5705,17 @@
   - "Today at a glance"
 DEMO DATA: A business with sales today.
 CTA: Try free + subscribe
-RELATED: [04-shifts.md](./04-shifts.md) (day close)</t>
+RELATED: [04-shifts.md](./04-shifts.md) (day close)
+PUBLISHED TITLE: Know your numbers at a glance.
+SHORT-FORM VARIANT: Know your numbers at a glance.
+PUBLISHED DESCRIPTION: Read your Custosell dashboard - net sales today, transactions, products sold, expenses, and total customers - all on one screen when you open the app. Try free + subscribe #custosell #dashboard #reports #salesreport #Custosell #SmallBusiness
+TAGS: custosell, dashboard, reports, sales report, net sales, vat, branch, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Today at a glance" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D88" s="5" t="n"/>
@@ -4890,7 +5763,17 @@
 DEMO DATA: A day with sales, a refund, and an expense recorded.
 CTA: Try free
 RELATED: [03-sales-pos.md](./03-sales-pos.md) (refunds),
-[08-expenses-budgets-income.md](./08-expenses-budgets-income.md)</t>
+[08-expenses-budgets-income.md](./08-expenses-budgets-income.md)
+PUBLISHED TITLE: Net sales = gross - refunds - expenses. Here's the math.
+SHORT-FORM VARIANT: Net sales = gross - refunds - expenses. Here's the
+PUBLISHED DESCRIPTION: See exactly how Custosell computes Net Sales Today on your dashboard - gross sales minus refunds minus expenses - so the number always makes sense. Try free #custosell #dashboard #reports #salesreport #Custosell #SmallBusiness
+TAGS: custosell, dashboard, reports, sales report, net sales, vat, branch, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Gross - refunds - expenses = net" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D89" s="5" t="n"/>
@@ -4939,7 +5822,17 @@
 DEMO DATA: At least a week of sales history.
 CTA: Try free + subscribe
 RELATED: [02-dashboard-reports.md](./02-dashboard-reports.md)
-(net sales), [03-sales-pos.md](./03-sales-pos.md)</t>
+(net sales), [03-sales-pos.md](./03-sales-pos.md)
+PUBLISHED TITLE: Is the week going up or down? The trend chart tells you.
+SHORT-FORM VARIANT: Is the week going up or down? The trend chart tells
+PUBLISHED DESCRIPTION: Read the 7-Day Net Sales Trend chart on your Custosell dashboard - daily net sales across the whole business, the average line, and how refunds plus expenses eat into gross. Try free + subscribe #custosell #dashboard #reports #salesreport #Custosell #SmallBusiness
+TAGS: custosell, dashboard, reports, sales report, net sales, vat, branch, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Daily net after refunds" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D90" s="5" t="n"/>
@@ -4986,7 +5879,17 @@
 DEMO DATA: At least one product near its low-stock threshold.
 CTA: Try free + subscribe
 RELATED: [05-inventory-products.md](./05-inventory-products.md),
-[06-marketplace-purchase-orders.md](./06-marketplace-purchase-orders.md)</t>
+[06-marketplace-purchase-orders.md](./06-marketplace-purchase-orders.md)
+PUBLISHED TITLE: Low stock? The dashboard tells you before customers notice.
+SHORT-FORM VARIANT: Low stock? The dashboard tells you before customers
+PUBLISHED DESCRIPTION: Spot low-stock alerts right on your Custosell dashboard - items at or below their threshold - and restock before you run out. Try free + subscribe #custosell #dashboard #reports #salesreport #Custosell #SmallBusiness
+TAGS: custosell, dashboard, reports, sales report, net sales, vat, branch, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Low: X / threshold Y" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D91" s="5" t="n"/>
@@ -5033,7 +5936,17 @@
   - "Live today's receipts"
 DEMO DATA: Several sales recorded today.
 CTA: Try free
-RELATED: [03-sales-pos.md](./03-sales-pos.md)</t>
+RELATED: [03-sales-pos.md](./03-sales-pos.md)
+PUBLISHED TITLE: Watch today's sales roll in, live.
+SHORT-FORM VARIANT: Watch today's sales roll in
+PUBLISHED DESCRIPTION: Use the Recent Activity panel on your Custosell dashboard to see today's sales as they happen - receipt number, payment method, and amount, with refunds flagged. Try free #custosell #dashboard #reports #salesreport #Custosell #SmallBusiness
+TAGS: custosell, dashboard, reports, sales report, net sales, vat, branch, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Live today's receipts" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D92" s="5" t="n"/>
@@ -5079,7 +5992,17 @@
   - "Today's leaks, visible"
 DEMO DATA: A few expenses in different categories today.
 CTA: Try free
-RELATED: [08-expenses-budgets-income.md](./08-expenses-budgets-income.md)</t>
+RELATED: [08-expenses-budgets-income.md](./08-expenses-budgets-income.md)
+PUBLISHED TITLE: Where did today's money go? The pie chart knows.
+SHORT-FORM VARIANT: Where did today's money go? The pie chart knows.
+PUBLISHED DESCRIPTION: Read the Today's Expenses by Category pie chart on your Custosell dashboard - a quick visual of what's eating today's profit. Try free #custosell #dashboard #reports #salesreport #Custosell #SmallBusiness
+TAGS: custosell, dashboard, reports, sales report, net sales, vat, branch, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Today's leaks, visible" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D93" s="5" t="n"/>
@@ -5129,7 +6052,17 @@
 DEMO DATA: A VAT-registered business with sales today.
 CTA: Try free + subscribe
 RELATED: [17-settings.md](./17-settings.md) (VAT registration),
-[02-dashboard-reports.md](./02-dashboard-reports.md) (VAT summary report)</t>
+[02-dashboard-reports.md](./02-dashboard-reports.md) (VAT summary report)
+PUBLISHED TITLE: Output VAT, input VAT, and what's payable - today.
+SHORT-FORM VARIANT: Output VAT, input VAT, and what's payable
+PUBLISHED DESCRIPTION: Read the VAT-today section on your Custosell dashboard - net output VAT, input VAT you can claim, and estimated VAT payable, updated as you sell. Try free + subscribe #custosell #dashboard #reports #salesreport #Custosell #SmallBusiness
+TAGS: custosell, dashboard, reports, sales report, net sales, vat, branch, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "VAT tracked separately from cash" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D94" s="5" t="n"/>
@@ -5177,7 +6110,17 @@
 DEMO DATA: Two branches with different sales.
 CTA: Try free
 RELATED: [01-account-auth-security.md](./01-account-auth-security.md),
-[02-dashboard-reports.md](./02-dashboard-reports.md) (branch report)</t>
+[02-dashboard-reports.md](./02-dashboard-reports.md) (branch report)
+PUBLISHED TITLE: Which branch is winning this week?
+SHORT-FORM VARIANT: Which branch is winning this week?
+PUBLISHED DESCRIPTION: Compare sales performance across your branches on Custosell - today, this week, this month, or this year - and see where to focus. Try free #custosell #dashboard #reports #salesreport #Custosell #SmallBusiness
+TAGS: custosell, dashboard, reports, sales report, net sales, vat, branch, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Branch vs branch" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D95" s="5" t="n"/>
@@ -5227,7 +6170,17 @@
 DEMO DATA: Sales and expense history for the period.
 CTA: Try free + subscribe
 RELATED: [02-dashboard-reports.md](./02-dashboard-reports.md)
-(each report), [10-documents.md](./10-documents.md)</t>
+(each report), [10-documents.md](./10-documents.md)
+PUBLISHED TITLE: PDF, Excel, or CSV - download any report in seconds.
+SHORT-FORM VARIANT: PDF, Excel, or CSV
+PUBLISHED DESCRIPTION: Use the Download Business Reports panel on your Custosell dashboard to generate and download any report - business summary, daily sales, product performance, and more - in PDF, Excel, or CSV. Try free + subscribe #custosell #dashboard #reports #salesreport #Custosell #SmallBusiness
+TAGS: custosell, dashboard, reports, sales report, net sales, vat, branch, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Pick. Set. Download." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D96" s="5" t="n"/>
@@ -5273,7 +6226,17 @@
   - "Any window, your way"
 DEMO DATA: Sales across multiple periods.
 CTA: Try free
-RELATED: [02-dashboard-reports.md](./02-dashboard-reports.md)</t>
+RELATED: [02-dashboard-reports.md](./02-dashboard-reports.md)
+PUBLISHED TITLE: Today, week, month, year - or any custom range.
+SHORT-FORM VARIANT: Today, week, month, year
+PUBLISHED DESCRIPTION: Set the exact date range for any Custosell report - preset periods or a custom from/to - so you always report the right window. Try free #custosell #dashboard #reports #salesreport #Custosell #SmallBusiness
+TAGS: custosell, dashboard, reports, sales report, net sales, vat, branch, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Any window, your way" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D97" s="5" t="n"/>
@@ -5319,7 +6282,17 @@
   - "Filter by person or shift"
 DEMO DATA: Two staff members with shifts and sales.
 CTA: Try free
-RELATED: [04-shifts.md](./04-shifts.md), [15-hr.md](./15-hr.md)</t>
+RELATED: [04-shifts.md](./04-shifts.md), [15-hr.md](./15-hr.md)
+PUBLISHED TITLE: One report, one cashier - or one shift.
+SHORT-FORM VARIANT: One report, one cashier
+PUBLISHED DESCRIPTION: Narrow any Custosell report to a specific sales person or a specific shift - great for payroll, disputes, and accountability. Try free #custosell #dashboard #reports #salesreport #Custosell #SmallBusiness
+TAGS: custosell, dashboard, reports, sales report, net sales, vat, branch, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Filter by person or shift" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D98" s="5" t="n"/>
@@ -5366,7 +6339,17 @@
   - "P&amp;L snapshot, on demand"
 DEMO DATA: Sales + expenses in the period.
 CTA: Try free
-RELATED: [09-accounting.md](./09-accounting.md)</t>
+RELATED: [09-accounting.md](./09-accounting.md)
+PUBLISHED TITLE: Am I making money? One report answers it.
+SHORT-FORM VARIANT: Am I making money? One report answers it.
+PUBLISHED DESCRIPTION: Generate the Business Summary report on Custosell - a P&amp;L snapshot for any period - and see your bottom line clearly. Try free #custosell #dashboard #reports #salesreport #Custosell #SmallBusiness
+TAGS: custosell, dashboard, reports, sales report, net sales, vat, branch, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "P&amp;L snapshot, on demand" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D99" s="5" t="n"/>
@@ -5414,7 +6397,17 @@
 DEMO DATA: A day with several sales, at least one refund.
 CTA: Try free
 RELATED: [03-sales-pos.md](./03-sales-pos.md),
-[04-shifts.md](./04-shifts.md)</t>
+[04-shifts.md](./04-shifts.md)
+PUBLISHED TITLE: Every transaction, with line items and refunds.
+SHORT-FORM VARIANT: Every transaction
+PUBLISHED DESCRIPTION: Pull the Daily Sales report on Custosell - full transactions with line items and refunds for any day - and reconcile the till with confidence. Try free #custosell #dashboard #reports #salesreport #Custosell #SmallBusiness
+TAGS: custosell, dashboard, reports, sales report, net sales, vat, branch, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Transactions + line items + refunds" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D100" s="5" t="n"/>
@@ -5462,7 +6455,17 @@
   - "Sell more of what sells"
 DEMO DATA: Products with varied sales history.
 CTA: Try free
-RELATED: [05-inventory-products.md](./05-inventory-products.md)</t>
+RELATED: [05-inventory-products.md](./05-inventory-products.md)
+PUBLISHED TITLE: Your top products and the ones killing you.
+SHORT-FORM VARIANT: Your top products and the ones killing you.
+PUBLISHED DESCRIPTION: Use the Product Performance report on Custosell to see top sellers by revenue and quantity, slow movers, and products with no sales - then stock smarter. Try free #custosell #dashboard #reports #salesreport #Custosell #SmallBusiness
+TAGS: custosell, dashboard, reports, sales report, net sales, vat, branch, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Sell more of what sells" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D101" s="5" t="n"/>
@@ -5508,7 +6511,17 @@
   - "Drawer balanced, proven"
 DEMO DATA: Closed shifts with cash movements.
 CTA: Try free
-RELATED: [04-shifts.md](./04-shifts.md)</t>
+RELATED: [04-shifts.md](./04-shifts.md)
+PUBLISHED TITLE: Cash handover and shift totals - balanced, on record.
+SHORT-FORM VARIANT: Cash handover and shift totals
+PUBLISHED DESCRIPTION: Generate the Shift Reconciliation report on Custosell - cash handover and shift totals - and prove the drawer balances for any shift. Try free #custosell #dashboard #reports #salesreport #Custosell #SmallBusiness
+TAGS: custosell, dashboard, reports, sales report, net sales, vat, branch, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Drawer balanced, proven" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D102" s="5" t="n"/>
@@ -5554,7 +6567,17 @@
   - "Every category, one file"
 DEMO DATA: Expenses across several categories.
 CTA: Try free
-RELATED: [08-expenses-budgets-income.md](./08-expenses-budgets-income.md)</t>
+RELATED: [08-expenses-budgets-income.md](./08-expenses-budgets-income.md)
+PUBLISHED TITLE: Your expenses, by category, with P&amp;L context.
+SHORT-FORM VARIANT: Your expenses
+PUBLISHED DESCRIPTION: Pull the Expenses report on Custosell - expense breakdown by category with P&amp;L context - and see where money is leaking. Try free #custosell #dashboard #reports #salesreport #Custosell #SmallBusiness
+TAGS: custosell, dashboard, reports, sales report, net sales, vat, branch, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Every category, one file" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D103" s="5" t="n"/>
@@ -5601,7 +6624,17 @@
 DEMO DATA: A VAT-registered business with sales and expenses.
 CTA: Try free + subscribe
 RELATED: [17-settings.md](./17-settings.md) (VAT registration),
-[09-accounting.md](./09-accounting.md)</t>
+[09-accounting.md](./09-accounting.md)
+PUBLISHED TITLE: Output VAT, input VAT, and estimated VAT payable.
+SHORT-FORM VARIANT: Output VAT
+PUBLISHED DESCRIPTION: Generate the VAT Summary report on Custosell - output VAT, input VAT, and estimated VAT payable for your jurisdiction - ready for filing. Try free + subscribe #custosell #dashboard #reports #salesreport #Custosell #SmallBusiness
+TAGS: custosell, dashboard, reports, sales report, net sales, vat, branch, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "VAT, ready to file" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D104" s="5" t="n"/>
@@ -5648,7 +6681,17 @@
 DEMO DATA: A product catalog with varied stock levels.
 CTA: Try free
 RELATED: [05-inventory-products.md](./05-inventory-products.md),
-[06-marketplace-purchase-orders.md](./06-marketplace-purchase-orders.md)</t>
+[06-marketplace-purchase-orders.md](./06-marketplace-purchase-orders.md)
+PUBLISHED TITLE: Stock levels, values, and low-stock alerts - one file.
+SHORT-FORM VARIANT: Stock levels, values, and low-stock alerts
+PUBLISHED DESCRIPTION: Export the Inventory report on Custosell - stock levels, values, and low-stock alerts as of today - and plan your next order. Try free #custosell #dashboard #reports #salesreport #Custosell #SmallBusiness
+TAGS: custosell, dashboard, reports, sales report, net sales, vat, branch, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Snapshot as of today" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D105" s="5" t="n"/>
@@ -5695,7 +6738,17 @@
 DEMO DATA: Sales across multiple payment methods.
 CTA: Try free
 RELATED: [03-sales-pos.md](./03-sales-pos.md),
-[17-settings.md](./17-settings.md) (payment methods)</t>
+[17-settings.md](./17-settings.md) (payment methods)
+PUBLISHED TITLE: Cash, Mobile Money, card - see the mix.
+SHORT-FORM VARIANT: Cash, Mobile Money, card
+PUBLISHED DESCRIPTION: Pull the Payment Breakdown report on Custosell - collections by payment method, net after refunds - and understand how customers pay. Try free #custosell #dashboard #reports #salesreport #Custosell #SmallBusiness
+TAGS: custosell, dashboard, reports, sales report, net sales, vat, branch, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Cash vs Mobile Money vs card" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D106" s="5" t="n"/>
@@ -5765,7 +6818,17 @@
 `/reports/daily-sales` · `/reports/sales-trend` · `/reports/product-performance`
 · `/reports/shift-reconciliation` · `/reports/shift-close` ·
 `/reports/expenses` · `/reports/vat-summary` · `/reports/inventory` ·
-`/reports/payment-breakdown` · `/reports/branch-performance`</t>
+`/reports/payment-breakdown` · `/reports/branch-performance`
+PUBLISHED TITLE: Every branch gross, expenses, net, transactions, share.
+SHORT-FORM VARIANT: Every branch: gross, expenses, net, transactions
+PUBLISHED DESCRIPTION: Open the full Branch Performance report on Custosell - per branch gross, expenses, net sales, transactions, and market share - for any period, right on screen. Try free #custosell #dashboard #reports #salesreport #Custosell #SmallBusiness
+TAGS: custosell, dashboard, reports, sales report, net sales, vat, branch, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Branch: gross, net, share" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D107" s="5" t="n"/>
@@ -5813,7 +6876,17 @@
 DEMO DATA: A seeded business with products and at least one staff
 user.
 CTA: Try free + subscribe
-RELATED: [03-sales-pos.md](./03-sales-pos.md) (first sale)</t>
+RELATED: [03-sales-pos.md](./03-sales-pos.md) (first sale)
+PUBLISHED TITLE: Open your shift in seconds - and know exactly how you start.
+SHORT-FORM VARIANT: Open your shift in seconds - and know exactly how you
+PUBLISHED DESCRIPTION: Learn how to open a shift on Custosell POS. Every sale you make is now tied to this shift, so who sold what is always traceable. Try free + subscribe #custosell #shift #openingbalance #cashdrawer #Custosell #SmallBusiness
+TAGS: custosell, shift, opening balance, cash drawer, close shift, attendance, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Open in one tap" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D108" s="5" t="n"/>
@@ -5861,7 +6934,17 @@
   - "Expected drawer = float + sales"
 DEMO DATA: An open shift with no opening balance yet.
 CTA: Try free
-RELATED: [04-shifts.md](./04-shifts.md) (balance your shift)</t>
+RELATED: [04-shifts.md](./04-shifts.md) (balance your shift)
+PUBLISHED TITLE: Start with a float? Record it - your drawer stays honest.
+SHORT-FORM VARIANT: Start with a float? Record it - your drawer stays
+PUBLISHED DESCRIPTION: Set the cash float you put in the drawer when your shift starts on Custosell. It becomes part of the expected cash at handover, or remove it if you started with nothing. Try free #custosell #shift #openingbalance #cashdrawer #Custosell #SmallBusiness
+TAGS: custosell, shift, opening balance, cash drawer, close shift, attendance, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Float recorded" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D109" s="5" t="n"/>
@@ -5909,7 +6992,17 @@
   - "Reduces cash at handover"
 DEMO DATA: An open shift with sales, plus an expense category.
 CTA: Try free
-RELATED: [08-expenses-budgets-income.md](./08-expenses-budgets-income.md)</t>
+RELATED: [08-expenses-budgets-income.md](./08-expenses-budgets-income.md)
+PUBLISHED TITLE: Transport, delivery, petty cash - log it against the shift.
+SHORT-FORM VARIANT: Transport, delivery, petty cash - log it against the
+PUBLISHED DESCRIPTION: Record an expense paid from the cash drawer on Custosell while a shift is open. It reduces the cash at handover and shows up in the shift summary and expense reports. Try free #custosell #shift #openingbalance #cashdrawer #Custosell #SmallBusiness
+TAGS: custosell, shift, opening balance, cash drawer, close shift, attendance, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Drawer expense logged" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D110" s="5" t="n"/>
@@ -5959,7 +7052,17 @@
   - "Balanced / Over / Short"
 DEMO DATA: An open shift with sales and some cash in the drawer.
 CTA: Try free
-RELATED: [04-shifts.md](./04-shifts.md) (opening balance)</t>
+RELATED: [04-shifts.md](./04-shifts.md) (opening balance)
+PUBLISHED TITLE: Count the drawer any time - know where the shift stands.
+SHORT-FORM VARIANT: Count the drawer any time - know where the shift
+PUBLISHED DESCRIPTION: Reconcile the cash drawer mid-shift on Custosell - set the starting cash and count what's in the drawer now. See expected cash and variance before you even close. Try free #custosell #shift #openingbalance #cashdrawer #Custosell #SmallBusiness
+TAGS: custosell, shift, opening balance, cash drawer, close shift, attendance, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Expected vs counted, live" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D111" s="5" t="n"/>
@@ -6009,7 +7112,17 @@
 DEMO DATA: An open shift with several sales and an expense.
 CTA: Try free + subscribe
 RELATED: [02-dashboard-reports.md](./02-dashboard-reports.md),
-[04-shifts.md](./04-shifts.md) (shift report)</t>
+[04-shifts.md](./04-shifts.md) (shift report)
+PUBLISHED TITLE: Close the day and balance the drawer - in one minute.
+SHORT-FORM VARIANT: Close the day and balance the drawer
+PUBLISHED DESCRIPTION: Close your shift on Custosell with a full drawer reconciliation. Count the cash, compare it to the expected amount, and end the shift - a mismatch is recorded, not blocked. Try free + subscribe #custosell #shift #openingbalance #cashdrawer #Custosell #SmallBusiness
+TAGS: custosell, shift, opening balance, cash drawer, close shift, attendance, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Count. Compare. Close." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D112" s="5" t="n"/>
@@ -6058,7 +7171,17 @@
 DEMO DATA: An open shift with sales, refunds, expenses, and VAT.
 CTA: Try free
 RELATED: [04-shifts.md](./04-shifts.md) (close your shift),
-[02-dashboard-reports.md](./02-dashboard-reports.md) (shift report)</t>
+[02-dashboard-reports.md](./02-dashboard-reports.md) (shift report)
+PUBLISHED TITLE: Your whole shift, on one printable report.
+SHORT-FORM VARIANT: Your whole shift
+PUBLISHED DESCRIPTION: Open the shift close report on Custosell - gross, expenses, refunds, VAT, net sales, cash by method, and expected drawer - then print it or download it as a PDF. Try free #custosell #shift #openingbalance #cashdrawer #Custosell #SmallBusiness
+TAGS: custosell, shift, opening balance, cash drawer, close shift, attendance, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "One page, whole shift" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D113" s="5" t="n"/>
@@ -6108,7 +7231,17 @@
   - "Expected drawer updates live"
 DEMO DATA: An open shift with sales across multiple methods.
 CTA: Try free
-RELATED: [04-shifts.md](./04-shifts.md) (open your shift)</t>
+RELATED: [04-shifts.md](./04-shifts.md) (open your shift)
+PUBLISHED TITLE: Watch your shift grow - receipts, cash, and net, live.
+SHORT-FORM VARIANT: Watch your shift grow
+PUBLISHED DESCRIPTION: Monitor the active shift on Custosell - stat cards for transactions, cash, mobile money, and card, a running net-sales progress chart, and every receipt of the shift. Try free #custosell #shift #openingbalance #cashdrawer #Custosell #SmallBusiness
+TAGS: custosell, shift, opening balance, cash drawer, close shift, attendance, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Cash / Mobile / Card, live" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D114" s="5" t="n"/>
@@ -6155,7 +7288,17 @@
   - "Shift by shift, net sales"
 DEMO DATA: At least 3-4 completed shifts with varying sales.
 CTA: Try free
-RELATED: [02-dashboard-reports.md](./02-dashboard-reports.md)</t>
+RELATED: [02-dashboard-reports.md](./02-dashboard-reports.md)
+PUBLISHED TITLE: Your past shifts, compared - where were you strongest?
+SHORT-FORM VARIANT: Your past shifts, compared
+PUBLISHED DESCRIPTION: Look back at your completed shifts on Custosell - a trend chart of net sales per shift and a history table - to spot your best days and busiest periods. Try free #custosell #shift #openingbalance #cashdrawer #Custosell #SmallBusiness
+TAGS: custosell, shift, opening balance, cash drawer, close shift, attendance, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Shift by shift, net sales" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D115" s="5" t="n"/>
@@ -6202,7 +7345,17 @@
   - "Every sale has an owner"
 DEMO DATA: Two staff users on a business.
 CTA: Try free
-RELATED: [03-sales-pos.md](./03-sales-pos.md)</t>
+RELATED: [03-sales-pos.md](./03-sales-pos.md)
+PUBLISHED TITLE: Handing over the till? Keep it accountable.
+SHORT-FORM VARIANT: Handing over the till? Keep it accountable.
+PUBLISHED DESCRIPTION: Switch staff mid-day on Custosell - one staff ends their shift with a drawer count, the next opens theirs, and every sale stays traceable to the right person. Try free #custosell #shift #openingbalance #cashdrawer #Custosell #SmallBusiness
+TAGS: custosell, shift, opening balance, cash drawer, close shift, attendance, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Every sale has an owner" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D116" s="5" t="n"/>
@@ -6272,7 +7425,17 @@
 / counted cash / clock out + close) · `/shifts/active` (current shift) ·
 `/shifts/{id}/payments` (shift payments) · `/sales/by-shift/{id}` (shift
 sales) · `/expenses?shift_id={id}` (shift expenses) · `/sales/daily` (day
-rollup per shift)</t>
+rollup per shift)
+PUBLISHED TITLE: Clock in, sell, and close - even with no internet.
+SHORT-FORM VARIANT: Clock in, sell, and close
+PUBLISHED DESCRIPTION: Open, run, and close a shift with no internet on Custosell. Shift changes save locally and sync when you reconnect - the drawer stays accountable the whole time. Try free #custosell #shift #openingbalance #cashdrawer #Custosell #SmallBusiness
+TAGS: custosell, shift, opening balance, cash drawer, close shift, attendance, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Shift runs offline" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D117" s="5" t="n"/>
@@ -6328,7 +7491,17 @@
 DevTools Network tab.
 CTA: Try free + subscribe
 RELATED: [03-sales-pos.md](./03-sales-pos.md) (first sale),
-[04-shifts.md](./04-shifts.md)</t>
+[04-shifts.md](./04-shifts.md)
+PUBLISHED TITLE: Internet down? You're still selling.
+SHORT-FORM VARIANT: Internet down? You're still selling.
+PUBLISHED DESCRIPTION: Custosell POS works offline. Ring up sales and take payments even when Wi-Fi or mobile data drops. The amber offline banner reassures you that your work is saved on the device, then everything syncs automatically when you're back online. Try free + subscribe #custosell #offline #sync #nointernet #Custosell #SmallBusiness
+TAGS: custosell, offline, sync, no internet, offline first, pos offline, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Offline. Still selling." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D118" s="5" t="n"/>
@@ -6385,7 +7558,18 @@
 category set up.
 CTA: Try free + subscribe
 RELATED: [21-offline-sync.md](./21-offline-sync.md) (short version),
-[05-inventory-products.md](./05-inventory-products.md)</t>
+[05-inventory-products.md](./05-inventory-products.md)
+PUBLISHED TITLE: Everything you can do offline - and what happens when you reconnect.
+SHORT-FORM VARIANT: Everything you can do offline - and what happens when
+PUBLISHED DESCRIPTION: A deep look at Custosell's offline engine. Which actions work without internet, how the ordered sync pipeline handles dependencies, and what happens when you reconnect. Perfect for owners deciding to switch. Try free + subscribe #custosell #offline #sync #nointernet #Custosell #SmallBusiness
+TAGS: custosell, offline, sync, no internet, offline first, pos offline, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Queued while offline" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover
+  - Intro / outro: 2s animated logo intro + end screen with subscribe</t>
         </is>
       </c>
       <c r="D119" s="5" t="n"/>
@@ -6439,7 +7623,17 @@
   - "N items failed to sync"
 DEMO DATA: A business with offline-created sales ready to sync.
 CTA: Try free
-RELATED: [21-offline-sync.md](./21-offline-sync.md)</t>
+RELATED: [21-offline-sync.md](./21-offline-sync.md)
+PUBLISHED TITLE: Wondering if your data made it? Watch the sync banner.
+SHORT-FORM VARIANT: Wondering if your data made it? Watch the sync banner.
+PUBLISHED DESCRIPTION: Custosell shows you sync progress in real time - a percentage chip in the top bar and a banner with a progress bar, phase label, and estimate. If anything fails, the banner tells you exactly how many items failed and links you to review them. Try free #custosell #offline #sync #nointernet #Custosell #SmallBusiness
+TAGS: custosell, offline, sync, no internet, offline first, pos offline, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Syncing 23 of 25 - 92%" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D120" s="5" t="n"/>
@@ -6520,7 +7714,17 @@
 sale_items, stock_movements, staff_transfers, quick_notes) · `GET /sync/pull?since=`
 · `GET /sync/full` · `sales.php` (auth:sanctum + business.active +
 subscription.active): `POST /sales/batch` (bulk sales sync) · `POST /sales` per
-sale fallback</t>
+sale fallback
+PUBLISHED TITLE: Set up Custosell offline. Sign in online later.
+SHORT-FORM VARIANT: Set up Custosell offline. Sign
+PUBLISHED DESCRIPTION: You can create your Custosell account without internet - the registration is saved on the device and synced to the server when you connect. An amber banner shows your account is pending sync, and offline sign-in keeps working after that. Try free + subscribe #custosell #offline #sync #nointernet #Custosell #SmallBusiness
+TAGS: custosell, offline, sync, no internet, offline first, pos offline, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Register offline. Sync when online." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D121" s="5" t="n"/>
@@ -6568,7 +7772,17 @@
   - "10-second expense"
 DEMO DATA: Expense categories set up.
 CTA: Try free
-RELATED: [02-dashboard-reports.md](./02-dashboard-reports.md)</t>
+RELATED: [02-dashboard-reports.md](./02-dashboard-reports.md)
+PUBLISHED TITLE: Log an expense before you forget it.
+SHORT-FORM VARIANT: Log an expense before you forget it.
+PUBLISHED DESCRIPTION: Record a business or personal expense on Custosell in seconds - amount, category, branch, description, and date. Your profit numbers stay honest. Try free #custosell #expenses #budgets #income #Custosell #SmallBusiness
+TAGS: custosell, expenses, budgets, income, receipts, categories, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "10-second expense" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D122" s="5" t="n"/>
@@ -6615,7 +7829,17 @@
   - "Filter. Find. Fix."
 DEMO DATA: A few expenses across categories, branches, and months.
 CTA: Try free
-RELATED: [08-expenses-budgets-income.md](./08-expenses-budgets-income.md)</t>
+RELATED: [08-expenses-budgets-income.md](./08-expenses-budgets-income.md)
+PUBLISHED TITLE: Find any expense by category, branch, or date.
+SHORT-FORM VARIANT: Find any expense by category
+PUBLISHED DESCRIPTION: Filter your expense list by category, branch, and date range, edit or delete entries, and spot recurring bills and pending-sync items at a glance. Try free #custosell #expenses #budgets #income #Custosell #SmallBusiness
+TAGS: custosell, expenses, budgets, income, receipts, categories, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Filter. Find. Fix." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D123" s="5" t="n"/>
@@ -6663,7 +7887,17 @@
   - "Categorize. Budget. Understand."
 DEMO DATA: Uncategorized expenses.
 CTA: Try free
-RELATED: [08-expenses-budgets-income.md](./08-expenses-budgets-income.md)</t>
+RELATED: [08-expenses-budgets-income.md](./08-expenses-budgets-income.md)
+PUBLISHED TITLE: Neat categories - and a budget per category.
+SHORT-FORM VARIANT: Neat categories
+PUBLISHED DESCRIPTION: Add, rename, and delete expense categories, and set a budget amount with a weekly, monthly, quarterly, or yearly period so reporting tells a clear story. Try free #custosell #expenses #budgets #income #Custosell #SmallBusiness
+TAGS: custosell, expenses, budgets, income, receipts, categories, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Categorize. Budget. Understand." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D124" s="5" t="n"/>
@@ -6710,7 +7944,17 @@
   - "Receipt attached"
 DEMO DATA: A supplier invoice or receipt image.
 CTA: Try free
-RELATED: [10-documents.md](./10-documents.md)</t>
+RELATED: [10-documents.md](./10-documents.md)
+PUBLISHED TITLE: Receipts stay attached - no more lost paper.
+SHORT-FORM VARIANT: Receipts stay attached
+PUBLISHED DESCRIPTION: Attach a photo of the receipt or a link to it, plus a reference number, on any expense so every shilling is provable at audit time. Try free #custosell #expenses #budgets #income #Custosell #SmallBusiness
+TAGS: custosell, expenses, budgets, income, receipts, categories, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Receipt attached" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D125" s="5" t="n"/>
@@ -6758,7 +8002,17 @@
   - "Budget. List. Track."
 DEMO DATA: A personal account with some expense history.
 CTA: Try free
-RELATED: [13-forecasting.md](./13-forecasting.md)</t>
+RELATED: [13-forecasting.md](./13-forecasting.md)
+PUBLISHED TITLE: A budget that warns you before you overspend.
+SHORT-FORM VARIANT: A budget that warns you before you overspend.
+PUBLISHED DESCRIPTION: Create a named budget on Custosell - like Groceries or June holiday - set the target, and add a shopping list that auto-totals and auto-saves. Try free #custosell #expenses #budgets #income #Custosell #SmallBusiness
+TAGS: custosell, expenses, budgets, income, receipts, categories, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Budget. List. Track." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D126" s="5" t="n"/>
@@ -6806,7 +8060,17 @@
   - "Planned. Spent. Converted."
 DEMO DATA: A budget with plan lines and linked income.
 CTA: Try free
-RELATED: [08-expenses-budgets-income.md](./08-expenses-budgets-income.md)</t>
+RELATED: [08-expenses-budgets-income.md](./08-expenses-budgets-income.md)
+PUBLISHED TITLE: Watch your plan become reality - item by item.
+SHORT-FORM VARIANT: Watch your plan become reality
+PUBLISHED DESCRIPTION: Open a budget to see planned vs spent vs income, pace, and affordability - then convert a shopping-list item straight into an expense when you buy it. Try free #custosell #expenses #budgets #income #Custosell #SmallBusiness
+TAGS: custosell, expenses, budgets, income, receipts, categories, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Planned. Spent. Converted." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D127" s="5" t="n"/>
@@ -6854,7 +8118,17 @@
   - "All income. All tracked."
 DEMO DATA: A personal account with a few income sources.
 CTA: Try free
-RELATED: [08-expenses-budgets-income.md](./08-expenses-budgets-income.md)</t>
+RELATED: [08-expenses-budgets-income.md](./08-expenses-budgets-income.md)
+PUBLISHED TITLE: Not every shilling comes from the till - record it anyway.
+SHORT-FORM VARIANT: Not every shilling comes from the till - record it
+PUBLISHED DESCRIPTION: Log income from any source - salary, freelance, rent - with a date, optional recurring schedule, and attachments. Your real profit picture becomes complete. Try free #custosell #expenses #budgets #income #Custosell #SmallBusiness
+TAGS: custosell, expenses, budgets, income, receipts, categories, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "All income. All tracked." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D128" s="5" t="n"/>
@@ -6902,7 +8176,18 @@
   - "Income. Expenses. Net."
 DEMO DATA: A month of income and expenses across categories.
 CTA: Try free + subscribe
-RELATED: [02-dashboard-reports.md](./02-dashboard-reports.md)</t>
+RELATED: [02-dashboard-reports.md](./02-dashboard-reports.md)
+PUBLISHED TITLE: See where money comes from and where it goes.
+SHORT-FORM VARIANT: See where money comes from and where it goes.
+PUBLISHED DESCRIPTION: The money overview shows total income, expenses, net balance, and transaction counts, with donuts for income by source and expenses by category, daily and monthly trends, and recent transactions. Try free + subscribe #custosell #expenses #budgets #income #Custosell #SmallBusiness
+TAGS: custosell, expenses, budgets, income, receipts, categories, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Income. Expenses. Net." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover
+  - Intro / outro: 2s animated logo intro + end screen with subscribe</t>
         </is>
       </c>
       <c r="D129" s="5" t="n"/>
@@ -6950,7 +8235,17 @@
   - "CSV or Excel - your call"
 DEMO DATA: A filtered set of expenses.
 CTA: Try free
-RELATED: [09-accounting.md](./09-accounting.md)</t>
+RELATED: [09-accounting.md](./09-accounting.md)
+PUBLISHED TITLE: Your expense ledger, ready for your accountant.
+SHORT-FORM VARIANT: Your expense ledger
+PUBLISHED DESCRIPTION: Export your expenses to CSV or Excel with date, category, description, amount, reference, and receipt columns - filtered exactly how you need them. Try free #custosell #expenses #budgets #income #Custosell #SmallBusiness
+TAGS: custosell, expenses, budgets, income, receipts, categories, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "CSV or Excel - your call" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D130" s="5" t="n"/>
@@ -7027,7 +8322,17 @@
 `/income-sources/{id}/attachments` + `/attachments/link` +
 `/income-source-attachments/{id}`) · `/budgets` CRUD (+ `/budgets/{id}/lines`,
 `/lines/{line}/purchase`, `/affordability`, `/download`) · `/money/summary` ·
-`/money/alerts`</t>
+`/money/alerts`
+PUBLISHED TITLE: Record expenses even when the internet is gone.
+SHORT-FORM VARIANT: Record expenses even when the internet is gone.
+PUBLISHED DESCRIPTION: Create and edit expenses offline - Custosell saves them instantly with a Pending sync badge (and pending receipt) and syncs automatically when you're back online. Try free #custosell #expenses #budgets #income #Custosell #SmallBusiness
+TAGS: custosell, expenses, budgets, income, receipts, categories, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Saved offline. Synced when back." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D131" s="5" t="n"/>
@@ -7075,7 +8380,17 @@
   - "Name + phone + email = profile"
 DEMO DATA: An empty (or small) customer list.
 CTA: Try free
-RELATED: [03-sales-pos.md](./03-sales-pos.md)</t>
+RELATED: [03-sales-pos.md](./03-sales-pos.md)
+PUBLISHED TITLE: Add a customer in 10 seconds - name, phone, done.
+SHORT-FORM VARIANT: Add a customer in 10 seconds
+PUBLISHED DESCRIPTION: Create a customer profile on Custosell with their name, phone, and email. Every future sale can attach to them automatically. Try free #custosell #customers #customerlist #purchasehistory #Custosell #SmallBusiness
+TAGS: custosell, customers, customer list, purchase history, loyalty, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Name + phone + email = profile" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D132" s="5" t="n"/>
@@ -7122,7 +8437,17 @@
   - "Search. Edit. Delete."
 DEMO DATA: Several customers with purchase history.
 CTA: Try free
-RELATED: [07-customers.md](./07-customers.md)</t>
+RELATED: [07-customers.md](./07-customers.md)
+PUBLISHED TITLE: Find any customer by name or phone - instantly.
+SHORT-FORM VARIANT: Find any customer by name or phone
+PUBLISHED DESCRIPTION: Search your customer list by name or phone, edit profiles, delete customers you no longer need, and spot purchases at a glance. Try free #custosell #customers #customerlist #purchasehistory #Custosell #SmallBusiness
+TAGS: custosell, customers, customer list, purchase history, loyalty, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Search. Edit. Delete." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D133" s="5" t="n"/>
@@ -7168,7 +8493,17 @@
   - "Every receipt, one tap away"
 DEMO DATA: A customer with multiple sales, some refunded.
 CTA: Try free
-RELATED: [03-sales-pos.md](./03-sales-pos.md)</t>
+RELATED: [03-sales-pos.md](./03-sales-pos.md)
+PUBLISHED TITLE: Every receipt that customer ever had, in one list.
+SHORT-FORM VARIANT: Every receipt that customer ever had
+PUBLISHED DESCRIPTION: Open a customer's purchase history to see each sale's date, receipt number, item count, total, payment method, and payment status. Try free #custosell #customers #customerlist #purchasehistory #Custosell #SmallBusiness
+TAGS: custosell, customers, customer list, purchase history, loyalty, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Every receipt, one tap away" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D134" s="5" t="n"/>
@@ -7216,7 +8551,18 @@
   - "Active. At risk. Lapsed. Never."
 DEMO DATA: A customer base with a mix of recency buckets.
 CTA: Try free + subscribe
-RELATED: [02-dashboard-reports.md](./02-dashboard-reports.md)</t>
+RELATED: [02-dashboard-reports.md](./02-dashboard-reports.md)
+PUBLISHED TITLE: See who buys, who's drifting, and who's gone.
+SHORT-FORM VARIANT: See who buys
+PUBLISHED DESCRIPTION: The customer overview dashboard segments your base into Active, At risk, Lapsed, and Never purchased, and shows repeat rate, revenue, purchase frequency, and top spenders. Try free + subscribe #custosell #customers #customerlist #purchasehistory #Custosell #SmallBusiness
+TAGS: custosell, customers, customer list, purchase history, loyalty, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Active. At risk. Lapsed. Never." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover
+  - Intro / outro: 2s animated logo intro + end screen with subscribe</t>
         </is>
       </c>
       <c r="D135" s="5" t="n"/>
@@ -7263,7 +8609,17 @@
   - "Walk-in or known - both fine"
 DEMO DATA: A sale in progress + a few saved customers.
 CTA: Try free
-RELATED: [03-sales-pos.md](./03-sales-pos.md)</t>
+RELATED: [03-sales-pos.md](./03-sales-pos.md)
+PUBLISHED TITLE: Pick the buyer before you hit Complete - no slowing down.
+SHORT-FORM VARIANT: Pick the buyer before you hit Complete - no slowing
+PUBLISHED DESCRIPTION: At the payment screen, attach a sale to an existing customer or leave it as a walk-in. Search picks from your saved list instantly. Try free #custosell #customers #customerlist #purchasehistory #Custosell #SmallBusiness
+TAGS: custosell, customers, customer list, purchase history, loyalty, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Walk-in or known - both fine" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D136" s="5" t="n"/>
@@ -7310,7 +8666,17 @@
   - "Added on the spot"
 DEMO DATA: A sale in progress with no matching customer.
 CTA: Try free
-RELATED: [03-sales-pos.md](./03-sales-pos.md)</t>
+RELATED: [03-sales-pos.md](./03-sales-pos.md)
+PUBLISHED TITLE: New buyer? Add them without leaving the sale.
+SHORT-FORM VARIANT: New buyer? Add them without leaving the sale.
+PUBLISHED DESCRIPTION: When a walk-in turns into a regular, add their contact right in the checkout picker - or type their number to create them on the spot. Try free #custosell #customers #customerlist #purchasehistory #Custosell #SmallBusiness
+TAGS: custosell, customers, customer list, purchase history, loyalty, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Added on the spot" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D137" s="5" t="n"/>
@@ -7374,7 +8740,17 @@
 `/sales/{id}/customer` (assign)
 **Overview segments (BE `CustomerService`):** Active (&lt;30 days) · At risk
 (30-90 days) · Lapsed (&gt;90 days) · Never purchased. Frequency buckets: 1 · 2-3 ·
-4-6 · 7+ purchases.</t>
+4-6 · 7+ purchases.
+PUBLISHED TITLE: Add customers even when the internet is gone.
+SHORT-FORM VARIANT: Add customers even when the internet is gone.
+PUBLISHED DESCRIPTION: Create and edit customers while offline - Custosell saves them instantly with a Pending sync badge and syncs automatically when you're back. Try free #custosell #customers #customerlist #purchasehistory #Custosell #SmallBusiness
+TAGS: custosell, customers, customer list, purchase history, loyalty, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Saved offline. Synced when back." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D138" s="5" t="n"/>
@@ -7422,7 +8798,17 @@
   - "Browse. Add. Order."
 DEMO DATA: A marketplace with suppliers and listed products.
 CTA: Try free + subscribe
-RELATED: [05-inventory-products.md](./05-inventory-products.md)</t>
+RELATED: [05-inventory-products.md](./05-inventory-products.md)
+PUBLISHED TITLE: Restock in minutes from the marketplace.
+SHORT-FORM VARIANT: Restock
+PUBLISHED DESCRIPTION: Browse the Custosell marketplace, find suppliers, and build a purchase order in a few taps. Buying smarter starts here. Try free + subscribe #custosell #marketplace #purchaseorder #suppliers #Custosell #SmallBusiness
+TAGS: custosell, marketplace, purchase order, suppliers, restock, supply, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Browse. Add. Order." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D139" s="5" t="n"/>
@@ -7470,7 +8856,17 @@
   - "Save. Find. Order again."
 DEMO DATA: A supplier card in the marketplace.
 CTA: Try free
-RELATED: [06-marketplace-purchase-orders.md](./06-marketplace-purchase-orders.md)</t>
+RELATED: [06-marketplace-purchase-orders.md](./06-marketplace-purchase-orders.md)
+PUBLISHED TITLE: Keep your regular suppliers one tap away.
+SHORT-FORM VARIANT: Keep your regular suppliers one tap away.
+PUBLISHED DESCRIPTION: Bookmark suppliers you reorder from so the next restock starts faster - and remove them when you stop buying. Try free #custosell #marketplace #purchaseorder #suppliers #Custosell #SmallBusiness
+TAGS: custosell, marketplace, purchase order, suppliers, restock, supply, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Save. Find. Order again." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D140" s="5" t="n"/>
@@ -7518,7 +8914,17 @@
   - "Price. Min order. Stock."
 DEMO DATA: A supplier with a large listed catalog.
 CTA: Try free
-RELATED: [06-marketplace-purchase-orders.md](./06-marketplace-purchase-orders.md)</t>
+RELATED: [06-marketplace-purchase-orders.md](./06-marketplace-purchase-orders.md)
+PUBLISHED TITLE: See exactly what a supplier stocks.
+SHORT-FORM VARIANT: See exactly what a supplier stocks.
+PUBLISHED DESCRIPTION: Open any supplier's catalog, search and filter their products, and check supply price, unit, and minimum order quantity. Try free #custosell #marketplace #purchaseorder #suppliers #Custosell #SmallBusiness
+TAGS: custosell, marketplace, purchase order, suppliers, restock, supply, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Price. Min order. Stock." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D141" s="5" t="n"/>
@@ -7566,7 +8972,17 @@
   - "Lines. Qty. Total."
 DEMO DATA: A supplier catalog with several products.
 CTA: Try free
-RELATED: [06-marketplace-purchase-orders.md](./06-marketplace-purchase-orders.md)</t>
+RELATED: [06-marketplace-purchase-orders.md](./06-marketplace-purchase-orders.md)
+PUBLISHED TITLE: Shop a supplier like a pro.
+SHORT-FORM VARIANT: Shop a supplier like a pro.
+PUBLISHED DESCRIPTION: Add products to your purchase order cart, adjust quantities, leave notes for the seller, and watch the order total update live. Try free #custosell #marketplace #purchaseorder #suppliers #Custosell #SmallBusiness
+TAGS: custosell, marketplace, purchase order, suppliers, restock, supply, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Lines. Qty. Total." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D142" s="5" t="n"/>
@@ -7614,7 +9030,17 @@
   - "Ordered. Tracked. Received."
 DEMO DATA: A cart with a few supplier products.
 CTA: Try free
-RELATED: [05-inventory-products.md](./05-inventory-products.md)</t>
+RELATED: [05-inventory-products.md](./05-inventory-products.md)
+PUBLISHED TITLE: Order stock without losing track.
+SHORT-FORM VARIANT: Order stock without losing track.
+PUBLISHED DESCRIPTION: Save your marketplace cart as a draft purchase order or submit it straight to the supplier - then track it until it arrives. Try free #custosell #marketplace #purchaseorder #suppliers #Custosell #SmallBusiness
+TAGS: custosell, marketplace, purchase order, suppliers, restock, supply, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Ordered. Tracked. Received." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D143" s="5" t="n"/>
@@ -7661,7 +9087,17 @@
   - "Draft. Edit. Submit right."
 DEMO DATA: A draft purchase order.
 CTA: Try free
-RELATED: [06-marketplace-purchase-orders.md](./06-marketplace-purchase-orders.md)</t>
+RELATED: [06-marketplace-purchase-orders.md](./06-marketplace-purchase-orders.md)
+PUBLISHED TITLE: Change your mind before the seller sees it.
+SHORT-FORM VARIANT: Change your mind before the seller sees it.
+PUBLISHED DESCRIPTION: A draft order is yours until you submit it - adjust quantities, rewrite notes, and fix the total before it goes out. Try free #custosell #marketplace #purchaseorder #suppliers #Custosell #SmallBusiness
+TAGS: custosell, marketplace, purchase order, suppliers, restock, supply, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Draft. Edit. Submit right." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D144" s="5" t="n"/>
@@ -7709,7 +9145,17 @@
   - "Submitted. Waiting on the seller."
 DEMO DATA: A draft purchase order.
 CTA: Try free
-RELATED: [06-marketplace-purchase-orders.md](./06-marketplace-purchase-orders.md)</t>
+RELATED: [06-marketplace-purchase-orders.md](./06-marketplace-purchase-orders.md)
+PUBLISHED TITLE: Send the order. Stop chasing.
+SHORT-FORM VARIANT: Send the order. Stop chasing.
+PUBLISHED DESCRIPTION: Submit a purchase order to your supplier and move it into the 'submitted' stage, where the seller reviews and responds. Try free #custosell #marketplace #purchaseorder #suppliers #Custosell #SmallBusiness
+TAGS: custosell, marketplace, purchase order, suppliers, restock, supply, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Submitted. Waiting on the seller." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D145" s="5" t="n"/>
@@ -7756,7 +9202,17 @@
   - "Cancel. Confirm. Clean."
 DEMO DATA: A submitted order to cancel.
 CTA: Try free
-RELATED: [06-marketplace-purchase-orders.md](./06-marketplace-purchase-orders.md)</t>
+RELATED: [06-marketplace-purchase-orders.md](./06-marketplace-purchase-orders.md)
+PUBLISHED TITLE: Change of plans? Cancel cleanly.
+SHORT-FORM VARIANT: Change of plans? Cancel cleanly.
+PUBLISHED DESCRIPTION: Cancel a submitted order you no longer need - the seller sees the cancellation and the order is closed out. Try free #custosell #marketplace #purchaseorder #suppliers #Custosell #SmallBusiness
+TAGS: custosell, marketplace, purchase order, suppliers, restock, supply, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Cancel. Confirm. Clean." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D146" s="5" t="n"/>
@@ -7803,7 +9259,17 @@
   - "Status. Search. Tracked."
 DEMO DATA: Several purchase orders in different states.
 CTA: Try free
-RELATED: [06-marketplace-purchase-orders.md](./06-marketplace-purchase-orders.md)</t>
+RELATED: [06-marketplace-purchase-orders.md](./06-marketplace-purchase-orders.md)
+PUBLISHED TITLE: Every order, one status away.
+SHORT-FORM VARIANT: Every order
+PUBLISHED DESCRIPTION: See all your purchase orders in one list with status tabs, search by PO number or seller, and an open-orders count from the marketplace. Try free #custosell #marketplace #purchaseorder #suppliers #Custosell #SmallBusiness
+TAGS: custosell, marketplace, purchase order, suppliers, restock, supply, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Status. Search. Tracked." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D147" s="5" t="n"/>
@@ -7851,7 +9317,18 @@
   - "Draft. Submitted. Accepted. Fulfilled. Received."
 DEMO DATA: A PO that has moved through several stages.
 CTA: Try free + subscribe
-RELATED: [05-inventory-products.md](./05-inventory-products.md)</t>
+RELATED: [05-inventory-products.md](./05-inventory-products.md)
+PUBLISHED TITLE: From draft to received, step by step.
+SHORT-FORM VARIANT: From draft to received
+PUBLISHED DESCRIPTION: Follow one purchase order through its full lifecycle - created, submitted, accepted, fulfilled, received - and see what each side can do. Try free + subscribe #custosell #marketplace #purchaseorder #suppliers #Custosell #SmallBusiness
+TAGS: custosell, marketplace, purchase order, suppliers, restock, supply, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Draft. Submitted. Accepted. Fulfilled. Received." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover
+  - Intro / outro: 2s animated logo intro + end screen with subscribe</t>
         </is>
       </c>
       <c r="D148" s="5" t="n"/>
@@ -7899,7 +9376,17 @@
   - "Accept. Invoice. Ready."
 DEMO DATA: A submitted order from a buyer business.
 CTA: Try free
-RELATED: [09-accounting.md](./09-accounting.md)</t>
+RELATED: [09-accounting.md](./09-accounting.md)
+PUBLISHED TITLE: Accept an order and an invoice is born.
+SHORT-FORM VARIANT: Accept an order and an invoice is born.
+PUBLISHED DESCRIPTION: Review a buyer's submitted purchase order on the incoming orders page and accept it - Custosell creates the buyer invoice automatically. Try free #custosell #marketplace #purchaseorder #suppliers #Custosell #SmallBusiness
+TAGS: custosell, marketplace, purchase order, suppliers, restock, supply, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Accept. Invoice. Ready." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D149" s="5" t="n"/>
@@ -7946,7 +9433,17 @@
   - "Reject. Explain. Move on."
 DEMO DATA: An order you cannot fulfill.
 CTA: Try free
-RELATED: [06-marketplace-purchase-orders.md](./06-marketplace-purchase-orders.md)</t>
+RELATED: [06-marketplace-purchase-orders.md](./06-marketplace-purchase-orders.md)
+PUBLISHED TITLE: Say no with a reason the buyer can read.
+SHORT-FORM VARIANT: Say no with a reason the buyer can read.
+PUBLISHED DESCRIPTION: Reject a purchase order you can't fulfill and give the buyer a clear reason so they know what happened and can reorder. Try free #custosell #marketplace #purchaseorder #suppliers #Custosell #SmallBusiness
+TAGS: custosell, marketplace, purchase order, suppliers, restock, supply, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Reject. Explain. Move on." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D150" s="5" t="n"/>
@@ -7994,7 +9491,17 @@
   - "Fulfilled. Stock out."
 DEMO DATA: An accepted order with sufficient stock.
 CTA: Try free
-RELATED: [05-inventory-products.md](./05-inventory-products.md)</t>
+RELATED: [05-inventory-products.md](./05-inventory-products.md)
+PUBLISHED TITLE: Ship it. Stock already knows.
+SHORT-FORM VARIANT: Ship it. Stock already knows.
+PUBLISHED DESCRIPTION: When the goods leave your shelf, mark the order fulfilled - Custosell deducts the items from your stock. Try free #custosell #marketplace #purchaseorder #suppliers #Custosell #SmallBusiness
+TAGS: custosell, marketplace, purchase order, suppliers, restock, supply, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Fulfilled. Stock out." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D151" s="5" t="n"/>
@@ -8042,7 +9549,17 @@
   - "Received. Stocked. Costed."
 DEMO DATA: A fulfilled P.O. awaiting delivery.
 CTA: Try free
-RELATED: [09-accounting.md](./09-accounting.md)</t>
+RELATED: [09-accounting.md](./09-accounting.md)
+PUBLISHED TITLE: Stock arrived? Receive it and it's yours.
+SHORT-FORM VARIANT: Stock arrived? Receive it and it's yours.
+PUBLISHED DESCRIPTION: Confirm receipt of a fulfilled order - map each line to a product you already stock or create a new product, and stock increases. Try free #custosell #marketplace #purchaseorder #suppliers #Custosell #SmallBusiness
+TAGS: custosell, marketplace, purchase order, suppliers, restock, supply, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Received. Stocked. Costed." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D152" s="5" t="n"/>
@@ -8090,7 +9607,17 @@
   - "Order. Invoice. Receipts."
 DEMO DATA: An accepted order with an invoice and a payment.
 CTA: Try free
-RELATED: [09-accounting.md](./09-accounting.md)</t>
+RELATED: [09-accounting.md](./09-accounting.md)
+PUBLISHED TITLE: The invoice is one click from the order.
+SHORT-FORM VARIANT: The invoice is one click from the order.
+PUBLISHED DESCRIPTION: Open the linked supplier invoice for any accepted order and view its payment receipts - no hunting through other menus. Try free #custosell #marketplace #purchaseorder #suppliers #Custosell #SmallBusiness
+TAGS: custosell, marketplace, purchase order, suppliers, restock, supply, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Order. Invoice. Receipts." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D153" s="5" t="n"/>
@@ -8137,7 +9664,17 @@
   - "Buyers. Orders. Payments."
 DEMO DATA: Multiple incoming orders from different buyers.
 CTA: Try free
-RELATED: [06-marketplace-purchase-orders.md](./06-marketplace-purchase-orders.md)</t>
+RELATED: [06-marketplace-purchase-orders.md](./06-marketplace-purchase-orders.md)
+PUBLISHED TITLE: Your wholesale pipeline, in one list.
+SHORT-FORM VARIANT: Your wholesale pipeline
+PUBLISHED DESCRIPTION: See every order buyers placed with you - filter by status, spot buyers, and check invoice and payment progress at a glance. Try free #custosell #marketplace #purchaseorder #suppliers #Custosell #SmallBusiness
+TAGS: custosell, marketplace, purchase order, suppliers, restock, supply, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Buyers. Orders. Payments." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D154" s="5" t="n"/>
@@ -8185,7 +9722,17 @@
   - "List it. Price it. Sell wholesale."
 DEMO DATA: An active physical product and a business open for supply.
 CTA: Try free
-RELATED: [05-inventory-products.md](./05-inventory-products.md)</t>
+RELATED: [05-inventory-products.md](./05-inventory-products.md)
+PUBLISHED TITLE: Turn your stock into other shops' restock.
+SHORT-FORM VARIANT: Turn your stock into other shops' restock.
+PUBLISHED DESCRIPTION: List a product on the B2B supply marketplace with a supply price and minimum order quantity so other businesses can order from you. Try free #custosell #marketplace #purchaseorder #suppliers #Custosell #SmallBusiness
+TAGS: custosell, marketplace, purchase order, suppliers, restock, supply, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "List it. Price it. Sell wholesale." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D155" s="5" t="n"/>
@@ -8233,7 +9780,17 @@
   - "Image. List. Sell."
 DEMO DATA: A product with an image and a shop-enabled business.
 CTA: Try free
-RELATED: [14-storefront.md](./14-storefront.md)</t>
+RELATED: [14-storefront.md](./14-storefront.md)
+PUBLISHED TITLE: Put your catalog in front of customers.
+SHORT-FORM VARIANT: Put your catalog
+PUBLISHED DESCRIPTION: List a product on your public shop for guests to browse and buy, with an image to make the listing shine. Try free #custosell #marketplace #purchaseorder #suppliers #Custosell #SmallBusiness
+TAGS: custosell, marketplace, purchase order, suppliers, restock, supply, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Image. List. Sell." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D156" s="5" t="n"/>
@@ -8301,7 +9858,17 @@
 `/purchase-orders` (GET/POST) + `/purchase-orders/{id}`
 (GET/PUT/DELETE) + `/purchase-orders/{id}/submit|cancel|accept|reject|
 fulfill|receive` · `/purchase-orders/incoming` ·
-`/products/{id}/supply-listing` · `/products/{id}/storefront-listing`</t>
+`/products/{id}/supply-listing` · `/products/{id}/storefront-listing`
+PUBLISHED TITLE: Know exactly what needs a connection.
+SHORT-FORM VARIANT: Know exactly what needs a connection.
+PUBLISHED DESCRIPTION: Marketplace browsing, ordering, and order management need the internet - see how Custosell tells you clearly and keeps your local work safe. Try free #custosell #marketplace #purchaseorder #suppliers #Custosell #SmallBusiness
+TAGS: custosell, marketplace, purchase order, suppliers, restock, supply, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Offline. Connect to order." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D157" s="5" t="n"/>
@@ -8351,7 +9918,17 @@
   - "Cost in. Price out. Margin seen."
 DEMO DATA: A customer and a few priced products/services.
 CTA: Try free + subscribe
-RELATED: [11-pipeline-crm.md](./11-pipeline-crm.md)</t>
+RELATED: [11-pipeline-crm.md](./11-pipeline-crm.md)
+PUBLISHED TITLE: Quote with a margin you can see.
+SHORT-FORM VARIANT: Quote with a margin you can see.
+PUBLISHED DESCRIPTION: Build a professional estimate on Custosell - title, customer, valid-until date, tax rate, and line items with cost, markup, and a live gross-profit margin summary. Starts as a draft. Try free + subscribe #custosell #estimates #projects #templates #Custosell #SmallBusiness
+TAGS: custosell, estimates, projects, templates, quotes, invoicing, project management, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Cost in. Price out. Margin seen." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D158" s="5" t="n"/>
@@ -8399,7 +9976,17 @@
   - "Sent. Emailed. PDF ready."
 DEMO DATA: A draft estimate.
 CTA: Try free + subscribe
-RELATED: [12-estimates-projects.md](./12-estimates-projects.md)</t>
+RELATED: [12-estimates-projects.md](./12-estimates-projects.md)
+PUBLISHED TITLE: Mark it sent - or really email it.
+SHORT-FORM VARIANT: Mark it sent
+PUBLISHED DESCRIPTION: Mark an estimate as sent to track the deal, or email the actual proposal to the customer, and always have a professional PDF ready to preview or download. Try free + subscribe #custosell #estimates #projects #templates #Custosell #SmallBusiness
+TAGS: custosell, estimates, projects, templates, quotes, invoicing, project management, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Sent. Emailed. PDF ready." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D159" s="5" t="n"/>
@@ -8448,7 +10035,17 @@
   - "Approved. And converted."
 DEMO DATA: A sent estimate.
 CTA: Try free
-RELATED: [12-estimates-projects.md](./12-estimates-projects.md)</t>
+RELATED: [12-estimates-projects.md](./12-estimates-projects.md)
+PUBLISHED TITLE: The customer said yes? Make it official.
+SHORT-FORM VARIANT: The customer said yes? Make it official.
+PUBLISHED DESCRIPTION: Approve an estimate to record the accepted deal - optionally creating the invoice and project in the same step - or decline it with a reason for the record. Try free #custosell #estimates #projects #templates #Custosell #SmallBusiness
+TAGS: custosell, estimates, projects, templates, quotes, invoicing, project management, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Approved. And converted." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D160" s="5" t="n"/>
@@ -8495,7 +10092,17 @@
   - "Estimate -&gt; Invoice / Project"
 DEMO DATA: An approved estimate.
 CTA: Try free
-RELATED: [03-sales-pos.md](./03-sales-pos.md)</t>
+RELATED: [03-sales-pos.md](./03-sales-pos.md)
+PUBLISHED TITLE: Accepted estimate -&gt; invoice or project, no re-typing.
+SHORT-FORM VARIANT: Accepted estimate -&gt; invoice or project
+PUBLISHED DESCRIPTION: Convert an approved estimate into a draft invoice from its billable items, or into a project seeded with the same budget and margin. Try free #custosell #estimates #projects #templates #Custosell #SmallBusiness
+TAGS: custosell, estimates, projects, templates, quotes, invoicing, project management, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Estimate -&gt; Invoice / Project" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D161" s="5" t="n"/>
@@ -8543,7 +10150,17 @@
   - "Template. Apply. Done."
 DEMO DATA: A recurring service or package.
 CTA: Try free
-RELATED: [12-estimates-projects.md](./12-estimates-projects.md)</t>
+RELATED: [12-estimates-projects.md](./12-estimates-projects.md)
+PUBLISHED TITLE: Quote the same package often? Make a template.
+SHORT-FORM VARIANT: Quote the same package often? Make a template.
+PUBLISHED DESCRIPTION: Save default line items, tax rate, and terms as a reusable estimate template - pick the customer and you're most of the way done. Try free #custosell #estimates #projects #templates #Custosell #SmallBusiness
+TAGS: custosell, estimates, projects, templates, quotes, invoicing, project management, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Template. Apply. Done." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D162" s="5" t="n"/>
@@ -8591,7 +10208,17 @@
   - "Won. Lost. Margin."
 DEMO DATA: Estimates across several months.
 CTA: Try free
-RELATED: [02-dashboard-reports.md](./02-dashboard-reports.md)</t>
+RELATED: [02-dashboard-reports.md](./02-dashboard-reports.md)
+PUBLISHED TITLE: Win rate, margins, and pipeline value - in one place.
+SHORT-FORM VARIANT: Win rate, margins, and pipeline value
+PUBLISHED DESCRIPTION: See how your estimates are performing - win rate, average margin, pipeline value, approved value, and gross profit - with a monthly trend and a breakdown by status. Try free #custosell #estimates #projects #templates #Custosell #SmallBusiness
+TAGS: custosell, estimates, projects, templates, quotes, invoicing, project management, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Won. Lost. Margin." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D163" s="5" t="n"/>
@@ -8639,7 +10266,17 @@
   - "Lead -&gt; Estimate"
 DEMO DATA: A pipeline lead with a customer and value.
 CTA: Try free
-RELATED: [11-pipeline-crm.md](./11-pipeline-crm.md)</t>
+RELATED: [11-pipeline-crm.md](./11-pipeline-crm.md)
+PUBLISHED TITLE: From hot lead to priced proposal in one click.
+SHORT-FORM VARIANT: From hot lead to priced proposal
+PUBLISHED DESCRIPTION: Turn a pipeline lead straight into an estimate - the lead's title, customer, notes, and estimated value come across, and the two stay linked. Try free #custosell #estimates #projects #templates #Custosell #SmallBusiness
+TAGS: custosell, estimates, projects, templates, quotes, invoicing, project management, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Lead -&gt; Estimate" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D164" s="5" t="n"/>
@@ -8688,7 +10325,17 @@
   - "Budget vs actual, live"
 DEMO DATA: A project converted from an approved estimate.
 CTA: Try free + subscribe
-RELATED: [09-accounting.md](./09-accounting.md)</t>
+RELATED: [09-accounting.md](./09-accounting.md)
+PUBLISHED TITLE: Know if the job is on budget - before it's too late.
+SHORT-FORM VARIANT: Know if the job is on budget
+PUBLISHED DESCRIPTION: Open a project to see budget revenue and cost against what's actually spent, with margin alerts that flag cost overruns and negative margins early. Try free + subscribe #custosell #estimates #projects #templates #Custosell #SmallBusiness
+TAGS: custosell, estimates, projects, templates, quotes, invoicing, project management, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Budget vs actual, live" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D165" s="5" t="n"/>
@@ -8736,7 +10383,17 @@
   - "Task. Hour. Cost. Recorded."
 DEMO DATA: A project with a team and budget.
 CTA: Try free
-RELATED: [15-hr.md](./15-hr.md)</t>
+RELATED: [15-hr.md](./15-hr.md)
+PUBLISHED TITLE: Every hour and every cost lands on the job.
+SHORT-FORM VARIANT: Every hour and every cost lands on the job.
+PUBLISHED DESCRIPTION: Break a project into tasks with estimated and actual hours, log staff timesheets against it, and record cost allocations by type - labor, material, overhead - so job costs stay true. Try free #custosell #estimates #projects #templates #Custosell #SmallBusiness
+TAGS: custosell, estimates, projects, templates, quotes, invoicing, project management, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Task. Hour. Cost. Recorded." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D166" s="5" t="n"/>
@@ -8785,7 +10442,17 @@
   - "Board = project progress"
 DEMO DATA: A project with a board.
 CTA: Try free
-RELATED: [11-pipeline-crm.md](./11-pipeline-crm.md)</t>
+RELATED: [11-pipeline-crm.md](./11-pipeline-crm.md)
+PUBLISHED TITLE: Your project as a kanban board - progress visible.
+SHORT-FORM VARIANT: Your project as a kanban board
+PUBLISHED DESCRIPTION: Open a project's board to see and move its work through stages - the same kanban engine as the pipeline - with cards that reflect task progress. Try free #custosell #estimates #projects #templates #Custosell #SmallBusiness
+TAGS: custosell, estimates, projects, templates, quotes, invoicing, project management, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Board = project progress" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D167" s="5" t="n"/>
@@ -8837,7 +10504,17 @@
   - "Private task board, one click"
 DEMO DATA: A business with the estimates workspace.
 CTA: Try free
-RELATED: [11-pipeline-crm.md](./11-pipeline-crm.md)</t>
+RELATED: [11-pipeline-crm.md](./11-pipeline-crm.md)
+PUBLISHED TITLE: Your own sprint board - private by default.
+SHORT-FORM VARIANT: Your own sprint board
+PUBLISHED DESCRIPTION: Make a personal kanban board in the Projects &amp; Estimates workspace for your own tasks - private to you unless you share it - with cards instead of leads. Name it, pick visibility and background, then open tasks and drag them through columns. Try free #custosell #estimates #projects #templates #Custosell #SmallBusiness
+TAGS: custosell, estimates, projects, templates, quotes, invoicing, project management, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Private task board, one click" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D168" s="5" t="n"/>
@@ -8888,7 +10565,17 @@
   - "Estimate -&gt; Project -&gt; Board"
 DEMO DATA: An approved estimate.
 CTA: Try free
-RELATED: [12-estimates-projects.md](./12-estimates-projects.md)</t>
+RELATED: [12-estimates-projects.md](./12-estimates-projects.md)
+PUBLISHED TITLE: Approve the estimate - the board appears.
+SHORT-FORM VARIANT: Approve the estimate
+PUBLISHED DESCRIPTION: Converting an approved estimate into a project also creates its kanban board automatically - named after the project, with To Do, In Progress, Review, and Done columns. The board carries the same budget as the estimate. Try free #custosell #estimates #projects #templates #Custosell #SmallBusiness
+TAGS: custosell, estimates, projects, templates, quotes, invoicing, project management, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Estimate -&gt; Project -&gt; Board" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D169" s="5" t="n"/>
@@ -8937,7 +10624,17 @@
   - "Stages. Cards. Open."
 DEMO DATA: A project with a board and a few cards.
 CTA: Try free
-RELATED: [12-estimates-projects.md](./12-estimates-projects.md)</t>
+RELATED: [12-estimates-projects.md](./12-estimates-projects.md)
+PUBLISHED TITLE: The project's board, one tab away.
+SHORT-FORM VARIANT: The project's board
+PUBLISHED DESCRIPTION: Inside a project you get a Board tab showing the project board's name, stage count, and total cards - open it to jump straight to the full kanban workspace. Try free #custosell #estimates #projects #templates #Custosell #SmallBusiness
+TAGS: custosell, estimates, projects, templates, quotes, invoicing, project management, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Stages. Cards. Open." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D170" s="5" t="n"/>
@@ -8989,7 +10686,17 @@
 DEMO DATA: A project, a board, and a staff account without full
 Estimates access.
 CTA: Try free
-RELATED: [17-settings.md](./17-settings.md)</t>
+RELATED: [17-settings.md](./17-settings.md)
+PUBLISHED TITLE: They see the board - not the costing.
+SHORT-FORM VARIANT: They see the board
+PUBLISHED DESCRIPTION: Staff and clients invited to a project board get a board-only workspace: they land straight on the board, can view and work cards, but never see costs, timesheets, or allocations. Owners keep full project control. Try free #custosell #estimates #projects #templates #Custosell #SmallBusiness
+TAGS: custosell, estimates, projects, templates, quotes, invoicing, project management, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Board view, no costing" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D171" s="5" t="n"/>
@@ -9038,7 +10745,17 @@
   - "Task in. Column filled."
 DEMO DATA: A project board with columns.
 CTA: Try free
-RELATED: [11-pipeline-crm.md](./11-pipeline-crm.md)</t>
+RELATED: [11-pipeline-crm.md](./11-pipeline-crm.md)
+PUBLISHED TITLE: A job broken into cards is a job getting done.
+SHORT-FORM VARIANT: A job broken into cards is a job getting done.
+PUBLISHED DESCRIPTION: Add a task card to any column on a project or personal board - give it a title and assign team members - then it sits in the column ready to be worked and dragged forward. Try free #custosell #estimates #projects #templates #Custosell #SmallBusiness
+TAGS: custosell, estimates, projects, templates, quotes, invoicing, project management, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Task in. Column filled." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D172" s="5" t="n"/>
@@ -9088,7 +10805,17 @@
   - "Title. Dates. Checklist. Done."
 DEMO DATA: A task card on a project board.
 CTA: Try free
-RELATED: [11-pipeline-crm.md](./11-pipeline-crm.md)</t>
+RELATED: [11-pipeline-crm.md](./11-pipeline-crm.md)
+PUBLISHED TITLE: Every task card is a mini project.
+SHORT-FORM VARIANT: Every task card is a mini project.
+PUBLISHED DESCRIPTION: Open a task card to edit its title, description, start and due dates, labels, checklist, links, custom fields, and attachments - assign people, add comments, and see its full history in one place. Try free #custosell #estimates #projects #templates #Custosell #SmallBusiness
+TAGS: custosell, estimates, projects, templates, quotes, invoicing, project management, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Title. Dates. Checklist. Done." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D173" s="5" t="n"/>
@@ -9137,7 +10864,17 @@
   - "Drag. Tick. Pin. Done."
 DEMO DATA: A project board with several cards.
 CTA: Try free
-RELATED: [11-pipeline-crm.md](./11-pipeline-crm.md)</t>
+RELATED: [11-pipeline-crm.md](./11-pipeline-crm.md)
+PUBLISHED TITLE: Drag it. Duplicate it. Mark it done.
+SHORT-FORM VARIANT: Drag it. Duplicate it. Mark it done.
+PUBLISHED DESCRIPTION: Run your board - drag task cards between columns, tick a card complete, pin it to the top, duplicate it, or move it to another board. Reorder columns too, so the board flows the way the job does. Try free #custosell #estimates #projects #templates #Custosell #SmallBusiness
+TAGS: custosell, estimates, projects, templates, quotes, invoicing, project management, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Drag. Tick. Pin. Done." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D174" s="5" t="n"/>
@@ -9186,7 +10923,17 @@
   - "Due. Overdue. Done."
 DEMO DATA: Project task cards with due dates.
 CTA: Try free
-RELATED: [11-pipeline-crm.md](./11-pipeline-crm.md)</t>
+RELATED: [11-pipeline-crm.md](./11-pipeline-crm.md)
+PUBLISHED TITLE: Task due dates, on one calendar you can scan.
+SHORT-FORM VARIANT: Task due dates
+PUBLISHED DESCRIPTION: Switch a project board to the calendar view to see task cards by due, start, or close date - with overdue tasks flagged, month/week/day modes, and a side panel for the day you pick. Try free #custosell #estimates #projects #templates #Custosell #SmallBusiness
+TAGS: custosell, estimates, projects, templates, quotes, invoicing, project management, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Due. Overdue. Done." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D175" s="5" t="n"/>
@@ -9234,7 +10981,17 @@
   - "Add. Reorder. Delete."
 DEMO DATA: A project board being set up.
 CTA: Try free
-RELATED: [11-pipeline-crm.md](./11-pipeline-crm.md)</t>
+RELATED: [11-pipeline-crm.md](./11-pipeline-crm.md)
+PUBLISHED TITLE: Columns that match how the job actually runs.
+SHORT-FORM VARIANT: Columns that match how the job actually runs.
+PUBLISHED DESCRIPTION: Add columns to a project board, rename and recolor them, drag them into the right order, and delete the ones you don't need - so the board mirrors your real workflow. Try free #custosell #estimates #projects #templates #Custosell #SmallBusiness
+TAGS: custosell, estimates, projects, templates, quotes, invoicing, project management, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Add. Reorder. Delete." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D176" s="5" t="n"/>
@@ -9283,7 +11040,17 @@
   - "@me. !high. #today. Found."
 DEMO DATA: A board with labeled, prioritized, dated task cards.
 CTA: Try free
-RELATED: [11-pipeline-crm.md](./11-pipeline-crm.md)</t>
+RELATED: [11-pipeline-crm.md](./11-pipeline-crm.md)
+PUBLISHED TITLE: Find any task. Or import a whole list.
+SHORT-FORM VARIANT: Find any task. Or import a whole list.
+PUBLISHED DESCRIPTION: Search tasks on a board with plain text or smart tokens (@label, !high, #today, @me) to narrow instantly, or import a whole task list from a spreadsheet using the import template. Try free #custosell #estimates #projects #templates #Custosell #SmallBusiness
+TAGS: custosell, estimates, projects, templates, quotes, invoicing, project management, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "@me. !high. #today. Found." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D177" s="5" t="n"/>
@@ -9332,7 +11099,17 @@
   - "Files. Goals. Wins. Chat."
 DEMO DATA: A project board with resources, a target, and a post.
 CTA: Try free
-RELATED: [11-pipeline-crm.md](./11-pipeline-crm.md)</t>
+RELATED: [11-pipeline-crm.md](./11-pipeline-crm.md)
+PUBLISHED TITLE: Everything the board needs, one tab bar.
+SHORT-FORM VARIANT: Everything the board needs
+PUBLISHED DESCRIPTION: Along the bottom of every board sit the workspace tabs - switch between boards, open shared resources, watch progress targets, celebrate on the wall of fame, and chat in the board discussion - each with live counts. Try free #custosell #estimates #projects #templates #Custosell #SmallBusiness
+TAGS: custosell, estimates, projects, templates, quotes, invoicing, project management, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Files. Goals. Wins. Chat." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D178" s="5" t="n"/>
@@ -9384,7 +11161,17 @@
   - "Viewer. Contributor. Manager."
 DEMO DATA: A project board and a few staff accounts.
 CTA: Try free
-RELATED: [11-pipeline-crm.md](./11-pipeline-crm.md)</t>
+RELATED: [11-pipeline-crm.md](./11-pipeline-crm.md)
+PUBLISHED TITLE: Who sees the board - and who can change it.
+SHORT-FORM VARIANT: Who sees the board
+PUBLISHED DESCRIPTION: Invite staff or any Custosell user to a project or personal board as Viewer, Contributor, or Manager - notify them by email, change roles later, and keep the owner locked in. Board access is separate from project team access. Try free #custosell #estimates #projects #templates #Custosell #SmallBusiness
+TAGS: custosell, estimates, projects, templates, quotes, invoicing, project management, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Viewer. Contributor. Manager." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D179" s="5" t="n"/>
@@ -9435,7 +11222,18 @@
   - "KPI. Goal. Key result. Planned."
 DEMO DATA: A project board with recent task activity.
 CTA: Try free + subscribe
-RELATED: [13-forecasting.md](./13-forecasting.md)</t>
+RELATED: [13-forecasting.md](./13-forecasting.md)
+PUBLISHED TITLE: Give the job a number the team can hit.
+SHORT-FORM VARIANT: Give the job a number the team can hit.
+PUBLISHED DESCRIPTION: Define what success looks like on a project board - KPIs, goals, or objectives with key results - pick a metric and a target value, assign an owner, and preview how it decomposes across the planning period. Try free + subscribe #custosell #estimates #projects #templates #Custosell #SmallBusiness
+TAGS: custosell, estimates, projects, templates, quotes, invoicing, project management, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "KPI. Goal. Key result. Planned." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover
+  - Intro / outro: 2s animated logo intro + end screen with subscribe</t>
         </is>
       </c>
       <c r="D180" s="5" t="n"/>
@@ -9484,7 +11282,17 @@
   - "Created. Completed. Delivered."
 DEMO DATA: A project board with a week of task activity.
 CTA: Try free
-RELATED: [11-pipeline-crm.md](./11-pipeline-crm.md)</t>
+RELATED: [11-pipeline-crm.md](./11-pipeline-crm.md)
+PUBLISHED TITLE: Throughput, completions, and who's delivering - live.
+SHORT-FORM VARIANT: Throughput, completions, and who's delivering
+PUBLISHED DESCRIPTION: Open the project progress view to see tasks created, completed, cancelled, open, completion rate, and completed value - switch between team delivery and your own progress, pick any period, and export the numbers. Try free #custosell #estimates #projects #templates #Custosell #SmallBusiness
+TAGS: custosell, estimates, projects, templates, quotes, invoicing, project management, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Created. Completed. Delivered." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D181" s="5" t="n"/>
@@ -9533,7 +11341,17 @@
   - "Assigned. Owned. Tracked."
 DEMO DATA: A project board with several staff members.
 CTA: Try free
-RELATED: [11-pipeline-crm.md](./11-pipeline-crm.md)</t>
+RELATED: [11-pipeline-crm.md](./11-pipeline-crm.md)
+PUBLISHED TITLE: Every task card has an owner.
+SHORT-FORM VARIANT: Every task card has an owner.
+PUBLISHED DESCRIPTION: Assign staff to a task card when you create it or later - the card shows the assignment chain from creator to assignee, @me filters to your cards, and My progress shows your personal delivery. Try free #custosell #estimates #projects #templates #Custosell #SmallBusiness
+TAGS: custosell, estimates, projects, templates, quotes, invoicing, project management, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Assigned. Owned. Tracked." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D182" s="5" t="n"/>
@@ -9611,7 +11429,17 @@
 `boardUsesTaskTerminology` (task/card language for project + estimates boards) ·
 `useProjectBoard`/`useProjectBoardKanban` (project board via project id) ·
 `isLimitedEstimatesUser`/`getEstimatesModuleDefaultRoute` (board-only users
-land on `/estimates/boards`)</t>
+land on `/estimates/boards`)
+PUBLISHED TITLE: Right people, right access, one project.
+SHORT-FORM VARIANT: Right people
+PUBLISHED DESCRIPTION: Invite staff to a project as Viewer, Contributor, or Manager, control who edits and who manages the team, and keep the owner locked in. Try free #custosell #estimates #projects #templates #Custosell #SmallBusiness
+TAGS: custosell, estimates, projects, templates, quotes, invoicing, project management, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Viewer. Contributor. Manager." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D183" s="5" t="n"/>
@@ -9661,7 +11489,17 @@
   - "Sell -&gt; Journal. Automatically."
 DEMO DATA: A sale and an expense just recorded.
 CTA: Try free + subscribe
-RELATED: [03-sales-pos.md](./03-sales-pos.md)</t>
+RELATED: [03-sales-pos.md](./03-sales-pos.md)
+PUBLISHED TITLE: Sell once. Your books update themselves.
+SHORT-FORM VARIANT: Sell once. Your books update themselves.
+PUBLISHED DESCRIPTION: See how every sale, refund, expense, invoice, and payment on Custosell writes itself into proper double-entry accounting - no accountant required at the till. Try free + subscribe #custosell #accounting #bookkeeping #journal #Custosell #SmallBusiness
+TAGS: custosell, accounting, bookkeeping, journal, trial balance, income statement, balance sheet, vat, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Sell -&gt; Journal. Automatically." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D184" s="5" t="n"/>
@@ -9710,7 +11548,18 @@
   - "Assets. Revenue. Expenses. It's that simple."
 DEMO DATA: A full chart of accounts.
 CTA: Try free + subscribe
-RELATED: [02-dashboard-reports.md](./02-dashboard-reports.md)</t>
+RELATED: [02-dashboard-reports.md](./02-dashboard-reports.md)
+PUBLISHED TITLE: Chart of accounts, explained for shop owners.
+SHORT-FORM VARIANT: Chart of accounts
+PUBLISHED DESCRIPTION: A plain-English tour of the chart of accounts on Custosell - assets, liabilities, equity, revenue, expenses - in flat view or as a parent- child tree, and how each account feeds your reports. Try free + subscribe #custosell #accounting #bookkeeping #journal #Custosell #SmallBusiness
+TAGS: custosell, accounting, bookkeeping, journal, trial balance, income statement, balance sheet, vat, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Assets. Revenue. Expenses. It's that simple." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover
+  - Intro / outro: 2s animated logo intro + end screen with subscribe</t>
         </is>
       </c>
       <c r="D185" s="5" t="n"/>
@@ -9760,7 +11609,17 @@
   - "Balanced = green light"
 DEMO DATA: Active accounts in the chart of accounts.
 CTA: Try free
-RELATED: [09-accounting.md](./09-accounting.md)</t>
+RELATED: [09-accounting.md](./09-accounting.md)
+PUBLISHED TITLE: When the system can't do it, you can.
+SHORT-FORM VARIANT: When the system can't do it
+PUBLISHED DESCRIPTION: Record your own balanced journal entry - pick accounts, mark each line Debit or Credit, and watch the live balanced indicator turn green. Attach a supporting document and save as a draft. Try free #custosell #accounting #bookkeeping #journal #Custosell #SmallBusiness
+TAGS: custosell, accounting, bookkeeping, journal, trial balance, income statement, balance sheet, vat, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Balanced = green light" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D186" s="5" t="n"/>
@@ -9809,7 +11668,17 @@
   - "Locked, not edited"
 DEMO DATA: A posted journal entry.
 CTA: Try free
-RELATED: [09-accounting.md](./09-accounting.md)</t>
+RELATED: [09-accounting.md](./09-accounting.md)
+PUBLISHED TITLE: Draft, post, reverse - the audit trail stays clean.
+SHORT-FORM VARIANT: Draft, post, reverse
+PUBLISHED DESCRIPTION: Keep draft entries editable, lock them forever by posting, and fix mistakes with a reversing entry instead of editing history. Every change stays traceable. Try free #custosell #accounting #bookkeeping #journal #Custosell #SmallBusiness
+TAGS: custosell, accounting, bookkeeping, journal, trial balance, income statement, balance sheet, vat, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Locked, not edited" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D187" s="5" t="n"/>
@@ -9857,7 +11726,17 @@
   - "Balanced or not, in one glance"
 DEMO DATA: A period with posted entries.
 CTA: Try free
-RELATED: [09-accounting.md](./09-accounting.md)</t>
+RELATED: [09-accounting.md](./09-accounting.md)
+PUBLISHED TITLE: Debits and credits - always equal?
+SHORT-FORM VARIANT: Debits and credits
+PUBLISHED DESCRIPTION: Open the trial balance for any accounting period, see every account's debit and credit balances, and confirm the books balance at a glance - or spot the difference. Try free #custosell #accounting #bookkeeping #journal #Custosell #SmallBusiness
+TAGS: custosell, accounting, bookkeeping, journal, trial balance, income statement, balance sheet, vat, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Balanced or not, in one glance" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D188" s="5" t="n"/>
@@ -9905,7 +11784,17 @@
   - "Clean P&amp;L, on demand"
 DEMO DATA: Full business activity in the period.
 CTA: Try free
-RELATED: [08-expenses-budgets-income.md](./08-expenses-budgets-income.md)</t>
+RELATED: [08-expenses-budgets-income.md](./08-expenses-budgets-income.md)
+PUBLISHED TITLE: Hand your accountant a clean P&amp;L - anytime.
+SHORT-FORM VARIANT: Hand your accountant a clean P&amp;L
+PUBLISHED DESCRIPTION: Generate a correct profit &amp; loss statement for any accounting period - revenue, COGS, gross profit, operating income, and net income, all built from real double-entry data. Try free #custosell #accounting #bookkeeping #journal #Custosell #SmallBusiness
+TAGS: custosell, accounting, bookkeeping, journal, trial balance, income statement, balance sheet, vat, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Clean P&amp;L, on demand" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D189" s="5" t="n"/>
@@ -9953,7 +11842,17 @@
   - "A = L + E, verified"
 DEMO DATA: Posted entries across asset, liability, and equity accounts.
 CTA: Try free
-RELATED: [09-accounting.md](./09-accounting.md)</t>
+RELATED: [09-accounting.md](./09-accounting.md)
+PUBLISHED TITLE: Assets = Liabilities + Equity. Verified.
+SHORT-FORM VARIANT: Assets = Liabilities + Equity. Verified.
+PUBLISHED DESCRIPTION: Open the balance sheet for any period and see assets, liabilities, and equity sections - with the accounting equation checked for you and a green tick when it holds. Try free #custosell #accounting #bookkeeping #journal #Custosell #SmallBusiness
+TAGS: custosell, accounting, bookkeeping, journal, trial balance, income statement, balance sheet, vat, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "A = L + E, verified" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D190" s="5" t="n"/>
@@ -10001,7 +11900,17 @@
   - "Five reports, one screen"
 DEMO DATA: A complete month of activity.
 CTA: Try free + subscribe
-RELATED: [02-dashboard-reports.md](./02-dashboard-reports.md)</t>
+RELATED: [02-dashboard-reports.md](./02-dashboard-reports.md)
+PUBLISHED TITLE: Trial balance, P&amp;L, balance sheet, cash flow, equity - one screen.
+SHORT-FORM VARIANT: Trial balance, P&amp;L, balance sheet, cash flow, equity
+PUBLISHED DESCRIPTION: The financial statements dashboard shows all five key reports for the same date range at once, each with its headline number - then export any one to PDF. Try free + subscribe #custosell #accounting #bookkeeping #journal #Custosell #SmallBusiness
+TAGS: custosell, accounting, bookkeeping, journal, trial balance, income statement, balance sheet, vat, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Five reports, one screen" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D191" s="5" t="n"/>
@@ -10049,7 +11958,17 @@
   - "Healthy. Warning. Act."
 DEMO DATA: Several periods of posted activity.
 CTA: Try free
-RELATED: [09-accounting.md](./09-accounting.md)</t>
+RELATED: [09-accounting.md](./09-accounting.md)
+PUBLISHED TITLE: Is the business healthy? The ratios know.
+SHORT-FORM VARIANT: Is the business healthy? The ratios know.
+PUBLISHED DESCRIPTION: Open the ratios dashboard for liquidity, profitability, solvency, and efficiency - click any ratio for a 12-month trend, and read the color-coded recommendations with actions. Try free #custosell #accounting #bookkeeping #journal #Custosell #SmallBusiness
+TAGS: custosell, accounting, bookkeeping, journal, trial balance, income statement, balance sheet, vat, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Healthy. Warning. Act." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D192" s="5" t="n"/>
@@ -10097,7 +12016,17 @@
   - "Month locked"
 DEMO DATA: An open accounting period with activity.
 CTA: Try free
-RELATED: [09-accounting.md](./09-accounting.md)</t>
+RELATED: [09-accounting.md](./09-accounting.md)
+PUBLISHED TITLE: Lock the month. Protect your books.
+SHORT-FORM VARIANT: Lock the month. Protect your books.
+PUBLISHED DESCRIPTION: Close an accounting period to lock every entry in it against further changes - the clean way to protect finished months - and reopen only when a correction is truly necessary. Try free #custosell #accounting #bookkeeping #journal #Custosell #SmallBusiness
+TAGS: custosell, accounting, bookkeeping, journal, trial balance, income statement, balance sheet, vat, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Month locked" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D193" s="5" t="n"/>
@@ -10147,7 +12076,17 @@
   - "Depreciation, on autopilot"
 DEMO DATA: At least one registered fixed asset.
 CTA: Try free + subscribe
-RELATED: [15-hr.md](./15-hr.md)</t>
+RELATED: [15-hr.md](./15-hr.md)
+PUBLISHED TITLE: Your assets lose value. Track it correctly.
+SHORT-FORM VARIANT: Your assets lose value. Track it correctly.
+PUBLISHED DESCRIPTION: Register fixed assets - laptops, phones, vehicles - with cost, salvage value, and useful life, then run depreciation to post the correct journal entries for a period and view each asset's full schedule. Try free + subscribe #custosell #accounting #bookkeeping #journal #Custosell #SmallBusiness
+TAGS: custosell, accounting, bookkeeping, journal, trial balance, income statement, balance sheet, vat, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Depreciation, on autopilot" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D194" s="5" t="n"/>
@@ -10196,7 +12135,17 @@
   - "Stock = Books"
 DEMO DATA: Tracked products with stock and cost.
 CTA: Try free
-RELATED: [05-inventory-products.md](./05-inventory-products.md)</t>
+RELATED: [05-inventory-products.md](./05-inventory-products.md)
+PUBLISHED TITLE: Stock on the shelf vs stock in your books - aligned.
+SHORT-FORM VARIANT: Stock on the shelf vs stock in your books
+PUBLISHED DESCRIPTION: See stock book value against the general ledger inventory account, find what's misaligned, and post the opening inventory adjustment to bring the books in line. Try free #custosell #accounting #bookkeeping #journal #Custosell #SmallBusiness
+TAGS: custosell, accounting, bookkeeping, journal, trial balance, income statement, balance sheet, vat, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Stock = Books" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D195" s="5" t="n"/>
@@ -10278,7 +12227,17 @@
 **Auto-journaling events (BE):** `SaleCreatedForAccounting` ·
 `SaleRefundedForAccounting` · `ExpenseCreatedForAccounting` ·
 `InvoiceSentForAccounting` · `InvoicePaidForAccounting` ·
-`PaymentRecordedForAccounting` · `PayoutCompletedForAccounting`</t>
+`PaymentRecordedForAccounting` · `PayoutCompletedForAccounting`
+PUBLISHED TITLE: Move your books in and out - cleanly.
+SHORT-FORM VARIANT: Move your books in and out
+PUBLISHED DESCRIPTION: Download a template, import your chart of accounts or journal entries from Excel/CSV, and export current data - with per-row validation so you always know what landed. Try free #custosell #accounting #bookkeeping #journal #Custosell #SmallBusiness
+TAGS: custosell, accounting, bookkeeping, journal, trial balance, income statement, balance sheet, vat, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Import. Validate. Done." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D196" s="5" t="n"/>
@@ -10326,7 +12285,17 @@
   - "A cabinet for every paper trail"
 DEMO DATA: A business with existing receipts and contracts.
 CTA: Try free + subscribe
-RELATED: [03-sales-pos.md](./03-sales-pos.md)</t>
+RELATED: [03-sales-pos.md](./03-sales-pos.md)
+PUBLISHED TITLE: One home for every paper your business owns.
+SHORT-FORM VARIANT: One home for every paper your business owns.
+PUBLISHED DESCRIPTION: Create named cabinets in the Custosell documents vault - like Receipts, Contracts, or Tax - and see every file you own as color-coded cards. Stop losing paper. Try free + subscribe #custosell #documents #filestorage #vault #Custosell #SmallBusiness
+TAGS: custosell, documents, file storage, vault, folders, tags, search, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "A cabinet for every paper trail" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D197" s="5" t="n"/>
@@ -10375,7 +12344,17 @@
   - "Uploaded and filed"
 DEMO DATA: A few receipts or PDF files to upload.
 CTA: Try free + subscribe
-RELATED: [10-documents.md](./10-documents.md)</t>
+RELATED: [10-documents.md](./10-documents.md)
+PUBLISHED TITLE: Drop a file or save a link - it's filed forever.
+SHORT-FORM VARIANT: Drop a file or save a link
+PUBLISHED DESCRIPTION: Upload receipts, invoices, and PDFs into a cabinet - or add a web link - with tags and access chosen at upload time. A live progress bar shows each file landing. Try free + subscribe #custosell #documents #filestorage #vault #Custosell #SmallBusiness
+TAGS: custosell, documents, file storage, vault, folders, tags, search, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Uploaded and filed" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D198" s="5" t="n"/>
@@ -10423,7 +12402,17 @@
   - "Imported with structure"
 DEMO DATA: A local folder with a few subfolders and files.
 CTA: Try free
-RELATED: [10-documents.md](./10-documents.md)</t>
+RELATED: [10-documents.md](./10-documents.md)
+PUBLISHED TITLE: Bring your whole folder in - structure included.
+SHORT-FORM VARIANT: Bring your whole folder in
+PUBLISHED DESCRIPTION: Build nested folders inside a cabinet and import a whole local folder so its tree of files is recreated in the vault - no reorganizing by hand. Try free #custosell #documents #filestorage #vault #Custosell #SmallBusiness
+TAGS: custosell, documents, file storage, vault, folders, tags, search, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Imported with structure" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D199" s="5" t="n"/>
@@ -10472,7 +12461,17 @@
   - "Viewer. Contributor. Manager."
 DEMO DATA: A team with several staff accounts.
 CTA: Try free
-RELATED: [17-settings.md](./17-settings.md)</t>
+RELATED: [17-settings.md](./17-settings.md)
+PUBLISHED TITLE: Some files are for everyone. Some are just for you.
+SHORT-FORM VARIANT: Some files are for everyone. Some are just for you.
+PUBLISHED DESCRIPTION: Control access on a cabinet, folder, or file - same as the folder, everyone on the team, specific people, or only you - and give each person Viewer, Contributor, or Manager powers. Try free #custosell #documents #filestorage #vault #Custosell #SmallBusiness
+TAGS: custosell, documents, file storage, vault, folders, tags, search, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Viewer. Contributor. Manager." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D200" s="5" t="n"/>
@@ -10519,7 +12518,17 @@
   - "Search. Filter. Found."
 DEMO DATA: Documents tagged across a few categories.
 CTA: Try free
-RELATED: [10-documents.md](./10-documents.md)</t>
+RELATED: [10-documents.md](./10-documents.md)
+PUBLISHED TITLE: That invoice from March? Found it.
+SHORT-FORM VARIANT: That invoice from March? Found it.
+PUBLISHED DESCRIPTION: Search files inside a cabinet by name, or filter by a tag, and click any tag chip on a document to instantly see all matching files. Try free #custosell #documents #filestorage #vault #Custosell #SmallBusiness
+TAGS: custosell, documents, file storage, vault, folders, tags, search, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Search. Filter. Found." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D201" s="5" t="n"/>
@@ -10566,7 +12575,17 @@
   - "Preview. Edit. Save."
 DEMO DATA: A PDF, an image, and a text or CSV file.
 CTA: Try free
-RELATED: [10-documents.md](./10-documents.md)</t>
+RELATED: [10-documents.md](./10-documents.md)
+PUBLISHED TITLE: PDFs, images, audio, and text - preview without leaving.
+SHORT-FORM VARIANT: PDFs, images, audio, and text - preview without
+PUBLISHED DESCRIPTION: Preview PDFs, images, audio, video, and text right in the vault - and edit plain-text and CSV files inline without downloading anything. Try free #custosell #documents #filestorage #vault #Custosell #SmallBusiness
+TAGS: custosell, documents, file storage, vault, folders, tags, search, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Preview. Edit. Save." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D202" s="5" t="n"/>
@@ -10613,7 +12632,17 @@
   - "Shared in one click"
 DEMO DATA: A folder with a few documents.
 CTA: Try free
-RELATED: [19-notifications-webpush.md](./19-notifications-webpush.md)</t>
+RELATED: [19-notifications-webpush.md](./19-notifications-webpush.md)
+PUBLISHED TITLE: Send a file or share a whole folder - from the vault.
+SHORT-FORM VARIANT: Send a file or share a whole folder
+PUBLISHED DESCRIPTION: Email a document or folder straight from the vault for your accountant or partner, or download any folder as a zip file with one click. Try free #custosell #documents #filestorage #vault #Custosell #SmallBusiness
+TAGS: custosell, documents, file storage, vault, folders, tags, search, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Shared in one click" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D203" s="5" t="n"/>
@@ -10660,7 +12689,17 @@
   - "Filed with its owner"
 DEMO DATA: A customer and a project with uploaded documents.
 CTA: Try free
-RELATED: [07-customers.md](./07-customers.md)</t>
+RELATED: [07-customers.md](./07-customers.md)
+PUBLISHED TITLE: Every file tied to who it belongs to.
+SHORT-FORM VARIANT: Every file tied to who it belongs to.
+PUBLISHED DESCRIPTION: Attach a document to a customer or project when you upload it - so invoices, contracts, and specs live with the record they belong to. Try free #custosell #documents #filestorage #vault #Custosell #SmallBusiness
+TAGS: custosell, documents, file storage, vault, folders, tags, search, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Filed with its owner" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D204" s="5" t="n"/>
@@ -10707,7 +12746,17 @@
   - "Your vault, your look"
 DEMO DATA: A populated vault.
 CTA: Try free
-RELATED: [17-settings.md](./17-settings.md)</t>
+RELATED: [17-settings.md](./17-settings.md)
+PUBLISHED TITLE: Make the vault feel like yours.
+SHORT-FORM VARIANT: Make the vault feel like yours.
+PUBLISHED DESCRIPTION: Set a business-wide vault canvas - accent color plus a gradient, solid, or photo background - and give each cabinet its own canvas look. Try free #custosell #documents #filestorage #vault #Custosell #SmallBusiness
+TAGS: custosell, documents, file storage, vault, folders, tags, search, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Your vault, your look" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D205" s="5" t="n"/>
@@ -10781,7 +12830,17 @@
 `/{id}/export` (zip) + `/{id}/email`
 **Vault client helpers (FE):** `uploadDocumentWithProgress` ·
 `downloadFileWithProgress` · `downloadFolderExportWithProgress` ·
-`importFolderTree` (recreates a local folder tree in the vault)</t>
+`importFolderTree` (recreates a local folder tree in the vault)
+PUBLISHED TITLE: Every upload, move, and email - on record.
+SHORT-FORM VARIANT: Every upload, move, and email
+PUBLISHED DESCRIPTION: Open the vault activity feed to see who uploaded, moved, renamed, emailed, or deleted what - a full audit trail for your documents. Try free #custosell #documents #filestorage #vault #Custosell #SmallBusiness
+TAGS: custosell, documents, file storage, vault, folders, tags, search, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Filed. Moved. Emailed. Logged." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D206" s="5" t="n"/>
@@ -10830,7 +12889,17 @@
   - "New. Contacted. Qualified. Proposal. Closed."
 DEMO DATA: A fresh business with the seeded board.
 CTA: Try free + subscribe
-RELATED: [07-customers.md](./07-customers.md)</t>
+RELATED: [07-customers.md](./07-customers.md)
+PUBLISHED TITLE: Your pipeline is already there - shape it.
+SHORT-FORM VARIANT: Your pipeline is already there
+PUBLISHED DESCRIPTION: Every new Custosell business gets a default sales board with the classic stages - New, Contacted, Qualified, Proposal, Negotiation, Closed won, Closed lost. Rename, recolor, reorder, and add stages to match how you sell. Try free + subscribe #custosell #crm #pipeline #leads #Custosell #SmallBusiness
+TAGS: custosell, crm, pipeline, leads, sales funnel, kanban, deals, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "New. Contacted. Qualified. Proposal. Closed." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D207" s="5" t="n"/>
@@ -10878,7 +12947,17 @@
   - "Add. Nurture. Close."
 DEMO DATA: A few leads in various stages.
 CTA: Try free + subscribe
-RELATED: [11-pipeline-crm.md](./11-pipeline-crm.md)</t>
+RELATED: [11-pipeline-crm.md](./11-pipeline-crm.md)
+PUBLISHED TITLE: Every opportunity has a place and a next step.
+SHORT-FORM VARIANT: Every opportunity has a place and a next step.
+PUBLISHED DESCRIPTION: Add a lead to your board with contact details, expected value, due date, priority, and labels - then drag it through the stages as the deal moves. Win it or lose it from the stage itself. Try free + subscribe #custosell #crm #pipeline #leads #Custosell #SmallBusiness
+TAGS: custosell, crm, pipeline, leads, sales funnel, kanban, deals, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Add. Nurture. Close." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D208" s="5" t="n"/>
@@ -10925,7 +13004,17 @@
   - "My work, one list"
 DEMO DATA: Leads assigned to the logged-in user.
 CTA: Try free
-RELATED: [11-pipeline-crm.md](./11-pipeline-crm.md)</t>
+RELATED: [11-pipeline-crm.md](./11-pipeline-crm.md)
+PUBLISHED TITLE: Your deals, your tasks - in one list.
+SHORT-FORM VARIANT: Your deals, your tasks
+PUBLISHED DESCRIPTION: See every open lead assigned to you in one place, then open its full detail straight from the list. No hunting through boards. Try free #custosell #crm #pipeline #leads #Custosell #SmallBusiness
+TAGS: custosell, crm, pipeline, leads, sales funnel, kanban, deals, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "My work, one list" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D209" s="5" t="n"/>
@@ -10972,7 +13061,17 @@
   - "Filter. Find. Act."
 DEMO DATA: Leads across multiple boards and statuses.
 CTA: Try free
-RELATED: [11-pipeline-crm.md](./11-pipeline-crm.md)</t>
+RELATED: [11-pipeline-crm.md](./11-pipeline-crm.md)
+PUBLISHED TITLE: Filter every lead across every board.
+SHORT-FORM VARIANT: Filter every lead across every board.
+PUBLISHED DESCRIPTION: Search and filter all leads and cards by status, board, assignee, source, and card type - with live totals for open leads, value, and wins. Try free #custosell #crm #pipeline #leads #Custosell #SmallBusiness
+TAGS: custosell, crm, pipeline, leads, sales funnel, kanban, deals, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Filter. Find. Act." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D210" s="5" t="n"/>
@@ -11019,7 +13118,17 @@
   - "Due dates, at a glance"
 DEMO DATA: Leads with due or expected close dates.
 CTA: Try free
-RELATED: [11-pipeline-crm.md](./11-pipeline-crm.md)</t>
+RELATED: [11-pipeline-crm.md](./11-pipeline-crm.md)
+PUBLISHED TITLE: Leads with dates, on a month you can scan.
+SHORT-FORM VARIANT: Leads with dates
+PUBLISHED DESCRIPTION: Switch any board to the calendar view to see leads by due, start, or expected close date - colored by priority, with a day panel for details. Try free #custosell #crm #pipeline #leads #Custosell #SmallBusiness
+TAGS: custosell, crm, pipeline, leads, sales funnel, kanban, deals, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Due dates, at a glance" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D211" s="5" t="n"/>
@@ -11066,7 +13175,17 @@
   - "Remind me. And I close."
 DEMO DATA: A lead with a follow-up date.
 CTA: Try free
-RELATED: [19-notifications-webpush.md](./19-notifications-webpush.md)</t>
+RELATED: [19-notifications-webpush.md](./19-notifications-webpush.md)
+PUBLISHED TITLE: The fortune is in the follow-up.
+SHORT-FORM VARIANT: The fortune is
+PUBLISHED DESCRIPTION: Set a reminder on any lead - when and how (in-app, email, or both) - and Custosell nags you so no deal goes cold. Try free #custosell #crm #pipeline #leads #Custosell #SmallBusiness
+TAGS: custosell, crm, pipeline, leads, sales funnel, kanban, deals, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Remind me. And I close." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D212" s="5" t="n"/>
@@ -11113,7 +13232,17 @@
   - "Won -&gt; Converted"
 DEMO DATA: A lead in a won stage.
 CTA: Try free
-RELATED: [07-customers.md](./07-customers.md)</t>
+RELATED: [07-customers.md](./07-customers.md)
+PUBLISHED TITLE: They said yes - lock them in as a customer.
+SHORT-FORM VARIANT: They said yes
+PUBLISHED DESCRIPTION: Convert a won lead into a customer record in one click, keeping the connection back to the deal. No re-typing contact details. Try free #custosell #crm #pipeline #leads #Custosell #SmallBusiness
+TAGS: custosell, crm, pipeline, leads, sales funnel, kanban, deals, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Won -&gt; Converted" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D213" s="5" t="n"/>
@@ -11160,7 +13289,17 @@
   - "Viewer. Contributor. Manager."
 DEMO DATA: A team with several staff accounts.
 CTA: Try free
-RELATED: [17-settings.md](./17-settings.md)</t>
+RELATED: [17-settings.md](./17-settings.md)
+PUBLISHED TITLE: Everyone knows their role on the board.
+SHORT-FORM VARIANT: Everyone knows their role on the board.
+PUBLISHED DESCRIPTION: Invite team members to a board as Viewer, Contributor, or Manager, and control who can edit cards, run automations, or manage settings. Try free #custosell #crm #pipeline #leads #Custosell #SmallBusiness
+TAGS: custosell, crm, pipeline, leads, sales funnel, kanban, deals, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Viewer. Contributor. Manager." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D214" s="5" t="n"/>
@@ -11207,7 +13346,17 @@
   - "Your board, your look"
 DEMO DATA: A populated board.
 CTA: Try free
-RELATED: [11-pipeline-crm.md](./11-pipeline-crm.md)</t>
+RELATED: [11-pipeline-crm.md](./11-pipeline-crm.md)
+PUBLISHED TITLE: Make your board feel like your business.
+SHORT-FORM VARIANT: Make your board feel like your business.
+PUBLISHED DESCRIPTION: Give a board its own cover color and background - gallery or your own upload - so each pipeline is instantly recognizable. Try free #custosell #crm #pipeline #leads #Custosell #SmallBusiness
+TAGS: custosell, crm, pipeline, leads, sales funnel, kanban, deals, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Your board, your look" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D215" s="5" t="n"/>
@@ -11255,7 +13404,17 @@
   - "Board chat, in context"
 DEMO DATA: A team using the board.
 CTA: Try free
-RELATED: [11-pipeline-crm.md](./11-pipeline-crm.md)</t>
+RELATED: [11-pipeline-crm.md](./11-pipeline-crm.md)
+PUBLISHED TITLE: Talk about the board, where the board lives.
+SHORT-FORM VARIANT: Talk about the board
+PUBLISHED DESCRIPTION: Chat on the board conversation - reply in threads, react, pin important messages, and @mention teammates - with unread badges so nothing is missed. Try free #custosell #crm #pipeline #leads #Custosell #SmallBusiness
+TAGS: custosell, crm, pipeline, leads, sales funnel, kanban, deals, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Board chat, in context" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D216" s="5" t="n"/>
@@ -11302,7 +13461,17 @@
   - "Announce. Ask. Decide."
 DEMO DATA: A board with a few members.
 CTA: Try free
-RELATED: [11-pipeline-crm.md](./11-pipeline-crm.md)</t>
+RELATED: [11-pipeline-crm.md](./11-pipeline-crm.md)
+PUBLISHED TITLE: Tell the team. Or ask them.
+SHORT-FORM VARIANT: Tell the team. Or ask them.
+PUBLISHED DESCRIPTION: Post an announcement to the board everyone sees on open, or run a poll with options and deadlines - perfect for quick team decisions. Try free #custosell #crm #pipeline #leads #Custosell #SmallBusiness
+TAGS: custosell, crm, pipeline, leads, sales funnel, kanban, deals, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Announce. Ask. Decide." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D217" s="5" t="n"/>
@@ -11350,7 +13519,17 @@
   - "Won -&gt; auto-announced"
 DEMO DATA: A board with automation rules.
 CTA: Try free
-RELATED: [19-notifications-webpush.md](./19-notifications-webpush.md)</t>
+RELATED: [19-notifications-webpush.md](./19-notifications-webpush.md)
+PUBLISHED TITLE: The board tells the team, automatically.
+SHORT-FORM VARIANT: The board tells the team
+PUBLISHED DESCRIPTION: Set automation rules - when a card enters a stage or is won or lost - and Custosell posts the update to the board conversation for you. Try free #custosell #crm #pipeline #leads #Custosell #SmallBusiness
+TAGS: custosell, crm, pipeline, leads, sales funnel, kanban, deals, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Won -&gt; auto-announced" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D218" s="5" t="n"/>
@@ -11400,7 +13579,18 @@
   - "Target. Key results. Daily plan."
 DEMO DATA: A board with recent activity.
 CTA: Try free + subscribe
-RELATED: [13-forecasting.md](./13-forecasting.md)</t>
+RELATED: [13-forecasting.md](./13-forecasting.md)
+PUBLISHED TITLE: Set a goal. Decompose it. Track it daily.
+SHORT-FORM VARIANT: Set a goal. Decompose it. Track it daily.
+PUBLISHED DESCRIPTION: Open the progress view to see team and personal delivery for any period, then set board targets - KPIs, goals, or objectives - with key results and a decomposition preview down to the day. Try free + subscribe #custosell #crm #pipeline #leads #Custosell #SmallBusiness
+TAGS: custosell, crm, pipeline, leads, sales funnel, kanban, deals, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Target. Key results. Daily plan." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover
+  - Intro / outro: 2s animated logo intro + end screen with subscribe</t>
         </is>
       </c>
       <c r="D219" s="5" t="n"/>
@@ -11447,7 +13637,17 @@
   - "Win rate. Value. Sources."
 DEMO DATA: A pipeline with won and lost history.
 CTA: Try free
-RELATED: [02-dashboard-reports.md](./02-dashboard-reports.md)</t>
+RELATED: [02-dashboard-reports.md](./02-dashboard-reports.md)
+PUBLISHED TITLE: Win rate, pipeline value, and where deals come from.
+SHORT-FORM VARIANT: Win rate
+PUBLISHED DESCRIPTION: See open leads, pipeline value, won and lost deals, converted customers, and win rate - with open leads broken down by stage and source. Try free #custosell #crm #pipeline #leads #Custosell #SmallBusiness
+TAGS: custosell, crm, pipeline, leads, sales funnel, kanban, deals, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Win rate. Value. Sources." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D220" s="5" t="n"/>
@@ -11494,7 +13694,17 @@
   - "Import once, track forever"
 DEMO DATA: A spreadsheet with lead data.
 CTA: Try free
-RELATED: [11-pipeline-crm.md](./11-pipeline-crm.md)</t>
+RELATED: [11-pipeline-crm.md](./11-pipeline-crm.md)
+PUBLISHED TITLE: Paste your leads once - never retype them.
+SHORT-FORM VARIANT: Paste your leads once
+PUBLISHED DESCRIPTION: Download the import template, fill in your leads, and upload them straight into a board - perfect for moving leads out of a spreadsheet. Try free #custosell #crm #pipeline #leads #Custosell #SmallBusiness
+TAGS: custosell, crm, pipeline, leads, sales funnel, kanban, deals, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Import once, track forever" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D221" s="5" t="n"/>
@@ -11541,7 +13751,17 @@
   - "Files with the deal"
 DEMO DATA: A few files or links to share.
 CTA: Try free
-RELATED: [10-documents.md](./10-documents.md)</t>
+RELATED: [10-documents.md](./10-documents.md)
+PUBLISHED TITLE: One home for every file your board needs.
+SHORT-FORM VARIANT: One home for every file your board needs.
+PUBLISHED DESCRIPTION: Add resources to a board - files or links - with visibility (board, team, members, or just you) and see who's using them. Try free #custosell #crm #pipeline #leads #Custosell #SmallBusiness
+TAGS: custosell, crm, pipeline, leads, sales funnel, kanban, deals, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Files with the deal" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D222" s="5" t="n"/>
@@ -11589,7 +13809,17 @@
   - "Booked. Pending. Approved."
 DEMO DATA: A board with booking enabled.
 CTA: Try free
-RELATED: [11-pipeline-crm.md](./11-pipeline-crm.md)</t>
+RELATED: [11-pipeline-crm.md](./11-pipeline-crm.md)
+PUBLISHED TITLE: Clients book your time without calling.
+SHORT-FORM VARIANT: Clients book your time without calling.
+PUBLISHED DESCRIPTION: Turn on a public booking page for a board - pick available days and hours - and share the link. Bookings become pending leads you approve, complete, or reject. Try free #custosell #crm #pipeline #leads #Custosell #SmallBusiness
+TAGS: custosell, crm, pipeline, leads, sales funnel, kanban, deals, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Booked. Pending. Approved." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D223" s="5" t="n"/>
@@ -11689,7 +13919,17 @@
 `/public/book/{token}` + `/slots` + `/check/{reference}`
 **Route middleware (BE):** `auth:sanctum` · `business.active` ·
 `subscription.active` · `pipeline.access` (EnsurePipelineModuleAccess) - public
-booking routes unauthenticated</t>
+booking routes unauthenticated
+PUBLISHED TITLE: Closed it? Put it on the wall.
+SHORT-FORM VARIANT: Closed it? Put it on the wall.
+PUBLISHED DESCRIPTION: Post quotes, shoutouts, performers, and milestones to the board's wall of fame - a fun, motivating feed your team sees when they open the board. Try free #custosell #crm #pipeline #leads #Custosell #SmallBusiness
+TAGS: custosell, crm, pipeline, leads, sales funnel, kanban, deals, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Posted. Pinned. Celebrated." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D224" s="5" t="n"/>
@@ -11738,7 +13978,17 @@
   - "Live at @yourbusiness"
 DEMO DATA: A business with a name, logo, and contact details.
 CTA: Try free + subscribe
-RELATED: [17-settings.md](./17-settings.md)</t>
+RELATED: [17-settings.md](./17-settings.md)
+PUBLISHED TITLE: Your shop, online, in minutes.
+SHORT-FORM VARIANT: Your shop
+PUBLISHED DESCRIPTION: Enable your public shop in Settings, claim a @username, save, and you're live at your own link. Disable it any time - the link then shows as closed. Try free + subscribe #custosell #storefront #onlineshop #ecommerce #Custosell #SmallBusiness
+TAGS: custosell, storefront, online shop, ecommerce, marketplace, buy online, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Live at @yourbusiness" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D225" s="5" t="n"/>
@@ -11787,7 +14037,17 @@
   - "Listed for storefront"
 DEMO DATA: Active products, a couple with images.
 CTA: Try free
-RELATED: [05-inventory-products.md](./05-inventory-products.md)</t>
+RELATED: [05-inventory-products.md](./05-inventory-products.md)
+PUBLISHED TITLE: Pick the products your online customers can buy.
+SHORT-FORM VARIANT: Pick the products your online customers can buy.
+PUBLISHED DESCRIPTION: Choose which products appear on your public shop with the List on my public shop toggle - per product or in bulk - and add product images so they look good online. Try free #custosell #storefront #onlineshop #ecommerce #Custosell #SmallBusiness
+TAGS: custosell, storefront, online shop, ecommerce, marketplace, buy online, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Listed for storefront" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D226" s="5" t="n"/>
@@ -11835,7 +14095,17 @@
   - "Scan. Shop. Done."
 DEMO DATA: A published public shop with a @username.
 CTA: Try free
-RELATED: [14-storefront.md](./14-storefront.md)</t>
+RELATED: [14-storefront.md](./14-storefront.md)
+PUBLISHED TITLE: One link, one QR, your whole shop.
+SHORT-FORM VARIANT: One link
+PUBLISHED DESCRIPTION: Copy your public shop link, share it on WhatsApp, or download a ready QR code to print - customers open your shop instantly on any phone. Try free #custosell #storefront #onlineshop #ecommerce #Custosell #SmallBusiness
+TAGS: custosell, storefront, online shop, ecommerce, marketplace, buy online, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Scan. Shop. Done." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D227" s="5" t="n"/>
@@ -11884,7 +14154,17 @@
   - "Shops, or products. Your pick."
 DEMO DATA: Several published shops with listed products.
 CTA: Try free + subscribe
-RELATED: [05-inventory-products.md](./05-inventory-products.md)</t>
+RELATED: [05-inventory-products.md](./05-inventory-products.md)
+PUBLISHED TITLE: Browse every public shop, or every product.
+SHORT-FORM VARIANT: Browse every public shop
+PUBLISHED DESCRIPTION: Open the discover page and switch between Businesses and Products &amp; Services - search, filter by category, city, currency, price, and rating, and keep scrolling for more. Try free + subscribe #custosell #storefront #onlineshop #ecommerce #Custosell #SmallBusiness
+TAGS: custosell, storefront, online shop, ecommerce, marketplace, buy online, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Shops, or products. Your pick." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D228" s="5" t="n"/>
@@ -11933,7 +14213,17 @@
   - "In stock. On sale. In your cart."
 DEMO DATA: A published shop with priced, in-stock products.
 CTA: Try free
-RELATED: [03-sales-pos.md](./03-sales-pos.md)</t>
+RELATED: [03-sales-pos.md](./03-sales-pos.md)
+PUBLISHED TITLE: A shop page that sells while you sleep.
+SHORT-FORM VARIANT: A shop page that sells while you sleep.
+PUBLISHED DESCRIPTION: Open a shop to see its description, location, phone, rating, and products with live stock badges and sale prices - then add items to your cart. Try free #custosell #storefront #onlineshop #ecommerce #Custosell #SmallBusiness
+TAGS: custosell, storefront, online shop, ecommerce, marketplace, buy online, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "In stock. On sale. In your cart." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D229" s="5" t="n"/>
@@ -11982,7 +14272,17 @@
   - "N businesses, one bag each"
 DEMO DATA: Items from two published shops in the cart.
 CTA: Try free + subscribe
-RELATED: [14-storefront.md](./14-storefront.md)</t>
+RELATED: [14-storefront.md](./14-storefront.md)
+PUBLISHED TITLE: Shop from many shops, one cart at a time.
+SHORT-FORM VARIANT: Shop from many shops
+PUBLISHED DESCRIPTION: Your cart holds one bag per shop - add products from several businesses, switch bags, set delivery contact, and place each order with the right shop. Try free + subscribe #custosell #storefront #onlineshop #ecommerce #Custosell #SmallBusiness
+TAGS: custosell, storefront, online shop, ecommerce, marketplace, buy online, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "N businesses, one bag each" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D230" s="5" t="n"/>
@@ -12031,7 +14331,17 @@
   - "Open -&gt; Completed. Chime included."
 DEMO DATA: A few orders in different statuses.
 CTA: Try free
-RELATED: [03-sales-pos.md](./03-sales-pos.md)</t>
+RELATED: [03-sales-pos.md](./03-sales-pos.md)
+PUBLISHED TITLE: Order status that updates while you watch.
+SHORT-FORM VARIANT: Order status that updates while you watch.
+PUBLISHED DESCRIPTION: See all your online orders with Open / Completed / Invoiced / Cancelled tabs, a live open-orders badge, and a chime when an order changes status. Try free #custosell #storefront #onlineshop #ecommerce #Custosell #SmallBusiness
+TAGS: custosell, storefront, online shop, ecommerce, marketplace, buy online, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Open -&gt; Completed. Chime included." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D231" s="5" t="n"/>
@@ -12080,7 +14390,17 @@
   - "Receipt or invoice, on demand"
 DEMO DATA: An order with a sale and one with an invoice.
 CTA: Try free
-RELATED: [09-accounting.md](./09-accounting.md)</t>
+RELATED: [09-accounting.md](./09-accounting.md)
+PUBLISHED TITLE: Your online order, documented.
+SHORT-FORM VARIANT: Your online order
+PUBLISHED DESCRIPTION: Open any online order and pull up its receipt or invoice - when a shop closes your order into a sale or invoice, the documents are one tap away. Try free #custosell #storefront #onlineshop #ecommerce #Custosell #SmallBusiness
+TAGS: custosell, storefront, online shop, ecommerce, marketplace, buy online, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Receipt or invoice, on demand" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D232" s="5" t="n"/>
@@ -12128,7 +14448,17 @@
   - "Saved for later"
 DEMO DATA: A signed-in buyer account and a few products.
 CTA: Try free
-RELATED: [07-customers.md](./07-customers.md)</t>
+RELATED: [07-customers.md](./07-customers.md)
+PUBLISHED TITLE: Heart it now, buy it later.
+SHORT-FORM VARIANT: Heart it now
+PUBLISHED DESCRIPTION: Tap the heart on any product to save it to your wishlist - it stays there across shops until you order, and ordered products clear themselves out. Try free #custosell #storefront #onlineshop #ecommerce #Custosell #SmallBusiness
+TAGS: custosell, storefront, online shop, ecommerce, marketplace, buy online, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Saved for later" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D233" s="5" t="n"/>
@@ -12176,7 +14506,17 @@
   - "Starred for next time"
 DEMO DATA: A signed-in buyer account and published shops.
 CTA: Try free
-RELATED: [14-storefront.md](./14-storefront.md)</t>
+RELATED: [14-storefront.md](./14-storefront.md)
+PUBLISHED TITLE: Star the shops you'll come back to.
+SHORT-FORM VARIANT: Star the shops you'll come back to.
+PUBLISHED DESCRIPTION: Star any business to keep it in your favorites list - then jump straight back to those shops instead of hunting for them again. Try free #custosell #storefront #onlineshop #ecommerce #Custosell #SmallBusiness
+TAGS: custosell, storefront, online shop, ecommerce, marketplace, buy online, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Starred for next time" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D234" s="5" t="n"/>
@@ -12224,7 +14564,17 @@
   - "Rate it. Help the next buyer."
 DEMO DATA: A signed-in buyer account and a shop with products.
 CTA: Try free
-RELATED: [07-customers.md](./07-customers.md)</t>
+RELATED: [07-customers.md](./07-customers.md)
+PUBLISHED TITLE: One to five stars. Real feedback.
+SHORT-FORM VARIANT: One to five stars. Real feedback.
+PUBLISHED DESCRIPTION: Rate a shop or a product right from its page - your rating saves instantly and updates the average, helping other buyers pick well. Try free #custosell #storefront #onlineshop #ecommerce #Custosell #SmallBusiness
+TAGS: custosell, storefront, online shop, ecommerce, marketplace, buy online, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Rate it. Help the next buyer." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D235" s="5" t="n"/>
@@ -12331,7 +14681,17 @@
 Wishlist is for products (heart); favorites are for businesses (star); both
 server-backed and sign-in gated. Orders poll every 30s with a status-change
 chime. No theme/branding customization exists - shop look comes from the
-Business record (name, logo, description, contact, currency, social links).</t>
+Business record (name, logo, description, contact, currency, social links).
+PUBLISHED TITLE: Facebook, WhatsApp, TikTok - on your shop page.
+SHORT-FORM VARIANT: Facebook, WhatsApp, TikTok
+PUBLISHED DESCRIPTION: Add your social links in settings and they appear on your public shop with brand icons - so customers can follow, message, and find you. Try free #custosell #storefront #onlineshop #ecommerce #Custosell #SmallBusiness
+TAGS: custosell, storefront, online shop, ecommerce, marketplace, buy online, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Follow. Message. Buy." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D236" s="5" t="n"/>
@@ -12380,7 +14740,17 @@
   - "People. Leave. Payroll. One screen."
 DEMO DATA: A few employees, attendance, pending leave, a pay run.
 CTA: Try free + subscribe
-RELATED: [02-dashboard-reports.md](./02-dashboard-reports.md)</t>
+RELATED: [02-dashboard-reports.md](./02-dashboard-reports.md)
+PUBLISHED TITLE: Your whole team, one pulse.
+SHORT-FORM VARIANT: Your whole team
+PUBLISHED DESCRIPTION: Open the HR dashboard to see active people, who's present today, pending leave, open pay runs, and your payroll cash runway - plus a pending leave inbox you can approve from the overview. Try free + subscribe #custosell #hr #payroll #employees #Custosell #SmallBusiness
+TAGS: custosell, hr, payroll, employees, leave, attendance, departments, salary, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "People. Leave. Payroll. One screen." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D237" s="5" t="n"/>
@@ -12429,7 +14799,17 @@
   - "Add. Assign. Onboard."
 DEMO DATA: Departments and positions set up.
 CTA: Try free + subscribe
-RELATED: [17-settings.md](./17-settings.md)</t>
+RELATED: [17-settings.md](./17-settings.md)
+PUBLISHED TITLE: Add staff in under a minute.
+SHORT-FORM VARIANT: Add staff
+PUBLISHED DESCRIPTION: Add an employee with their number, name, employment type, department, and position - they start in onboarding status, and you can create their app login right away if they need one. Try free + subscribe #custosell #hr #payroll #employees #Custosell #SmallBusiness
+TAGS: custosell, hr, payroll, employees, leave, attendance, departments, salary, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Add. Assign. Onboard." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D238" s="5" t="n"/>
@@ -12476,7 +14856,17 @@
   - "Departments first. People second."
 DEMO DATA: A small team to structure.
 CTA: Try free
-RELATED: [15-hr.md](./15-hr.md)</t>
+RELATED: [15-hr.md](./15-hr.md)
+PUBLISHED TITLE: Structure your team before you grow it.
+SHORT-FORM VARIANT: Structure your team before you grow it.
+PUBLISHED DESCRIPTION: Create the departments and positions your team works in - then use them to organize every employee you add. Try free #custosell #hr #payroll #employees #Custosell #SmallBusiness
+TAGS: custosell, hr, payroll, employees, leave, attendance, departments, salary, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Departments first. People second." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D239" s="5" t="n"/>
@@ -12525,7 +14915,17 @@
   - "Login = access. Access = role."
 DEMO DATA: An employee without a login.
 CTA: Try free
-RELATED: [01-account-auth-security.md](./01-account-auth-security.md)</t>
+RELATED: [01-account-auth-security.md](./01-account-auth-security.md)
+PUBLISHED TITLE: A login for every staff member.
+SHORT-FORM VARIANT: A login for every staff member.
+PUBLISHED DESCRIPTION: Create an app login for an employee - with a role and module access - or link an existing staff account, and disconnect or detach it whenever needed. Try free #custosell #hr #payroll #employees #Custosell #SmallBusiness
+TAGS: custosell, hr, payroll, employees, leave, attendance, departments, salary, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Login = access. Access = role." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D240" s="5" t="n"/>
@@ -12572,7 +14972,17 @@
   - "In. Break. Back. Out."
 DEMO DATA: An employee linked to a login.
 CTA: Try free
-RELATED: [04-shifts.md](./04-shifts.md)</t>
+RELATED: [04-shifts.md](./04-shifts.md)
+PUBLISHED TITLE: Clock in. Clock out. Done.
+SHORT-FORM VARIANT: Clock in. Clock out. Done.
+PUBLISHED DESCRIPTION: Staff record their punches - clock in, break start, break end, clock out - and the day builds into the attendance register automatically. Try free #custosell #hr #payroll #employees #Custosell #SmallBusiness
+TAGS: custosell, hr, payroll, employees, leave, attendance, departments, salary, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "In. Break. Back. Out." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D241" s="5" t="n"/>
@@ -12620,7 +15030,17 @@
   - "Present. Absent. Leave. Holiday."
 DEMO DATA: Punch events and a shift or two.
 CTA: Try free
-RELATED: [04-shifts.md](./04-shifts.md)</t>
+RELATED: [04-shifts.md](./04-shifts.md)
+PUBLISHED TITLE: Who's here, who's on leave - at a glance.
+SHORT-FORM VARIANT: Who's here, who's on leave
+PUBLISHED DESCRIPTION: Review the daily register, correct a day's status, import timesheets, and see POS shift clock-ins alongside HR punches. Try free #custosell #hr #payroll #employees #Custosell #SmallBusiness
+TAGS: custosell, hr, payroll, employees, leave, attendance, departments, salary, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Present. Absent. Leave. Holiday." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D242" s="5" t="n"/>
@@ -12668,7 +15088,17 @@
   - "Entitled. Used. Pending. Remaining."
 DEMO DATA: Employees with requests recorded.
 CTA: Try free
-RELATED: [15-hr.md](./15-hr.md)</t>
+RELATED: [15-hr.md](./15-hr.md)
+PUBLISHED TITLE: Leave that runs itself.
+SHORT-FORM VARIANT: Leave that runs itself.
+PUBLISHED DESCRIPTION: Define your leave types - annual, sick, and more - with days per year, whether they're paid, and whether approval is required, then watch balances track used, pending, and remaining days per year. Try free #custosell #hr #payroll #employees #Custosell #SmallBusiness
+TAGS: custosell, hr, payroll, employees, leave, attendance, departments, salary, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Entitled. Used. Pending. Remaining." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D243" s="5" t="n"/>
@@ -12716,7 +15146,17 @@
   - "Pending -&gt; Approved -&gt; Attendance"
 DEMO DATA: A pending leave request.
 CTA: Try free
-RELATED: [15-hr.md](./15-hr.md)</t>
+RELATED: [15-hr.md](./15-hr.md)
+PUBLISHED TITLE: Approve leave without the guesswork.
+SHORT-FORM VARIANT: Approve leave without the guesswork.
+PUBLISHED DESCRIPTION: Staff submit leave, you approve, reject, or cancel with a note - and approved days sync through to attendance while balances stay accurate. Try free #custosell #hr #payroll #employees #Custosell #SmallBusiness
+TAGS: custosell, hr, payroll, employees, leave, attendance, departments, salary, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Pending -&gt; Approved -&gt; Attendance" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D244" s="5" t="n"/>
@@ -12764,7 +15204,17 @@
   - "Structure. Salary. Effective date."
 DEMO DATA: Active employees.
 CTA: Try free
-RELATED: [08-expenses-budgets-income.md](./08-expenses-budgets-income.md)</t>
+RELATED: [08-expenses-budgets-income.md](./08-expenses-budgets-income.md)
+PUBLISHED TITLE: Payroll starts with a plan.
+SHORT-FORM VARIANT: Payroll starts with a plan.
+PUBLISHED DESCRIPTION: Create salary structures for your team and assign each active employee a basic salary with an effective date - the foundation every pay run builds on. Try free #custosell #hr #payroll #employees #Custosell #SmallBusiness
+TAGS: custosell, hr, payroll, employees, leave, attendance, departments, salary, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Structure. Salary. Effective date." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D245" s="5" t="n"/>
@@ -12814,7 +15264,18 @@
   - "Draft -&gt; Calculated -&gt; Approved -&gt; Posted"
 DEMO DATA: Employees with compensations and an open accounting period.
 CTA: Try free + subscribe
-RELATED: [09-accounting.md](./09-accounting.md)</t>
+RELATED: [09-accounting.md](./09-accounting.md)
+PUBLISHED TITLE: Payroll with PAYE and NSSF handled.
+SHORT-FORM VARIANT: Payroll with PAYE and NSSF handled.
+PUBLISHED DESCRIPTION: Create a pay run for a period, calculate gross and Uganda statutory taxes (PAYE, NSSF employee and employer), approve, post to accounting, settle the net, and remit statutory deductions. Try free + subscribe #custosell #hr #payroll #employees #Custosell #SmallBusiness
+TAGS: custosell, hr, payroll, employees, leave, attendance, departments, salary, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Draft -&gt; Calculated -&gt; Approved -&gt; Posted" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover
+  - Intro / outro: 2s animated logo intro + end screen with subscribe</t>
         </is>
       </c>
       <c r="D246" s="5" t="n"/>
@@ -12863,7 +15324,17 @@
   - "Hire = cash runway, quantified"
 DEMO DATA: Employees with compensation and sales history.
 CTA: Try free
-RELATED: [13-forecasting.md](./13-forecasting.md)</t>
+RELATED: [13-forecasting.md](./13-forecasting.md)
+PUBLISHED TITLE: Can you afford that hire? Check before you sign.
+SHORT-FORM VARIANT: Can you afford that hire? Check before you sign.
+PUBLISHED DESCRIPTION: See your monthly payroll burn, cash available, and runway in months - then model a new hire with a basic salary and see how much cash runway it costs. Try free #custosell #hr #payroll #employees #Custosell #SmallBusiness
+TAGS: custosell, hr, payroll, employees, leave, attendance, departments, salary, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Hire = cash runway, quantified" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D247" s="5" t="n"/>
@@ -12911,7 +15382,17 @@
   - "Onboard. Track. Done."
 DEMO DATA: A new employee in onboarding status.
 CTA: Try free
-RELATED: [15-hr.md](./15-hr.md)</t>
+RELATED: [15-hr.md](./15-hr.md)
+PUBLISHED TITLE: A checklist so nothing slips on day one.
+SHORT-FORM VARIANT: A checklist so nothing slips on day one.
+PUBLISHED DESCRIPTION: Build onboarding templates, assign tasks with due dates to new hires, and track progress to done - staff can see their own checklist too. Try free #custosell #hr #payroll #employees #Custosell #SmallBusiness
+TAGS: custosell, hr, payroll, employees, leave, attendance, departments, salary, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Onboard. Track. Done." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D248" s="5" t="n"/>
@@ -12960,7 +15441,17 @@
   - "On track. At risk. Behind."
 DEMO DATA: Employees linked to logins with pipeline and project work.
 CTA: Try free
-RELATED: [11-pipeline-crm.md](./11-pipeline-crm.md)</t>
+RELATED: [11-pipeline-crm.md](./11-pipeline-crm.md)
+PUBLISHED TITLE: Performance scored from real work.
+SHORT-FORM VARIANT: Performance scored from real work.
+PUBLISHED DESCRIPTION: See each linked employee's performance verdict - on track, at risk, or behind - built from pipeline leads, project tasks, and goals, then seed a review draft from that work. Try free #custosell #hr #payroll #employees #Custosell #SmallBusiness
+TAGS: custosell, hr, payroll, employees, leave, attendance, departments, salary, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "On track. At risk. Behind." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D249" s="5" t="n"/>
@@ -13009,7 +15500,17 @@
   - "Assign. Transfer. Return."
 DEMO DATA: An employee and a couple of assets.
 CTA: Try free
-RELATED: [09-accounting.md](./09-accounting.md)</t>
+RELATED: [09-accounting.md](./09-accounting.md)
+PUBLISHED TITLE: Who has the laptop? One tap.
+SHORT-FORM VARIANT: Who has the laptop? One tap.
+PUBLISHED DESCRIPTION: Register company assets, assign them to employees, transfer between staff, and return them - with a full assignment history and book value that syncs with accounting. Try free #custosell #hr #payroll #employees #Custosell #SmallBusiness
+TAGS: custosell, hr, payroll, employees, leave, attendance, departments, salary, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Assign. Transfer. Return." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D250" s="5" t="n"/>
@@ -13058,7 +15559,17 @@
   - "PAYE in. NSSF in. Filed."
 DEMO DATA: A posted pay run.
 CTA: Try free
-RELATED: [09-accounting.md](./09-accounting.md)</t>
+RELATED: [09-accounting.md](./09-accounting.md)
+PUBLISHED TITLE: Statutory reports, ready for the accountant.
+SHORT-FORM VARIANT: Statutory reports
+PUBLISHED DESCRIPTION: Generate the PAYE schedule and NSSF schedule for a pay run or a date range - per employee, with employer and employee contributions - for submission and filing. Try free #custosell #hr #payroll #employees #Custosell #SmallBusiness
+TAGS: custosell, hr, payroll, employees, leave, attendance, departments, salary, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "PAYE in. NSSF in. Filed." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D251" s="5" t="n"/>
@@ -13187,7 +15698,17 @@
 goals, and seeded review drafts carry that snapshot. Payroll affordability
 defaults to a 3-month horizon and supports a hire what-if (basic salary,
 allowances, deductions, start month offset). Payslips are embedded on pay-run
-lines (no dedicated endpoint yet).</t>
+lines (no dedicated endpoint yet).
+PUBLISHED TITLE: Move staff between branches, tracked.
+SHORT-FORM VARIANT: Move staff between branches
+PUBLISHED DESCRIPTION: Transfer a staff member from one branch to another - permanent or temporary - and keep the whole history visible with branch headcount overviews. Try free #custosell #hr #payroll #employees #Custosell #SmallBusiness
+TAGS: custosell, hr, payroll, employees, leave, attendance, departments, salary, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Permanent or temporary, tracked" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D252" s="5" t="n"/>
@@ -13235,7 +15756,17 @@
   - "Runway: months of cash, visible"
 DEMO DATA: An open accounting period, sales history, and payroll.
 CTA: Try free + subscribe
-RELATED: [02-dashboard-reports.md](./02-dashboard-reports.md)</t>
+RELATED: [02-dashboard-reports.md](./02-dashboard-reports.md)
+PUBLISHED TITLE: How many months can you pay everyone?
+SHORT-FORM VARIANT: How many months can you pay everyone?
+PUBLISHED DESCRIPTION: Open the forecasting overview to see cash available, unpaid payroll, monthly burn, and cash runway - with a month-by-month cash ladder that shows exactly when you could go short. Try free + subscribe #custosell #forecasting #budget #cashrunway #Custosell #SmallBusiness
+TAGS: custosell, forecasting, budget, cash runway, scenarios, kpi, projections, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Runway: months of cash, visible" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D253" s="5" t="n"/>
@@ -13284,7 +15815,17 @@
   - "Planned vs spent, per category"
 DEMO DATA: Expense categories with budgets + recorded expenses.
 CTA: Try free
-RELATED: [08-expenses-budgets-income.md](./08-expenses-budgets-income.md)</t>
+RELATED: [08-expenses-budgets-income.md](./08-expenses-budgets-income.md)
+PUBLISHED TITLE: Every category, planned vs spent.
+SHORT-FORM VARIANT: Every category
+PUBLISHED DESCRIPTION: See each expense category's budget against what you actually spent, with variance percentages and an over/under/on-track status so you catch overspend early. Try free #custosell #forecasting #budget #cashrunway #Custosell #SmallBusiness
+TAGS: custosell, forecasting, budget, cash runway, scenarios, kpi, projections, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Planned vs spent, per category" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D254" s="5" t="n"/>
@@ -13332,7 +15873,17 @@
   - "From zero, line by line"
 DEMO DATA: A calendar year and a few expense categories.
 CTA: Try free
-RELATED: [13-forecasting.md](./13-forecasting.md)</t>
+RELATED: [13-forecasting.md](./13-forecasting.md)
+PUBLISHED TITLE: Every shilling starts at zero and earns its place.
+SHORT-FORM VARIANT: Every shilling starts at zero and earns its place.
+PUBLISHED DESCRIPTION: Create an annual budget for a year, then add zero-based lines - each one starts as a draft and every amount can be edited inline. Try free #custosell #forecasting #budget #cashrunway #Custosell #SmallBusiness
+TAGS: custosell, forecasting, budget, cash runway, scenarios, kpi, projections, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "From zero, line by line" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D255" s="5" t="n"/>
@@ -13379,7 +15930,17 @@
   - "Draft -&gt; Justified -&gt; Approved"
 DEMO DATA: A draft budget with at least one line.
 CTA: Try free
-RELATED: [13-forecasting.md](./13-forecasting.md)</t>
+RELATED: [13-forecasting.md](./13-forecasting.md)
+PUBLISHED TITLE: Fund it only if you can argue for it.
+SHORT-FORM VARIANT: Fund it only if you can argue for it.
+PUBLISHED DESCRIPTION: Move each budget line from draft to justified to approved - a line can't be approved until it carries a written business justification. Try free #custosell #forecasting #budget #cashrunway #Custosell #SmallBusiness
+TAGS: custosell, forecasting, budget, cash runway, scenarios, kpi, projections, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Draft -&gt; Justified -&gt; Approved" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D256" s="5" t="n"/>
@@ -13426,7 +15987,17 @@
   - "Plan frozen in time"
 DEMO DATA: A budget with lines and some recorded expenses.
 CTA: Try free
-RELATED: [09-accounting.md](./09-accounting.md)</t>
+RELATED: [09-accounting.md](./09-accounting.md)
+PUBLISHED TITLE: Freeze the forecast so you can compare later.
+SHORT-FORM VARIANT: Freeze the forecast so you can compare later.
+PUBLISHED DESCRIPTION: Roll a budget to capture a forecast snapshot - budget lines plus year-to-date expense actuals - so you have a dated record of your plan. Try free #custosell #forecasting #budget #cashrunway #Custosell #SmallBusiness
+TAGS: custosell, forecasting, budget, cash runway, scenarios, kpi, projections, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Plan frozen in time" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D257" s="5" t="n"/>
@@ -13474,7 +16045,17 @@
   - "Baseline vs what-if"
 DEMO DATA: An overview forecast to use as the baseline.
 CTA: Try free + subscribe
-RELATED: [15-hr.md](./15-hr.md)</t>
+RELATED: [15-hr.md](./15-hr.md)
+PUBLISHED TITLE: What if you hire? What if sales grow?
+SHORT-FORM VARIANT: What if you hire? What if sales grow?
+PUBLISHED DESCRIPTION: Model a hire, extra monthly opex, or a revenue uplift against your baseline cash ladder, and compare scenario vs baseline month by month. Try free + subscribe #custosell #forecasting #budget #cashrunway #Custosell #SmallBusiness
+TAGS: custosell, forecasting, budget, cash runway, scenarios, kpi, projections, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Baseline vs what-if" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D258" s="5" t="n"/>
@@ -13521,7 +16102,17 @@
   - "CAC in. LTV out. Churn visible."
 DEMO DATA: Sales, customers, and acquisition spend data.
 CTA: Try free
-RELATED: [07-customers.md](./07-customers.md)</t>
+RELATED: [07-customers.md](./07-customers.md)
+PUBLISHED TITLE: Growth numbers that tell you if you're healthy.
+SHORT-FORM VARIANT: Growth numbers that tell you if you're healthy.
+PUBLISHED DESCRIPTION: See your trailing 30-day sales pulse, customer acquisition cost, customer lifetime value, and 90-day churn - with monthly burn and runway. Try free #custosell #forecasting #budget #cashrunway #Custosell #SmallBusiness
+TAGS: custosell, forecasting, budget, cash runway, scenarios, kpi, projections, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "CAC in. LTV out. Churn visible." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D259" s="5" t="n"/>
@@ -13607,7 +16198,17 @@
 `ForecastSnapshot` (budget lines + YTD expense actuals captured on roll) ·
 `ForecastKpis` (retail: pulse/CAC/LTV/churn; saas: MRR/ARR/subscribers) ·
 `ForecastScenario` + `ForecastScenarioRun` (baseline + scenario forecast +
-delta)</t>
+delta)
+PUBLISHED TITLE: Sell recurring? See MRR and ARR proxies.
+SHORT-FORM VARIANT: Sell recurring? See MRR and ARR proxies.
+PUBLISHED DESCRIPTION: Mark products or services as recurring and the KPIs page shows MRR, ARR, active subscribers, and average recurring price as simple proxies from your own catalog. Try free #custosell #forecasting #budget #cashrunway #Custosell #SmallBusiness
+TAGS: custosell, forecasting, budget, cash runway, scenarios, kpi, projections, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "MRR from your catalog" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D260" s="5" t="n"/>
@@ -13656,7 +16257,17 @@
   - "Compare. Pick. Pay."
 DEMO DATA: A new business without a plan.
 CTA: Try free + subscribe
-RELATED: [17-settings.md](./17-settings.md)</t>
+RELATED: [17-settings.md](./17-settings.md)
+PUBLISHED TITLE: Pick what fits. Not more.
+SHORT-FORM VARIANT: Pick what fits. Not more.
+PUBLISHED DESCRIPTION: Compare Custosell plans side by side - features and limits - pick a monthly or yearly billing cycle, pay the setup fee, and subscribe with your phone via PesaPal. Try free + subscribe #custosell #subscription #billing #plans #Custosell #SmallBusiness
+TAGS: custosell, subscription, billing, plans, upgrade, invoice, payment, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Compare. Pick. Pay." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D261" s="5" t="n"/>
@@ -13705,7 +16316,17 @@
   - "Proration: credit minus charge"
 DEMO DATA: An active subscription on a lower plan.
 CTA: Try free
-RELATED: [16-subscriptions-billing.md](./16-subscriptions-billing.md)</t>
+RELATED: [16-subscriptions-billing.md](./16-subscriptions-billing.md)
+PUBLISHED TITLE: Upgrade now, pay only the difference.
+SHORT-FORM VARIANT: Upgrade now
+PUBLISHED DESCRIPTION: Move to a higher plan instantly - Custosell shows a proration quote with any credit from your remaining period, and access unlocks right away. Try free #custosell #subscription #billing #plans #Custosell #SmallBusiness
+TAGS: custosell, subscription, billing, plans, upgrade, invoice, payment, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Proration: credit minus charge" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D262" s="5" t="n"/>
@@ -13754,7 +16375,17 @@
   - "End-of-period. Fully reversible."
 DEMO DATA: An active subscription on a higher plan.
 CTA: Try free
-RELATED: [16-subscriptions-billing.md](./16-subscriptions-billing.md)</t>
+RELATED: [16-subscriptions-billing.md](./16-subscriptions-billing.md)
+PUBLISHED TITLE: Downgrade at period end - no surprises.
+SHORT-FORM VARIANT: Downgrade at period end
+PUBLISHED DESCRIPTION: Move to a lower plan at the end of your billing period instead of losing time you already paid for - and cancel the scheduled change if you change your mind. Try free #custosell #subscription #billing #plans #Custosell #SmallBusiness
+TAGS: custosell, subscription, billing, plans, upgrade, invoice, payment, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "End-of-period. Fully reversible." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D263" s="5" t="n"/>
@@ -13801,7 +16432,17 @@
   - "Monthly or yearly. Your call."
 DEMO DATA: An active monthly subscription.
 CTA: Try free
-RELATED: [16-subscriptions-billing.md](./16-subscriptions-billing.md)</t>
+RELATED: [16-subscriptions-billing.md](./16-subscriptions-billing.md)
+PUBLISHED TITLE: Yearly billing saves. Switch when you're ready.
+SHORT-FORM VARIANT: Yearly billing saves. Switch when you're ready.
+PUBLISHED DESCRIPTION: Toggle between monthly and yearly billing on the plans page - yearly shows the Save label - and apply the change to your subscription. Try free #custosell #subscription #billing #plans #Custosell #SmallBusiness
+TAGS: custosell, subscription, billing, plans, upgrade, invoice, payment, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Monthly or yearly. Your call." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D264" s="5" t="n"/>
@@ -13848,7 +16489,17 @@
   - "Early renew = no gap"
 DEMO DATA: An active plan.
 CTA: Try free
-RELATED: [16-subscriptions-billing.md](./16-subscriptions-billing.md)</t>
+RELATED: [16-subscriptions-billing.md](./16-subscriptions-billing.md)
+PUBLISHED TITLE: Top up months now, skip the rush later.
+SHORT-FORM VARIANT: Top up months now
+PUBLISHED DESCRIPTION: Renew before your billing date - pick how many months to top up and pay early, so access never lapses. Try free #custosell #subscription #billing #plans #Custosell #SmallBusiness
+TAGS: custosell, subscription, billing, plans, upgrade, invoice, payment, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Early renew = no gap" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D265" s="5" t="n"/>
@@ -13896,7 +16547,17 @@
   - "Payments. Changes. Credits."
 DEMO DATA: A few payments and a plan change.
 CTA: Try free
-RELATED: [10-documents.md](./10-documents.md)</t>
+RELATED: [10-documents.md](./10-documents.md)
+PUBLISHED TITLE: Every charge and change, in one timeline.
+SHORT-FORM VARIANT: Every charge and change
+PUBLISHED DESCRIPTION: Open the billing history to see every payment, plan change, and credit applied - newest first - with status badges and references. Try free #custosell #subscription #billing #plans #Custosell #SmallBusiness
+TAGS: custosell, subscription, billing, plans, upgrade, invoice, payment, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Payments. Changes. Credits." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D266" s="5" t="n"/>
@@ -13943,7 +16604,17 @@
   - "Download. Email. Done."
 DEMO DATA: At least one completed payment.
 CTA: Try free
-RELATED: [10-documents.md](./10-documents.md)</t>
+RELATED: [10-documents.md](./10-documents.md)
+PUBLISHED TITLE: Receipt PDF, one tap away.
+SHORT-FORM VARIANT: Receipt PDF
+PUBLISHED DESCRIPTION: Download any payment's receipt as a PDF or send it to your email - useful for records, refunds, and your accountant. Try free #custosell #subscription #billing #plans #Custosell #SmallBusiness
+TAGS: custosell, subscription, billing, plans, upgrade, invoice, payment, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Download. Email. Done." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D267" s="5" t="n"/>
@@ -14047,7 +16718,17 @@
 payment_action. History item types = payment | change | credit with statuses
 applied/pending/cancelled/failed/refunded/completed/successful. Payment
 currency: UGX/KES/TZS via PesaPal, otherwise USD. Billing history lives on the
-profile (auth store) and refreshes after confirmed payments.</t>
+profile (auth store) and refreshes after confirmed payments.
+PUBLISHED TITLE: Paid but still pending? Sync it.
+SHORT-FORM VARIANT: Paid but still pending? Sync it.
+PUBLISHED DESCRIPTION: When a payment shows pending, tap Sync payment to re-check with the provider and confirm the real status - so your subscription updates immediately. Try free #custosell #subscription #billing #plans #Custosell #SmallBusiness
+TAGS: custosell, subscription, billing, plans, upgrade, invoice, payment, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Pending -&gt; Applied" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D268" s="5" t="n"/>
@@ -14102,7 +16783,17 @@
 least one referred business.
 CTA: Try free + subscribe
 RELATED: [16-subscriptions-billing.md](./16-subscriptions-billing.md) ·
-[20-referrals-credits.md](./20-referrals-credits.md)</t>
+[20-referrals-credits.md](./20-referrals-credits.md)
+PUBLISHED TITLE: Got a referral code? Start earning rewards in minutes.
+SHORT-FORM VARIANT: Got a referral code? Start earning rewards
+PUBLISHED DESCRIPTION: Generate your Custosell referral code, then share it as a link or QR code. When a new business signs up with your code and subscribes, you earn a reward on their plan. One code, unlimited referrals. Try free + subscribe #custosell #referrals #credits #rewards #Custosell #SmallBusiness
+TAGS: custosell, referrals, credits, rewards, sales reps, commission, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Refer. Earn. Grow." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D269" s="5" t="n"/>
@@ -14152,7 +16843,17 @@
   - "Enter a referral code to get a discount on your subscription."
 DEMO DATA: A valid active referral code to enter.
 CTA: Try free
-RELATED: [16-subscriptions-billing.md](./16-subscriptions-billing.md)</t>
+RELATED: [16-subscriptions-billing.md](./16-subscriptions-billing.md)
+PUBLISHED TITLE: Got a friend on Custosell? Use their code and save.
+SHORT-FORM VARIANT: Got a friend on Custosell? Use their code and save.
+PUBLISHED DESCRIPTION: Enter a referral code right after creating your account to get a discount on your subscription. The code is validated live, applied to your plan, then you continue straight to onboarding. Try free #custosell #referrals #credits #rewards #Custosell #SmallBusiness
+TAGS: custosell, referrals, credits, rewards, sales reps, commission, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Have a referral code?" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D270" s="5" t="n"/>
@@ -14204,7 +16905,17 @@
 DEMO DATA: A business with several referred businesses in different
 statuses (pending, active, rewarded) and at least one recorded payout.
 CTA: Try free + subscribe
-RELATED: [16-subscriptions-billing.md](./16-subscriptions-billing.md)</t>
+RELATED: [16-subscriptions-billing.md](./16-subscriptions-billing.md)
+PUBLISHED TITLE: See exactly what your referrals have earned you.
+SHORT-FORM VARIANT: See exactly what your referrals have earned you.
+PUBLISHED DESCRIPTION: Open your Referral Dashboard to see total referrals, amount earned, amount paid, and your current balance. Review every referred business with its status and reward, then check your payout history. Try free + subscribe #custosell #referrals #credits #rewards #Custosell #SmallBusiness
+TAGS: custosell, referrals, credits, rewards, sales reps, commission, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Referrals. Earned. Paid. Balance." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D271" s="5" t="n"/>
@@ -14255,7 +16966,17 @@
 DEMO DATA: A business without saved payment info (to show the add
 state), then with both mobile money and bank details.
 CTA: Try free
-RELATED: [20-referrals-credits.md](./20-referrals-credits.md)</t>
+RELATED: [20-referrals-credits.md](./20-referrals-credits.md)
+PUBLISHED TITLE: Where do referral rewards get paid? You decide.
+SHORT-FORM VARIANT: Where do referral rewards get paid? You decide.
+PUBLISHED DESCRIPTION: Add where your referral rewards should be paid - mobile money or bank transfer to any bank worldwide. The Payment Information section on your Referral Dashboard keeps those details ready for every payout. Try free #custosell #referrals #credits #rewards #Custosell #SmallBusiness
+TAGS: custosell, referrals, credits, rewards, sales reps, commission, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Mobile money or bank transfer - worldwide." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D272" s="5" t="n"/>
@@ -14308,7 +17029,17 @@
 DEMO DATA: A business flagged as a sales rep with commission rate and
 type set, plus commission amounts in earnings.
 CTA: Try free
-RELATED: [20-referrals-credits.md](./20-referrals-credits.md)</t>
+RELATED: [20-referrals-credits.md](./20-referrals-credits.md)
+PUBLISHED TITLE: A sales rep's referrals pay commissions - tracked right here.
+SHORT-FORM VARIANT: A sales rep's referrals pay commissions - tracked
+PUBLISHED DESCRIPTION: Businesses enrolled as sales reps see a Sales Rep badge with their commission rate on the Referral Dashboard. Their referral rewards and commissions are combined into one earnings view, and payouts appear in the same history. Try free #custosell #referrals #credits #rewards #Custosell #SmallBusiness
+TAGS: custosell, referrals, credits, rewards, sales reps, commission, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Sales Rep · {rate}%" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D273" s="5" t="n"/>
@@ -14392,7 +17123,17 @@
 **Platform admin (not end-user):** `/platform/sales-reps` - manage sales reps
 (add/edit with commission rate + type + referee discount + active toggle,
 remove blocked while unpaid commission remains, CSV import from template, record
-payouts now or scheduled with method/notes/attachments).</t>
+payouts now or scheduled with method/notes/attachments).
+PUBLISHED TITLE: How Custosell referrals work - the simple version.
+SHORT-FORM VARIANT: How Custosell referrals work
+PUBLISHED DESCRIPTION: Understand the Custosell referral program in plain language: how rewards are calculated, whether there are limits, when payouts happen, and what is not allowed. One referral code per referred business, rewards based on the plan actually paid. Try free #custosell #referrals #credits #rewards #Custosell #SmallBusiness
+TAGS: custosell, referrals, credits, rewards, sales reps, commission, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Rewards on what's actually paid." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D274" s="5" t="n"/>
@@ -14439,7 +17180,17 @@
   - "One inbox"
 DEMO DATA: A few unread notifications.
 CTA: Try free
-RELATED: [19-notifications-webpush.md](./19-notifications-webpush.md)</t>
+RELATED: [19-notifications-webpush.md](./19-notifications-webpush.md)
+PUBLISHED TITLE: Team updates and pipeline news, all in one inbox.
+SHORT-FORM VARIANT: Team updates and pipeline news
+PUBLISHED DESCRIPTION: Open your notifications on Custosell to see updates from the Custosell team and activity from your pipeline - boards, comments, reminders - with unread messages flagged and marked read as you open them. Try free #custosell #notifications #webpush #alerts #Custosell #SmallBusiness
+TAGS: custosell, notifications, web push, alerts, inbox, orders, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "One inbox" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D275" s="5" t="n"/>
@@ -14485,7 +17236,17 @@
   - "Tidy inbox"
 DEMO DATA: Multiple notifications, some read.
 CTA: Try free
-RELATED: [19-notifications-webpush.md](./19-notifications-webpush.md)</t>
+RELATED: [19-notifications-webpush.md](./19-notifications-webpush.md)
+PUBLISHED TITLE: Mark read, delete, done.
+SHORT-FORM VARIANT: Mark read
+PUBLISHED DESCRIPTION: Manage your notifications on Custosell - mark all as read, delete one message, or clear your whole inbox in a couple of taps. Try free #custosell #notifications #webpush #alerts #Custosell #SmallBusiness
+TAGS: custosell, notifications, web push, alerts, inbox, orders, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Tidy inbox" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D276" s="5" t="n"/>
@@ -14532,7 +17293,17 @@
   - "Alerts on"
 DEMO DATA: A browser where notifications are supported.
 CTA: Try free
-RELATED: [19-notifications-webpush.md](./19-notifications-webpush.md)</t>
+RELATED: [19-notifications-webpush.md](./19-notifications-webpush.md)
+PUBLISHED TITLE: Alerts even when the app is closed.
+SHORT-FORM VARIANT: Alerts even when the app is closed.
+PUBLISHED DESCRIPTION: Turn on desktop notifications on Custosell so new orders, sales, and account updates arrive as system alerts - even when you're not looking at the app. Try free #custosell #notifications #webpush #alerts #Custosell #SmallBusiness
+TAGS: custosell, notifications, web push, alerts, inbox, orders, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Alerts on" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D277" s="5" t="n"/>
@@ -14608,7 +17379,17 @@
 message auto-marks it read; unread bubbles show on the bell. Web Push is
 browser-only (hidden in Electron) and delivers new orders, sales, and account
 updates as system notifications even while the app is closed. The order sound
-and big-order threshold are device-local preferences for business accounts.</t>
+and big-order threshold are device-local preferences for business accounts.
+PUBLISHED TITLE: A chime when the order comes in.
+SHORT-FORM VARIANT: A chime when the order comes in.
+PUBLISHED DESCRIPTION: Set the order sound on Custosell so your device chimes when a new open order arrives - and set a big-order threshold so large orders get an urgent chime and a highlighted alert. Try free #custosell #notifications #webpush #alerts #Custosell #SmallBusiness
+TAGS: custosell, notifications, web push, alerts, inbox, orders, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Chime on order" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D278" s="5" t="n"/>
@@ -14655,7 +17436,17 @@
   - "Jot. Saved."
 DEMO DATA: A business with a few notes.
 CTA: Try free
-RELATED: [18-quick-notes.md](./18-quick-notes.md)</t>
+RELATED: [18-quick-notes.md](./18-quick-notes.md)
+PUBLISHED TITLE: A note in 3 seconds - and it's never lost.
+SHORT-FORM VARIANT: A note in 3 seconds
+PUBLISHED DESCRIPTION: Use quick notes on Custosell to capture reminders, customer preferences, and ideas right where your business lives - with a title, body, color, and tag, all saved instantly even when you're offline. Try free #custosell #quicknotes #notes #memo #Custosell #SmallBusiness
+TAGS: custosell, quick notes, notes, memo, pin, share, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Jot. Saved." over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D279" s="5" t="n"/>
@@ -14701,7 +17492,17 @@
   - "Find anything"
 DEMO DATA: Several notes with varied content and tags.
 CTA: Try free
-RELATED: [18-quick-notes.md](./18-quick-notes.md)</t>
+RELATED: [18-quick-notes.md](./18-quick-notes.md)
+PUBLISHED TITLE: That note about the supplier? Found in seconds.
+SHORT-FORM VARIANT: That note about the supplier? Found
+PUBLISHED DESCRIPTION: Search your quick notes by title or body and filter them by tag on Custosell - so every detail you write down is easy to find again. Try free #custosell #quicknotes #notes #memo #Custosell #SmallBusiness
+TAGS: custosell, quick notes, notes, memo, pin, share, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Find anything" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D280" s="5" t="n"/>
@@ -14747,7 +17548,17 @@
   - "Pin it up"
 DEMO DATA: A handful of notes on a board.
 CTA: Try free
-RELATED: [18-quick-notes.md](./18-quick-notes.md)</t>
+RELATED: [18-quick-notes.md](./18-quick-notes.md)
+PUBLISHED TITLE: Pin it, drag it, never lose it.
+SHORT-FORM VARIANT: Pin it
+PUBLISHED DESCRIPTION: Pin the quick notes that matter on Custosell so they always sit at the top of your board, and drag notes into the order you want. Try free #custosell #quicknotes #notes #memo #Custosell #SmallBusiness
+TAGS: custosell, quick notes, notes, memo, pin, share, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Pin it up" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D281" s="5" t="n"/>
@@ -14794,7 +17605,17 @@
   - "One note, whole team"
 DEMO DATA: A business account with staff.
 CTA: Try free
-RELATED: [18-quick-notes.md](./18-quick-notes.md)</t>
+RELATED: [18-quick-notes.md](./18-quick-notes.md)
+PUBLISHED TITLE: One note, your whole team sees it.
+SHORT-FORM VARIANT: One note
+PUBLISHED DESCRIPTION: Share quick notes with everyone in your organization on Custosell - handovers, daily reminders, and team ideas show up for the whole team with the author's name attached. Try free #custosell #quicknotes #notes #memo #Custosell #SmallBusiness
+TAGS: custosell, quick notes, notes, memo, pin, share, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "One note, whole team" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D282" s="5" t="n"/>
@@ -14862,7 +17683,17 @@
 board; tag rename/remove are the only tag endpoints. Offline-first: creates,
 updates, and deletes complete locally and sync later (dedupe by `client_uuid`,
 pending-sync badges on notes); `is_shared` notes show a Shared badge plus the
-author's name and are visible to the whole organization.</t>
+author's name and are visible to the whole organization.
+PUBLISHED TITLE: Your notes, your style.
+SHORT-FORM VARIANT: Your notes
+PUBLISHED DESCRIPTION: Change the look of your quick notes board on Custosell - pick a background, use full-screen mode to hide navigation, and color-code notes the way you like. Try free #custosell #quicknotes #notes #memo #Custosell #SmallBusiness
+TAGS: custosell, quick notes, notes, memo, pin, share, how to, tutorial, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Your space" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D283" s="5" t="n"/>
@@ -14911,7 +17742,17 @@
   - "Watch"
 DEMO DATA: Published tutorials across at least two categories.
 CTA: Try free + subscribe
-RELATED: [22-guide.md](./22-guide.md)</t>
+RELATED: [22-guide.md](./22-guide.md)
+PUBLISHED TITLE: Short videos from the Custosell team - search, filter, watch.
+SHORT-FORM VARIANT: Short videos from the Custosell team - search, filter
+PUBLISHED DESCRIPTION: Open the Custosell Guide and browse short video tutorials from the team. Search by keyword and filter by category - Getting started, Sales, Inventory, or General - then watch the one you need. Try free + subscribe #custosell #guide #tutorials #faq #Custosell #SmallBusiness
+TAGS: custosell, guide, tutorials, faq, help, feedback, support, how to, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Tutorials - search &amp; filter" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D284" s="5" t="n"/>
@@ -14961,7 +17802,17 @@
   - "FAQs - browse by topic or search"
 DEMO DATA: Published FAQs in each of the four categories.
 CTA: Try free
-RELATED: [22-guide.md](./22-guide.md)</t>
+RELATED: [22-guide.md](./22-guide.md)
+PUBLISHED TITLE: Billing, offline, security - answered by the team.
+SHORT-FORM VARIANT: Billing, offline, security
+PUBLISHED DESCRIPTION: Browse the Custosell FAQ library grouped by topic - Getting Started &amp; Plans, Personal Accounts, Business Accounts, and Technical &amp; Data. Search questions and answers, then expand the one you need. Try free #custosell #guide #tutorials #faq #Custosell #SmallBusiness
+TAGS: custosell, guide, tutorials, faq, help, feedback, support, how to, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "FAQs - browse by topic or search" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D285" s="5" t="n"/>
@@ -15015,7 +17866,17 @@
 DEMO DATA: A logged-in user; optionally go offline to show the queue.
 CTA: Try free
 RELATED: [21-offline-sync.md](./21-offline-sync.md) ·
-[22-guide.md](./22-guide.md)</t>
+[22-guide.md](./22-guide.md)
+PUBLISHED TITLE: Tell us what to build - even without internet.
+SHORT-FORM VARIANT: Tell us what to build
+PUBLISHED DESCRIPTION: Send general feedback or a feature request straight from Custosell. It is offline-first: if there is no internet, your message is saved on the device and queued to send automatically when you reconnect. Try free #custosell #guide #tutorials #faq #Custosell #SmallBusiness
+TAGS: custosell, guide, tutorials, faq, help, feedback, support, how to, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Send a message" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D286" s="5" t="n"/>
@@ -15064,7 +17925,17 @@
 DEMO DATA: A few submissions in different statuses, one with a team
 reply, and one pending sync.
 CTA: Try free
-RELATED: [22-guide.md](./22-guide.md)</t>
+RELATED: [22-guide.md](./22-guide.md)
+PUBLISHED TITLE: What happened to my feedback? Check its status.
+SHORT-FORM VARIANT: What happened to my feedback? Check its status.
+PUBLISHED DESCRIPTION: See every message you have sent to the Custosell team, its status - Submitted, Acknowledged, In progress, Resolved, or Closed - and any reply from the team. Pending or failed syncs are shown too. Try free #custosell #guide #tutorials #faq #Custosell #SmallBusiness
+TAGS: custosell, guide, tutorials, faq, help, feedback, support, how to, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Submitted · Acknowledged · In progress · Resolved · Closed" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D287" s="5" t="n"/>
@@ -15145,7 +18016,17 @@
 **Platform admin (not end-user):** `/platform/guide/*` - manage tutorials
 (create/edit/publish, thumbnail upload + preview) with
 `platform.guide.manage`, manage FAQs, and triage feedback (status updates,
-staff replies, bulk actions) with `platform.guide.feedback.manage`.</t>
+staff replies, bulk actions) with `platform.guide.feedback.manage`.
+PUBLISHED TITLE: A human, one tap away.
+SHORT-FORM VARIANT: A human
+PUBLISHED DESCRIPTION: Reach the Custosell team when you need a person - support email and phone lines with one-tap copy, plus business hours. Works offline too: the details stay copyable so you can contact the team after you reconnect. Try free #custosell #guide #tutorials #faq #Custosell #SmallBusiness
+TAGS: custosell, guide, tutorials, faq, help, feedback, support, how to, walkthrough, tips
+VIDEO ASSETS:
+  - Thumbnail: bold text "Support email" over a bright screenshot of the action
+  - Screen-record clips: the Screen flow steps, trimmed to the script beats
+  - Captions / subtitles: full on-screen captions exported as a caption file
+  - Brand overlay / watermark: Custosell logo, corner placement
+  - Music: royalty-free background bed, low volume under the voiceover</t>
         </is>
       </c>
       <c r="D288" s="5" t="n"/>

--- a/docs/videos/video_import_file.xlsx
+++ b/docs/videos/video_import_file.xlsx
@@ -1467,43 +1467,6 @@
 RELATED: [01-account-auth-security.md](./01-account-auth-security.md)
 (2FA), [01-account-auth-security.md](./01-account-auth-security.md)
 (change password)
----
-## Technical reference (source of truth)
-**Screens:** `/register` (Account type selector: business / personal /
-shopping), `/login`, `/forgot-password`, `/onboarding/*`, `/your-tools`
-(personal modules), `/discover` (storefront buyer landing), `/account/profile`
-(profile edit), `/account/security` (tabs: Password, Verification, Linked
-Accounts, Activity)
-**User actions (FE hooks):** `useRegister` (personal / shopping via
-`account_type`) · `useRegisterBusiness` (business + onboarding) · `useLogin` ·
-`useLogout` · `useRequestPasswordReset` · `useResetPassword` ·
-`useSendVerificationCode` · `useVerifyCode` · `useToggleTwoFactor` ·
-`useAccountActivity` · `useInitiateProfileChange` / `useConfirmProfileChange`
-(profile, email, photo - code confirmed) · `useLinkedAccounts` ·
-`useInitiateLinkAccount` / `useConfirmLinkAccount` (link - code confirmed) ·
-`useSwitchAccount` · `useSetPrimary` (set default) ·
-`useInitiateUnlinkAccount` / `useConfirmUnlinkAccount` (unlink - code
-confirmed)
-**API endpoints (BE):** `/auth/register` (one endpoint; `account_type` selects
-business / personal / storefront-buyer) · `/businesses/register` (business
-workspace setup) · `/auth/login` · `/auth/logout` · `/auth/forgot-password` ·
-`/auth/reset-password` · `/auth/verify/send` · `/auth/verify` ·
-`/auth/password/initiate` / `/auth/password/confirm` (change password - code
-confirmed) · `/auth/profile/initiate` / `/auth/profile/confirm` (profile/email/
-photo - code confirmed) · `/auth/two-factor` (toggle) · `/auth/activity`
-(feed) · `/linked-accounts` (list) · `/linked-accounts` (initiate link) ·
-`/linked-accounts/confirm` · `/linked-accounts/{id}/switch` ·
-`/linked-accounts/{id}/set-primary` · `/linked-accounts/{id}/unlink` +
-`/linked-accounts/{id}/unlink/confirm`
-**Your Tools hub (FE):** `PersonalModulesPage` (`/your-tools`) - tool card
-grid via `resolveAccessibleNavGroups` + `usePlanAccessibleModules` (cards only
-for accessible groups, ordered by `TOOL_ORDER`, first six visible then Show
-more), descriptions from `toolDescriptions.ts` (`TOOL_DESCRIPTIONS` personal
-vs business voice), locked-tool cards derived from subscription
-`plan_features` + `getAccessibleModules` (business slugs only), status line
-and gating via `hasSubscriptionAccess` + `STATUS_CONFIG` (trial / active /
-past_due / cancelled / suspended / expired + grace period), card targets are
-`MODULE_DEFAULT_ROUTES` / each group's first sub-route.
 PUBLISHED TITLE: See every sign-in, every change - in one feed.
 SHORT-FORM VARIANT: See every sign-in, every change
 PUBLISHED DESCRIPTION: Review your account activity on Custosell - sign-ins, sign-outs, email verification, 2FA events, password changes, and profile updates, each with the device and IP address. Try free + subscribe #custosell #account #signup #Custosell #SmallBusiness
@@ -1513,7 +1476,44 @@
   - Screen-record clips: the Screen flow steps, trimmed to the script beats
   - Captions / subtitles: full on-screen captions exported as a caption file
   - Brand overlay / watermark: Custosell logo, corner placement
-  - Music: royalty-free background bed, low volume under the voiceover</t>
+  - Music: royalty-free background bed, low volume under the voiceover
+  - ---
+  - ## Technical reference (source of truth)
+  - **Screens:** `/register` (Account type selector: business / personal /
+  - shopping), `/login`, `/forgot-password`, `/onboarding/*`, `/your-tools`
+  - (personal modules), `/discover` (storefront buyer landing), `/account/profile`
+  - (profile edit), `/account/security` (tabs: Password, Verification, Linked
+  - Accounts, Activity)
+  - **User actions (FE hooks):** `useRegister` (personal / shopping via
+  - `account_type`) · `useRegisterBusiness` (business + onboarding) · `useLogin` ·
+  - `useLogout` · `useRequestPasswordReset` · `useResetPassword` ·
+  - `useSendVerificationCode` · `useVerifyCode` · `useToggleTwoFactor` ·
+  - `useAccountActivity` · `useInitiateProfileChange` / `useConfirmProfileChange`
+  - (profile, email, photo - code confirmed) · `useLinkedAccounts` ·
+  - `useInitiateLinkAccount` / `useConfirmLinkAccount` (link - code confirmed) ·
+  - `useSwitchAccount` · `useSetPrimary` (set default) ·
+  - `useInitiateUnlinkAccount` / `useConfirmUnlinkAccount` (unlink - code
+  - confirmed)
+  - **API endpoints (BE):** `/auth/register` (one endpoint; `account_type` selects
+  - business / personal / storefront-buyer) · `/businesses/register` (business
+  - workspace setup) · `/auth/login` · `/auth/logout` · `/auth/forgot-password` ·
+  - `/auth/reset-password` · `/auth/verify/send` · `/auth/verify` ·
+  - `/auth/password/initiate` / `/auth/password/confirm` (change password - code
+  - confirmed) · `/auth/profile/initiate` / `/auth/profile/confirm` (profile/email/
+  - photo - code confirmed) · `/auth/two-factor` (toggle) · `/auth/activity`
+  - (feed) · `/linked-accounts` (list) · `/linked-accounts` (initiate link) ·
+  - `/linked-accounts/confirm` · `/linked-accounts/{id}/switch` ·
+  - `/linked-accounts/{id}/set-primary` · `/linked-accounts/{id}/unlink` +
+  - `/linked-accounts/{id}/unlink/confirm`
+  - **Your Tools hub (FE):** `PersonalModulesPage` (`/your-tools`) - tool card
+  - grid via `resolveAccessibleNavGroups` + `usePlanAccessibleModules` (cards only
+  - for accessible groups, ordered by `TOOL_ORDER`, first six visible then Show
+  - more), descriptions from `toolDescriptions.ts` (`TOOL_DESCRIPTIONS` personal
+  - vs business voice), locked-tool cards derived from subscription
+  - `plan_features` + `getAccessibleModules` (business slugs only), status line
+  - and gating via `hasSubscriptionAccess` + `STATUS_CONFIG` (trial / active /
+  - past_due / cancelled / suspended / expired + grace period), card targets are
+  - `MODULE_DEFAULT_ROUTES` / each group's first sub-route.</t>
         </is>
       </c>
       <c r="D17" s="5" t="n"/>
@@ -2129,46 +2129,6 @@
 DEMO DATA: A business owner account.
 CTA: Try free + subscribe
 RELATED: [17-settings.md](./17-settings.md)
----
-## Technical reference (source of truth)
-**Screens:** `/settings/business` [M] (Profile / Location / Payments / Receipts / Social tabs) ·
-`/settings/tax` [M] (tax profile, EFRIS status, VAT summary) ·
-`/settings/staff` [M] (staff list, add/edit, transfer, transfer history) ·
-`/settings/roles` [M] (role CRUD, system roles protected) ·
-`/settings/locations` [M] (branch CRUD, set default) ·
-`/settings/modules` [M, owner] (module tiles + Estimates/HR depth) ·
-`/settings/data-export` (owner-only export) ·
-`/settings/subscription` and `/settings/sales-channels` covered in [16-subscriptions-billing.md](./16-subscriptions-billing.md) and [14-storefront.md](./14-storefront.md).
-**User actions (FE hooks):** `useBusiness` · `useUpdateBusiness` ·
-`useBusinessExport` · `useInitiateBusinessDelete` · `useConfirmBusinessDelete` ·
-`useBusinessSocialLinks` · `useUpsertBusinessSocialLink` ·
-`useDeleteBusinessSocialLink` · `useVatSummary` · `useEfrisStatus` ·
-`useStaff` · `useCreateStaff` · `useUpdateStaff` · `useAttachStaff` ·
-`useDetachStaff` · `lookupStaffEmail` · `useRoles` · `useCreateRole` ·
-`useUpdateRole` · `useDeleteRole` · `useLocations` · `useCreateLocation` ·
-`useUpdateLocation` · `useSetDefaultLocation` · `useDeleteLocation`.
-**API endpoints (BE):** `GET /businesses/mine` · `PUT /businesses/profile`
-(logo upload uses multipart via `POST ...?_method=PUT`) ·
-`GET /businesses/export?format=json|csv|xlsx` ·
-`POST /businesses/account/initiate` (throttle 3/min) ·
-`POST /businesses/account/confirm` (throttle 10/min) ·
-`GET|POST /business-social-links` · `PUT|DELETE /business-social-links/{id}` ·
-`GET /reports/vat-summary?date_from&amp;date_to&amp;format` ·
-`GET /efris/status` · `GET|POST /users` · `PUT /users/{id}` ·
-`GET /users/lookup?email` · `POST /users/attach` · `POST /users/{id}/detach` ·
-`GET|POST /roles` · `PUT|DELETE /roles/{id}` ·
-`GET|POST /locations` · `PUT|DELETE /locations/{id}` ·
-`POST /locations/{id}/default` · `PUT /auth/profile` (owner module access).
-**Middleware:** business + social-link + staff/role/location management routes
-use `auth:sanctum` + `business.active` + `subscription.active` + `module:settings`;
-`business-social-links` additionally requires `business.owner`; EFRIS status and
-VAT summary require `subscription.active` (no settings gate); `GET /locations`
-reads are open to any active business user, only writes need `module:settings`.
-Delete-account confirm logs the user out and redirects to login.
-**Notable behavior:** business settings, staff, and roles updates can complete
-locally and sync when back online (pending-sync badges); export and delete flows
-are owner-only; personal accounts keep only Profile + Location tabs and skip the
-Danger Zone.
 PUBLISHED TITLE: Your app, your workspaces.
 SHORT-FORM VARIANT: Your app
 PUBLISHED DESCRIPTION: Pick which workspaces the business owner sees on Custosell - hide the modules you don't use and go deeper on Estimates or HR with full access toggles, all from one screen. Try free + subscribe #custosell #settings #businessprofile #tax #Custosell #SmallBusiness
@@ -2178,7 +2138,47 @@
   - Screen-record clips: the Screen flow steps, trimmed to the script beats
   - Captions / subtitles: full on-screen captions exported as a caption file
   - Brand overlay / watermark: Custosell logo, corner placement
-  - Music: royalty-free background bed, low volume under the voiceover</t>
+  - Music: royalty-free background bed, low volume under the voiceover
+  - ---
+  - ## Technical reference (source of truth)
+  - **Screens:** `/settings/business` [M] (Profile / Location / Payments / Receipts / Social tabs) ·
+  - `/settings/tax` [M] (tax profile, EFRIS status, VAT summary) ·
+  - `/settings/staff` [M] (staff list, add/edit, transfer, transfer history) ·
+  - `/settings/roles` [M] (role CRUD, system roles protected) ·
+  - `/settings/locations` [M] (branch CRUD, set default) ·
+  - `/settings/modules` [M, owner] (module tiles + Estimates/HR depth) ·
+  - `/settings/data-export` (owner-only export) ·
+  - `/settings/subscription` and `/settings/sales-channels` covered in [16-subscriptions-billing.md](./16-subscriptions-billing.md) and [14-storefront.md](./14-storefront.md).
+  - **User actions (FE hooks):** `useBusiness` · `useUpdateBusiness` ·
+  - `useBusinessExport` · `useInitiateBusinessDelete` · `useConfirmBusinessDelete` ·
+  - `useBusinessSocialLinks` · `useUpsertBusinessSocialLink` ·
+  - `useDeleteBusinessSocialLink` · `useVatSummary` · `useEfrisStatus` ·
+  - `useStaff` · `useCreateStaff` · `useUpdateStaff` · `useAttachStaff` ·
+  - `useDetachStaff` · `lookupStaffEmail` · `useRoles` · `useCreateRole` ·
+  - `useUpdateRole` · `useDeleteRole` · `useLocations` · `useCreateLocation` ·
+  - `useUpdateLocation` · `useSetDefaultLocation` · `useDeleteLocation`.
+  - **API endpoints (BE):** `GET /businesses/mine` · `PUT /businesses/profile`
+  - (logo upload uses multipart via `POST ...?_method=PUT`) ·
+  - `GET /businesses/export?format=json|csv|xlsx` ·
+  - `POST /businesses/account/initiate` (throttle 3/min) ·
+  - `POST /businesses/account/confirm` (throttle 10/min) ·
+  - `GET|POST /business-social-links` · `PUT|DELETE /business-social-links/{id}` ·
+  - `GET /reports/vat-summary?date_from&amp;date_to&amp;format` ·
+  - `GET /efris/status` · `GET|POST /users` · `PUT /users/{id}` ·
+  - `GET /users/lookup?email` · `POST /users/attach` · `POST /users/{id}/detach` ·
+  - `GET|POST /roles` · `PUT|DELETE /roles/{id}` ·
+  - `GET|POST /locations` · `PUT|DELETE /locations/{id}` ·
+  - `POST /locations/{id}/default` · `PUT /auth/profile` (owner module access).
+  - **Middleware:** business + social-link + staff/role/location management routes
+  - use `auth:sanctum` + `business.active` + `subscription.active` + `module:settings`;
+  - `business-social-links` additionally requires `business.owner`; EFRIS status and
+  - VAT summary require `subscription.active` (no settings gate); `GET /locations`
+  - reads are open to any active business user, only writes need `module:settings`.
+  - Delete-account confirm logs the user out and redirects to login.
+  - **Notable behavior:** business settings, staff, and roles updates can complete
+  - locally and sync when back online (pending-sync badges); export and delete flows
+  - are owner-only; personal accounts keep only Profile + Location tabs and skip the
+  - Danger Zone.</t>
         </is>
       </c>
       <c r="D28" s="5" t="n"/>
@@ -2632,8 +2632,8 @@
 DEMO DATA: A product with a barcode.
 CTA: Try free
 RELATED: [03-sales-pos.md](./03-sales-pos.md)
-PUBLISHED TITLE: Find any product in a second.
-SHORT-FORM VARIANT: Find any product
+PUBLISHED TITLE: SKU and barcode find any product in a second.
+SHORT-FORM VARIANT: SKU. Barcode. Found.
 PUBLISHED DESCRIPTION: Add a SKU and barcode to products so you can search and scan them fast at the till and in the catalog. Try free #custosell #inventory #products #categories #Custosell #SmallBusiness
 TAGS: custosell, inventory, products, categories, sku, barcode, stock, low stock, how to, tutorial, walkthrough, tips
 VIDEO ASSETS:
@@ -3152,8 +3152,8 @@
 DEMO DATA: Products at various stock levels including low and out.
 CTA: Try free
 RELATED: [06-marketplace-purchase-orders.md](./06-marketplace-purchase-orders.md)
-PUBLISHED TITLE: Out of stock before you run out of stock.
-SHORT-FORM VARIANT: Out of stock before you run out of stock.
+PUBLISHED TITLE: Spot low stock before you run out.
+SHORT-FORM VARIANT: Spot low stock before it's gone
 PUBLISHED DESCRIPTION: Read your stock level indicator on Custosell - see what's low, what's out, and what needs restocking at a glance. Try free #custosell #inventory #products #categories #Custosell #SmallBusiness
 TAGS: custosell, inventory, products, categories, sku, barcode, stock, low stock, how to, tutorial, walkthrough, tips
 VIDEO ASSETS:
@@ -3617,26 +3617,6 @@
 DEMO DATA: A disconnected device and an existing catalog.
 CTA: Try free
 RELATED: [21-offline-sync.md](./21-offline-sync.md)
----
-## Technical reference (source of truth)
-**Screens:** `/inventory/overview` [M], `/inventory/products` [M],
-`/inventory/categories`, `/inventory/stock`
-**User actions (FE hooks):** `useProducts` · `useProduct` ·
-`useCreateProduct` · `useUpdateProduct` · `useDeleteProduct` ·
-`useBulkUpdateListing` · `useCategories` · `useCreateCategory` ·
-`useUpdateCategory` · `useDeleteCategory` · `useCreateStockMovement` ·
-`useStockMovements` · `useProductStockMovements` · `useLowStockProducts` ·
-`useLocationStock` · `useStockTransfer` · `useInventoryOverview` ·
-`useUpdateSupplyListing` · `useUpdateStorefrontListing` ·
-`useUploadProductImage`
-**API endpoints (BE):** `/products` CRUD · `/products/low-stock` ·
-`/products/stock/{locationId}` · `/products/import-template` ·
-`/products/import` · `/products/export` · `/products/{id}/stock-movements` ·
-`/products/bulk-delete` · `/products/bulk-listing` ·
-`/products/{id}/supply-listing` · `/products/{id}/storefront-listing` ·
-`/products/{id}/image` · `/categories` CRUD · `/stock-movements` CRUD +
-`/stock-movements/bulk-delete` + `/stock-movements/transfer` ·
-`/inventory/overview`
 PUBLISHED TITLE: Keep building your catalog without internet.
 SHORT-FORM VARIANT: Keep building your catalog without internet.
 PUBLISHED DESCRIPTION: Create, edit, and adjust products even when offline - Custosell queues the changes and syncs them when you're back online. Try free #custosell #inventory #products #categories #Custosell #SmallBusiness
@@ -3646,7 +3626,27 @@
   - Screen-record clips: the Screen flow steps, trimmed to the script beats
   - Captions / subtitles: full on-screen captions exported as a caption file
   - Brand overlay / watermark: Custosell logo, corner placement
-  - Music: royalty-free background bed, low volume under the voiceover</t>
+  - Music: royalty-free background bed, low volume under the voiceover
+  - ---
+  - ## Technical reference (source of truth)
+  - **Screens:** `/inventory/overview` [M], `/inventory/products` [M],
+  - `/inventory/categories`, `/inventory/stock`
+  - **User actions (FE hooks):** `useProducts` · `useProduct` ·
+  - `useCreateProduct` · `useUpdateProduct` · `useDeleteProduct` ·
+  - `useBulkUpdateListing` · `useCategories` · `useCreateCategory` ·
+  - `useUpdateCategory` · `useDeleteCategory` · `useCreateStockMovement` ·
+  - `useStockMovements` · `useProductStockMovements` · `useLowStockProducts` ·
+  - `useLocationStock` · `useStockTransfer` · `useInventoryOverview` ·
+  - `useUpdateSupplyListing` · `useUpdateStorefrontListing` ·
+  - `useUploadProductImage`
+  - **API endpoints (BE):** `/products` CRUD · `/products/low-stock` ·
+  - `/products/stock/{locationId}` · `/products/import-template` ·
+  - `/products/import` · `/products/export` · `/products/{id}/stock-movements` ·
+  - `/products/bulk-delete` · `/products/bulk-listing` ·
+  - `/products/{id}/supply-listing` · `/products/{id}/storefront-listing` ·
+  - `/products/{id}/image` · `/categories` CRUD · `/stock-movements` CRUD +
+  - `/stock-movements/bulk-delete` + `/stock-movements/transfer` ·
+  - `/inventory/overview`</t>
         </is>
       </c>
       <c r="D53" s="5" t="n"/>
@@ -5623,32 +5623,6 @@
 DEMO DATA: A synced sale to refund and offline mode enabled.
 CTA: Try free
 RELATED: [21-offline-sync.md](./21-offline-sync.md)
----
-## Technical reference (source of truth)
-**Screens:** `/sales` -&gt; `/sales/new` [M] (CheckoutStepper: Items -&gt; Payment;
-SaleItemsStep: search/scan, cart, tier toggles, line discounts, Hold Order,
-Take Order, Generate Invoice, Manage Orders/Invoices) · `/sales/orders` [M]
-(status tabs Open/Completed/Invoiced/Cancelled, Online filter, search, branch
-filter, Delivery popover, Resume/Update/Rename/Cancel, invoice from sale) ·
-`/sales/history` [M] (search by receipt, branch/status filters, Select All,
-bulk delete, fiscal status, invoice/email/payments row actions, net + refunds
-summary) · `/sales/refunds` [M] (find by receipt, per-item refund quantities,
-refund total + max-refundable + net remaining, bulk delete) ·
-`/sales/my-shift` [M] (shift-scoped receipts, stat cards, shift summary) ·
-`/invoices`, `/invoices/supplier`
-**User actions (FE hooks):** `useCreateSale` (checkout, online or offline) ·
-`useRefund` (item-level refund, offline-aware) · `useRecordSalePayment`
-(collect balance) · `useAssignSaleCustomer` · `useResolveCustomerContact`
-(walk-in customer at checkout) · `useEmailSaleReceipt` (email receipt) ·
-`useSale` / `useDailySales` / `useShiftSales` · `useCreateOrder` /
-`useUpdateOrder` / `useCancelOrder` (hold/draft, offline-aware) ·
-`useOpenOrders` / `useOrders` (polling list) · `useCreateInvoice` /
-`useSendInvoice` / `useRecordPayment` / `useEmailInvoice` / `viewInvoicePdf`
-**API endpoints (BE):** `/sales` CRUD · `/sales/daily` · `/sales/by-shift/{id}`
-· `/sales/batch` (offline sync) · `/sales/bulk-delete` · `/sales/{id}/refund` ·
-`/sales/{id}/payment` · `/sales/{id}/customer` · `/sales/{id}/pdf` ·
-`/sales/{id}/email` · `/orders` (index/store) · `/orders/{id}` (show/update) ·
-`/orders/{id}/cancel` · `/invoices` CRUD + `/send` `/payment` `/email` `/pdf`
 PUBLISHED TITLE: Refund offline? Saved - and synced when you're back.
 SHORT-FORM VARIANT: Refund offline? Saved
 PUBLISHED DESCRIPTION: Process a refund with no internet on Custosell. It saves locally and syncs when you reconnect; sales that haven't synced yet are protected from being refunded early. Try free #custosell #pos #pointofsale #sell #Custosell #SmallBusiness
@@ -5658,7 +5632,33 @@
   - Screen-record clips: the Screen flow steps, trimmed to the script beats
   - Captions / subtitles: full on-screen captions exported as a caption file
   - Brand overlay / watermark: Custosell logo, corner placement
-  - Music: royalty-free background bed, low volume under the voiceover</t>
+  - Music: royalty-free background bed, low volume under the voiceover
+  - ---
+  - ## Technical reference (source of truth)
+  - **Screens:** `/sales` -&gt; `/sales/new` [M] (CheckoutStepper: Items -&gt; Payment;
+  - SaleItemsStep: search/scan, cart, tier toggles, line discounts, Hold Order,
+  - Take Order, Generate Invoice, Manage Orders/Invoices) · `/sales/orders` [M]
+  - (status tabs Open/Completed/Invoiced/Cancelled, Online filter, search, branch
+  - filter, Delivery popover, Resume/Update/Rename/Cancel, invoice from sale) ·
+  - `/sales/history` [M] (search by receipt, branch/status filters, Select All,
+  - bulk delete, fiscal status, invoice/email/payments row actions, net + refunds
+  - summary) · `/sales/refunds` [M] (find by receipt, per-item refund quantities,
+  - refund total + max-refundable + net remaining, bulk delete) ·
+  - `/sales/my-shift` [M] (shift-scoped receipts, stat cards, shift summary) ·
+  - `/invoices`, `/invoices/supplier`
+  - **User actions (FE hooks):** `useCreateSale` (checkout, online or offline) ·
+  - `useRefund` (item-level refund, offline-aware) · `useRecordSalePayment`
+  - (collect balance) · `useAssignSaleCustomer` · `useResolveCustomerContact`
+  - (walk-in customer at checkout) · `useEmailSaleReceipt` (email receipt) ·
+  - `useSale` / `useDailySales` / `useShiftSales` · `useCreateOrder` /
+  - `useUpdateOrder` / `useCancelOrder` (hold/draft, offline-aware) ·
+  - `useOpenOrders` / `useOrders` (polling list) · `useCreateInvoice` /
+  - `useSendInvoice` / `useRecordPayment` / `useEmailInvoice` / `viewInvoicePdf`
+  - **API endpoints (BE):** `/sales` CRUD · `/sales/daily` · `/sales/by-shift/{id}`
+  - · `/sales/batch` (offline sync) · `/sales/bulk-delete` · `/sales/{id}/refund` ·
+  - `/sales/{id}/payment` · `/sales/{id}/customer` · `/sales/{id}/pdf` ·
+  - `/sales/{id}/email` · `/orders` (index/store) · `/orders/{id}` (show/update) ·
+  - `/orders/{id}/cancel` · `/invoices` CRUD + `/send` `/payment` `/email` `/pdf`</t>
         </is>
       </c>
       <c r="D87" s="5" t="n"/>
@@ -6798,27 +6798,6 @@
 CTA: Try free
 RELATED: [02-dashboard-reports.md](./02-dashboard-reports.md)
 (branch card)
----
-## Technical reference (source of truth)
-**Screens:** `/dashboard` [M] (5 KPI cards, 7-Day Net Sales Trend chart, Low
-Stock Alerts, Recent Activity, Branch Performance card, QuickReports download
-panel, VAT today section, Today's Expenses by Category pie)
-**Report catalog (QuickReports panel, 10 types):** Business Summary (P&amp;L
-snapshot) · Daily Sales · Sales Trend · Product Performance · Shift
-Reconciliation · Expenses · VAT Summary · Inventory (snapshot) · Branch
-Performance (on-screen table) · Payment Breakdown. Each supports date presets
-(Today / This week / This month / This year / Custom) and, where applicable,
-Sales Person + Shift filters, plus PDF / XLSX / CSV export formats.
-**User actions (FE hooks):** `useDashboardSummary` (KPIs + trend + low stock +
-recent sales + today VAT) · `useExpenseSummary` (expense pie) ·
-`useBranchPerformance` (branch card + full report) · `useReportDownload`
-(QuickReports download, blob handling) · `useBusinessTaxSettings` (VAT
-section)
-**API endpoints (BE):** `/dashboard/summary` · `/reports/business-summary` ·
-`/reports/daily-sales` · `/reports/sales-trend` · `/reports/product-performance`
-· `/reports/shift-reconciliation` · `/reports/shift-close` ·
-`/reports/expenses` · `/reports/vat-summary` · `/reports/inventory` ·
-`/reports/payment-breakdown` · `/reports/branch-performance`
 PUBLISHED TITLE: Every branch gross, expenses, net, transactions, share.
 SHORT-FORM VARIANT: Every branch: gross, expenses, net, transactions
 PUBLISHED DESCRIPTION: Open the full Branch Performance report on Custosell - per branch gross, expenses, net sales, transactions, and market share - for any period, right on screen. Try free #custosell #dashboard #reports #salesreport #Custosell #SmallBusiness
@@ -6828,7 +6807,28 @@
   - Screen-record clips: the Screen flow steps, trimmed to the script beats
   - Captions / subtitles: full on-screen captions exported as a caption file
   - Brand overlay / watermark: Custosell logo, corner placement
-  - Music: royalty-free background bed, low volume under the voiceover</t>
+  - Music: royalty-free background bed, low volume under the voiceover
+  - ---
+  - ## Technical reference (source of truth)
+  - **Screens:** `/dashboard` [M] (5 KPI cards, 7-Day Net Sales Trend chart, Low
+  - Stock Alerts, Recent Activity, Branch Performance card, QuickReports download
+  - panel, VAT today section, Today's Expenses by Category pie)
+  - **Report catalog (QuickReports panel, 10 types):** Business Summary (P&amp;L
+  - snapshot) · Daily Sales · Sales Trend · Product Performance · Shift
+  - Reconciliation · Expenses · VAT Summary · Inventory (snapshot) · Branch
+  - Performance (on-screen table) · Payment Breakdown. Each supports date presets
+  - (Today / This week / This month / This year / Custom) and, where applicable,
+  - Sales Person + Shift filters, plus PDF / XLSX / CSV export formats.
+  - **User actions (FE hooks):** `useDashboardSummary` (KPIs + trend + low stock +
+  - recent sales + today VAT) · `useExpenseSummary` (expense pie) ·
+  - `useBranchPerformance` (branch card + full report) · `useReportDownload`
+  - (QuickReports download, blob handling) · `useBusinessTaxSettings` (VAT
+  - section)
+  - **API endpoints (BE):** `/dashboard/summary` · `/reports/business-summary` ·
+  - `/reports/daily-sales` · `/reports/sales-trend` · `/reports/product-performance`
+  - · `/reports/shift-reconciliation` · `/reports/shift-close` ·
+  - `/reports/expenses` · `/reports/vat-summary` · `/reports/inventory` ·
+  - `/reports/payment-breakdown` · `/reports/branch-performance`</t>
         </is>
       </c>
       <c r="D107" s="5" t="n"/>
@@ -7168,7 +7168,7 @@
 ON-SCREEN TEXT / CAPTIONS:
   - "One page, whole shift"
   - "Print or PDF"
-DEMO DATA: An open shift with sales, refunds, expenses, and VAT.
+DEMO DATA: A closed shift with sales, refunds, expenses, and VAT.
 CTA: Try free
 RELATED: [04-shifts.md](./04-shifts.md) (close your shift),
 [02-dashboard-reports.md](./02-dashboard-reports.md) (shift report)
@@ -7406,26 +7406,6 @@
 CTA: Try free
 RELATED: [21-offline-sync.md](./21-offline-sync.md),
 [03-sales-pos.md](./03-sales-pos.md) (sell offline)
----
-## Technical reference (source of truth)
-**Screens:** `/sales/my-shift` [M] (Start Shift, stat cards, Shift Summary,
-Shift Progress chart, Shift Receipts, Shift Expenses, Past Shift Net Sales
-chart, Shift History table, Shift Report preview, Balance Shift, Record
-Expense, End Shift) · `/sales/history` (per-shift sales via filters) ·
-`/sales/refunds` (per shift)
-**User actions (FE hooks):** `useActiveShift` / `useShifts` / `useShiftSales`
-(/sales/by-shift) / `useShiftPayments` (/shifts/{id}/payments) /
-`useShiftExpenses` (/expenses?shift_id=) · `useClockIn` (start shift) ·
-`useClockOut` (end shift + totals: total_sales, total_cash,
-total_mobile_money, total_card, counted_cash) · `useUpdateShiftOpeningBalance`
-(opening_balance) · `useUpdateShiftBalance` (opening_balance + counted_cash) ·
-`useEndShiftAction` (totals math + logout) · `buildShiftCloseReportData` /
-`canDownloadShiftClosePdf` / `downloadShiftClosePdf` (report + PDF)
-**API endpoints (BE):** `/shifts` CRUD (POST = clock in, PUT = opening balance
-/ counted cash / clock out + close) · `/shifts/active` (current shift) ·
-`/shifts/{id}/payments` (shift payments) · `/sales/by-shift/{id}` (shift
-sales) · `/expenses?shift_id={id}` (shift expenses) · `/sales/daily` (day
-rollup per shift)
 PUBLISHED TITLE: Clock in, sell, and close - even with no internet.
 SHORT-FORM VARIANT: Clock in, sell, and close
 PUBLISHED DESCRIPTION: Open, run, and close a shift with no internet on Custosell. Shift changes save locally and sync when you reconnect - the drawer stays accountable the whole time. Try free #custosell #shift #openingbalance #cashdrawer #Custosell #SmallBusiness
@@ -7435,7 +7415,27 @@
   - Screen-record clips: the Screen flow steps, trimmed to the script beats
   - Captions / subtitles: full on-screen captions exported as a caption file
   - Brand overlay / watermark: Custosell logo, corner placement
-  - Music: royalty-free background bed, low volume under the voiceover</t>
+  - Music: royalty-free background bed, low volume under the voiceover
+  - ---
+  - ## Technical reference (source of truth)
+  - **Screens:** `/sales/my-shift` [M] (Start Shift, stat cards, Shift Summary,
+  - Shift Progress chart, Shift Receipts, Shift Expenses, Past Shift Net Sales
+  - chart, Shift History table, Shift Report preview, Balance Shift, Record
+  - Expense, End Shift) · `/sales/history` (per-shift sales via filters) ·
+  - `/sales/refunds` (per shift)
+  - **User actions (FE hooks):** `useActiveShift` / `useShifts` / `useShiftSales`
+  - (/sales/by-shift) / `useShiftPayments` (/shifts/{id}/payments) /
+  - `useShiftExpenses` (/expenses?shift_id=) · `useClockIn` (start shift) ·
+  - `useClockOut` (end shift + totals: total_sales, total_cash,
+  - total_mobile_money, total_card, counted_cash) · `useUpdateShiftOpeningBalance`
+  - (opening_balance) · `useUpdateShiftBalance` (opening_balance + counted_cash) ·
+  - `useEndShiftAction` (totals math + logout) · `buildShiftCloseReportData` /
+  - `canDownloadShiftClosePdf` / `downloadShiftClosePdf` (report + PDF)
+  - **API endpoints (BE):** `/shifts` CRUD (POST = clock in, PUT = opening balance
+  - / counted cash / clock out + close) · `/shifts/active` (current shift) ·
+  - `/shifts/{id}/payments` (shift payments) · `/sales/by-shift/{id}` (shift
+  - sales) · `/expenses?shift_id={id}` (shift expenses) · `/sales/daily` (day
+  - rollup per shift)</t>
         </is>
       </c>
       <c r="D117" s="5" t="n"/>
@@ -7686,35 +7686,6 @@
 DEMO DATA: A fresh device state with no account.
 CTA: Try free + subscribe
 RELATED: [01-account-auth-security.md](./01-account-auth-security.md)
----
-## Technical reference (source of truth)
-**Screens:** OfflineBanner (amber, dismissible, "you can keep working") ·
-AuthPendingBanner (amber, "your account is pending sync") · SyncProgressBanner
-(progress bar, phase label, per-item count, ETA, pause/failure/success states)
-· SyncHeaderChip in the navbar (spinner + percent) · pending-payment notices in
-Payment history
-**Sync engine (FE):** `syncCoordinator.runSyncCoordinator()` drains the queue in
-ordered tiers (Account, Foundation, Transactions, Closures, Stock), looping
-until empty or offline · `syncEngine.runSyncPipeline()` orders mutations by
-dependency (shift opens -&gt; categories -&gt; roles -&gt; staff -&gt; orders -&gt; sales -&gt;
-sale payments -&gt; refunds -&gt; shift closes -&gt; other updates -&gt; stock adjustments)
-· `mutationQueue` persists queued mutations to IndexedDB + durable localStorage
-backup, with retry counters, stale-syncing recovery (5 min), and per-business
-scoping · offline sales upload in batches of 25 (`SALES_BATCH_SIZE`) with
-retry/backoff, then fall back to per-sale sync; duplicate and ambiguous
-failures are reconciled · offline-created entities get negative local IDs that
-are remapped to server IDs (`entityIdMapper`) · reads use
-`readWithOfflineStrategy()` (server first, client cache/IndexedDB fallback on
-network error, 404, or pre-auth 401) · offline auth: `completeOfflineRegistration`
-(local account + queued `/businesses/register` with maxRetries 10, pendingAuthSync
-flag) and `completeOfflineLogin` (local session token; offline login after
-registering on-device or one online login)
-**API endpoints (BE):** `sync.php` (auth:sanctum + business.active):
-`POST /sync/push` (categories, products, customers, expenses, invoices, sales,
-sale_items, stock_movements, staff_transfers, quick_notes) · `GET /sync/pull?since=`
-· `GET /sync/full` · `sales.php` (auth:sanctum + business.active +
-subscription.active): `POST /sales/batch` (bulk sales sync) · `POST /sales` per
-sale fallback
 PUBLISHED TITLE: Set up Custosell offline. Sign in online later.
 SHORT-FORM VARIANT: Set up Custosell offline. Sign
 PUBLISHED DESCRIPTION: You can create your Custosell account without internet - the registration is saved on the device and synced to the server when you connect. An amber banner shows your account is pending sync, and offline sign-in keeps working after that. Try free + subscribe #custosell #offline #sync #nointernet #Custosell #SmallBusiness
@@ -7724,7 +7695,36 @@
   - Screen-record clips: the Screen flow steps, trimmed to the script beats
   - Captions / subtitles: full on-screen captions exported as a caption file
   - Brand overlay / watermark: Custosell logo, corner placement
-  - Music: royalty-free background bed, low volume under the voiceover</t>
+  - Music: royalty-free background bed, low volume under the voiceover
+  - ---
+  - ## Technical reference (source of truth)
+  - **Screens:** OfflineBanner (amber, dismissible, "you can keep working") ·
+  - AuthPendingBanner (amber, "your account is pending sync") · SyncProgressBanner
+  - (progress bar, phase label, per-item count, ETA, pause/failure/success states)
+  - · SyncHeaderChip in the navbar (spinner + percent) · pending-payment notices in
+  - Payment history
+  - **Sync engine (FE):** `syncCoordinator.runSyncCoordinator()` drains the queue in
+  - ordered tiers (Account, Foundation, Transactions, Closures, Stock), looping
+  - until empty or offline · `syncEngine.runSyncPipeline()` orders mutations by
+  - dependency (shift opens -&gt; categories -&gt; roles -&gt; staff -&gt; orders -&gt; sales -&gt;
+  - sale payments -&gt; refunds -&gt; shift closes -&gt; other updates -&gt; stock adjustments)
+  - · `mutationQueue` persists queued mutations to IndexedDB + durable localStorage
+  - backup, with retry counters, stale-syncing recovery (5 min), and per-business
+  - scoping · offline sales upload in batches of 25 (`SALES_BATCH_SIZE`) with
+  - retry/backoff, then fall back to per-sale sync; duplicate and ambiguous
+  - failures are reconciled · offline-created entities get negative local IDs that
+  - are remapped to server IDs (`entityIdMapper`) · reads use
+  - `readWithOfflineStrategy()` (server first, client cache/IndexedDB fallback on
+  - network error, 404, or pre-auth 401) · offline auth: `completeOfflineRegistration`
+  - (local account + queued `/businesses/register` with maxRetries 10, pendingAuthSync
+  - flag) and `completeOfflineLogin` (local session token; offline login after
+  - registering on-device or one online login)
+  - **API endpoints (BE):** `sync.php` (auth:sanctum + business.active):
+  - `POST /sync/push` (categories, products, customers, expenses, invoices, sales,
+  - sale_items, stock_movements, staff_transfers, quick_notes) · `GET /sync/pull?since=`
+  - · `GET /sync/full` · `sales.php` (auth:sanctum + business.active +
+  - subscription.active): `POST /sales/batch` (bulk sales sync) · `POST /sales` per
+  - sale fallback</t>
         </is>
       </c>
       <c r="D121" s="5" t="n"/>
@@ -8294,35 +8294,6 @@
 DEMO DATA: A device with connectivity toggled off.
 CTA: Try free
 RELATED: [21-offline-sync.md](./21-offline-sync.md)
----
-## Technical reference (source of truth)
-**Screens:** `/expenses/list` [M] (list, filters, CRUD, attachments) ·
-`/expenses/categories` [M] (category manager with per-category budgets) ·
-`/expenses/overview` [M] (stat cards + charts, period/branch filters) ·
-`/expenses/budgets` [M] (personal budgets, shopping lists, PDF download) ·
-`/expenses/income` [M] (income records, personal accounts only)
-**User actions (FE hooks):** `useExpenses` · `useExpense(id)` ·
-`useExpenseSummary` · `useExpenseCategories` · `useCreateExpense` ·
-`useUpdateExpense` · `useDeleteExpense` · `useCreateExpenseCategory` ·
-`useUpdateExpenseCategory` · `useDeleteExpenseCategory` ·
-`useUploadExpenseAttachment` · `useCreateExpenseAttachmentLink` ·
-`useDeleteExpenseAttachment` · `useBudgetsIndex` · `useBudget(id)` ·
-`useCreateBudget` · `useUpdateBudget` · `useDeleteBudget` ·
-`useBudgetDetail` · `useSyncBudgetLines` · `usePurchaseLine` ·
-`useBudgetAffordability` · `useBudgetAlerts` · `useMoneySummary` ·
-`useIncomeSources` · `useCreateIncome` · `useUpdateIncome` ·
-`useDeleteIncome` · `useUploadIncomeAttachment` ·
-`useCreateIncomeAttachmentLink` · `useDeleteIncomeAttachment` ·
-`useIncomeOverview` · `useBudgets` · `downloadBudgetPdf`
-**API endpoints (BE):** `/expenses` (GET/POST + `/expenses/{id}` GET/PUT/PATCH/
-DELETE) · `/expenses/overview` · `/expenses/summary` · `/expenses/budgets` ·
-`/expenses/export` (CSV/XLSX) · `/expenses/by-shift/{shiftId}` ·
-`/expenses/{id}/attachments` (+ `/attachments/link` + `/expense-attachments/{id}`)
-· `/expense-categories` CRUD · `/income-sources` CRUD (+ `/summary` +
-`/income-sources/{id}/attachments` + `/attachments/link` +
-`/income-source-attachments/{id}`) · `/budgets` CRUD (+ `/budgets/{id}/lines`,
-`/lines/{line}/purchase`, `/affordability`, `/download`) · `/money/summary` ·
-`/money/alerts`
 PUBLISHED TITLE: Record expenses even when the internet is gone.
 SHORT-FORM VARIANT: Record expenses even when the internet is gone.
 PUBLISHED DESCRIPTION: Create and edit expenses offline - Custosell saves them instantly with a Pending sync badge (and pending receipt) and syncs automatically when you're back online. Try free #custosell #expenses #budgets #income #Custosell #SmallBusiness
@@ -8332,7 +8303,36 @@
   - Screen-record clips: the Screen flow steps, trimmed to the script beats
   - Captions / subtitles: full on-screen captions exported as a caption file
   - Brand overlay / watermark: Custosell logo, corner placement
-  - Music: royalty-free background bed, low volume under the voiceover</t>
+  - Music: royalty-free background bed, low volume under the voiceover
+  - ---
+  - ## Technical reference (source of truth)
+  - **Screens:** `/expenses/list` [M] (list, filters, CRUD, attachments) ·
+  - `/expenses/categories` [M] (category manager with per-category budgets) ·
+  - `/expenses/overview` [M] (stat cards + charts, period/branch filters) ·
+  - `/expenses/budgets` [M] (personal budgets, shopping lists, PDF download) ·
+  - `/expenses/income` [M] (income records, personal accounts only)
+  - **User actions (FE hooks):** `useExpenses` · `useExpense(id)` ·
+  - `useExpenseSummary` · `useExpenseCategories` · `useCreateExpense` ·
+  - `useUpdateExpense` · `useDeleteExpense` · `useCreateExpenseCategory` ·
+  - `useUpdateExpenseCategory` · `useDeleteExpenseCategory` ·
+  - `useUploadExpenseAttachment` · `useCreateExpenseAttachmentLink` ·
+  - `useDeleteExpenseAttachment` · `useBudgetsIndex` · `useBudget(id)` ·
+  - `useCreateBudget` · `useUpdateBudget` · `useDeleteBudget` ·
+  - `useBudgetDetail` · `useSyncBudgetLines` · `usePurchaseLine` ·
+  - `useBudgetAffordability` · `useBudgetAlerts` · `useMoneySummary` ·
+  - `useIncomeSources` · `useCreateIncome` · `useUpdateIncome` ·
+  - `useDeleteIncome` · `useUploadIncomeAttachment` ·
+  - `useCreateIncomeAttachmentLink` · `useDeleteIncomeAttachment` ·
+  - `useIncomeOverview` · `useBudgets` · `downloadBudgetPdf`
+  - **API endpoints (BE):** `/expenses` (GET/POST + `/expenses/{id}` GET/PUT/PATCH/
+  - DELETE) · `/expenses/overview` · `/expenses/summary` · `/expenses/budgets` ·
+  - `/expenses/export` (CSV/XLSX) · `/expenses/by-shift/{shiftId}` ·
+  - `/expenses/{id}/attachments` (+ `/attachments/link` + `/expense-attachments/{id}`)
+  - · `/expense-categories` CRUD · `/income-sources` CRUD (+ `/summary` +
+  - `/income-sources/{id}/attachments` + `/attachments/link` +
+  - `/income-source-attachments/{id}`) · `/budgets` CRUD (+ `/budgets/{id}/lines`,
+  - `/lines/{line}/purchase`, `/affordability`, `/download`) · `/money/summary` ·
+  - `/money/alerts`</t>
         </is>
       </c>
       <c r="D131" s="5" t="n"/>
@@ -8724,23 +8724,6 @@
 DEMO DATA: A device with connectivity toggled off.
 CTA: Try free
 RELATED: [21-offline-sync.md](./21-offline-sync.md)
----
-## Technical reference (source of truth)
-**Screens:** `/customers` [M] (list, search, add/edit/delete, purchases),
-`/customers/overview` [M] (stats + charts), `/sales/new` billing column
-(checkout picker)
-**User actions (FE hooks):** `useCustomers` · `useCustomer(id)` ·
-`useCustomerOverview` · `useCustomerPurchases(id)` ·
-`useCreateCustomer` · `useUpdateCustomer` · `useDeleteCustomer` ·
-`useResolveCustomerContact` (find-or-create + merge contact) ·
-`useAssignSaleCustomer` (attach customer to an existing sale)
-**API endpoints (BE):** `/customers` (GET/POST) · `/customers/overview` ·
-`/customers/resolve` (find-or-create by id/email/phone, merges contact) ·
-`/customers/{id}` (GET/PUT/PATCH/DELETE) · `/customers/{id}/purchases` ·
-`/sales/{id}/customer` (assign)
-**Overview segments (BE `CustomerService`):** Active (&lt;30 days) · At risk
-(30-90 days) · Lapsed (&gt;90 days) · Never purchased. Frequency buckets: 1 · 2-3 ·
-4-6 · 7+ purchases.
 PUBLISHED TITLE: Add customers even when the internet is gone.
 SHORT-FORM VARIANT: Add customers even when the internet is gone.
 PUBLISHED DESCRIPTION: Create and edit customers while offline - Custosell saves them instantly with a Pending sync badge and syncs automatically when you're back. Try free #custosell #customers #customerlist #purchasehistory #Custosell #SmallBusiness
@@ -8750,7 +8733,24 @@
   - Screen-record clips: the Screen flow steps, trimmed to the script beats
   - Captions / subtitles: full on-screen captions exported as a caption file
   - Brand overlay / watermark: Custosell logo, corner placement
-  - Music: royalty-free background bed, low volume under the voiceover</t>
+  - Music: royalty-free background bed, low volume under the voiceover
+  - ---
+  - ## Technical reference (source of truth)
+  - **Screens:** `/customers` [M] (list, search, add/edit/delete, purchases),
+  - `/customers/overview` [M] (stats + charts), `/sales/new` billing column
+  - (checkout picker)
+  - **User actions (FE hooks):** `useCustomers` · `useCustomer(id)` ·
+  - `useCustomerOverview` · `useCustomerPurchases(id)` ·
+  - `useCreateCustomer` · `useUpdateCustomer` · `useDeleteCustomer` ·
+  - `useResolveCustomerContact` (find-or-create + merge contact) ·
+  - `useAssignSaleCustomer` (attach customer to an existing sale)
+  - **API endpoints (BE):** `/customers` (GET/POST) · `/customers/overview` ·
+  - `/customers/resolve` (find-or-create by id/email/phone, merges contact) ·
+  - `/customers/{id}` (GET/PUT/PATCH/DELETE) · `/customers/{id}/purchases` ·
+  - `/sales/{id}/customer` (assign)
+  - **Overview segments (BE `CustomerService`):** Active (&lt;30 days) · At risk
+  - (30-90 days) · Lapsed (&gt;90 days) · Never purchased. Frequency buckets: 1 · 2-3 ·
+  - 4-6 · 7+ purchases.</t>
         </is>
       </c>
       <c r="D138" s="5" t="n"/>
@@ -9750,7 +9750,7 @@
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
         <is>
-          <t>MKT-18 List products on your public shop</t>
+          <t>MKT-18 Put your catalog in front of customers</t>
         </is>
       </c>
       <c r="B156" s="5" t="inlineStr">
@@ -9839,26 +9839,6 @@
 DEMO DATA: A device with connectivity toggled off.
 CTA: Try free
 RELATED: [21-offline-sync.md](./21-offline-sync.md)
----
-## Technical reference (source of truth)
-**Screens:** `/inventory/marketplace` [M], `/inventory/purchase-orders` [M],
-`/inventory/incoming-orders` [M]
-**User actions (FE hooks):** `useMarketplaceBusinesses` ·
-`useMarketplaceProducts` · `useMySuppliers` · `useAddSupplier` ·
-`useRemoveSupplier` · `useCreatePurchaseOrder` · `useUpdatePurchaseOrder` ·
-`useSubmitPurchaseOrder` · `useCancelPurchaseOrder` ·
-`useDeletePurchaseOrder` · `useAcceptPurchaseOrder` ·
-`useRejectPurchaseOrder` · `useFulfillPurchaseOrder` ·
-`useReceivePurchaseOrder` · `usePurchaseOrders` ·
-`useIncomingPurchaseOrders` · `usePurchaseOrder` ·
-`useUpdateSupplyListing` · `useUpdateStorefrontListing`
-**API endpoints (BE):** `/marketplace/businesses` ·
-`/marketplace/businesses/{id}/products` · `/marketplace/suppliers`
-(GET/POST) + `/marketplace/suppliers/{sellerBusinessId}` (DELETE) ·
-`/purchase-orders` (GET/POST) + `/purchase-orders/{id}`
-(GET/PUT/DELETE) + `/purchase-orders/{id}/submit|cancel|accept|reject|
-fulfill|receive` · `/purchase-orders/incoming` ·
-`/products/{id}/supply-listing` · `/products/{id}/storefront-listing`
 PUBLISHED TITLE: Know exactly what needs a connection.
 SHORT-FORM VARIANT: Know exactly what needs a connection.
 PUBLISHED DESCRIPTION: Marketplace browsing, ordering, and order management need the internet - see how Custosell tells you clearly and keeps your local work safe. Try free #custosell #marketplace #purchaseorder #suppliers #Custosell #SmallBusiness
@@ -9868,7 +9848,27 @@
   - Screen-record clips: the Screen flow steps, trimmed to the script beats
   - Captions / subtitles: full on-screen captions exported as a caption file
   - Brand overlay / watermark: Custosell logo, corner placement
-  - Music: royalty-free background bed, low volume under the voiceover</t>
+  - Music: royalty-free background bed, low volume under the voiceover
+  - ---
+  - ## Technical reference (source of truth)
+  - **Screens:** `/inventory/marketplace` [M], `/inventory/purchase-orders` [M],
+  - `/inventory/incoming-orders` [M]
+  - **User actions (FE hooks):** `useMarketplaceBusinesses` ·
+  - `useMarketplaceProducts` · `useMySuppliers` · `useAddSupplier` ·
+  - `useRemoveSupplier` · `useCreatePurchaseOrder` · `useUpdatePurchaseOrder` ·
+  - `useSubmitPurchaseOrder` · `useCancelPurchaseOrder` ·
+  - `useDeletePurchaseOrder` · `useAcceptPurchaseOrder` ·
+  - `useRejectPurchaseOrder` · `useFulfillPurchaseOrder` ·
+  - `useReceivePurchaseOrder` · `usePurchaseOrders` ·
+  - `useIncomingPurchaseOrders` · `usePurchaseOrder` ·
+  - `useUpdateSupplyListing` · `useUpdateStorefrontListing`
+  - **API endpoints (BE):** `/marketplace/businesses` ·
+  - `/marketplace/businesses/{id}/products` · `/marketplace/suppliers`
+  - (GET/POST) + `/marketplace/suppliers/{sellerBusinessId}` (DELETE) ·
+  - `/purchase-orders` (GET/POST) + `/purchase-orders/{id}`
+  - (GET/PUT/DELETE) + `/purchase-orders/{id}/submit|cancel|accept|reject|
+  - fulfill|receive` · `/purchase-orders/incoming` ·
+  - `/products/{id}/supply-listing` · `/products/{id}/storefront-listing`</t>
         </is>
       </c>
       <c r="D157" s="5" t="n"/>
@@ -11399,37 +11399,6 @@
 DEMO DATA: A project and a few staff accounts.
 CTA: Try free
 RELATED: [17-settings.md](./17-settings.md)
----
-## Technical reference (source of truth)
-**Screens:** `/estimates` [M] (list + stat cards + New estimate drawer) ·
-`/estimates/{id}` [M] (detail: send/email/approve/reject/convert/PDF/duplicate +
-line items, versions, notes) · `/estimates/templates` [M] (template cards) ·
-`/estimates/insights` [M] (win rate, margin, trends) ·
-`/estimates/projects` [M] (project list with budget vs actual) ·
-`/estimates/projects/{id}` [M] (overview/tasks/timesheets/board/documents/
-allocations) · `/estimates/boards` [M] (estimates-workspace kanban boards -
-"My boards" personal + "Project boards", New personal board drawer)
-**User actions (FE hooks):** `useEstimates` · `useEstimate` ·
-`useCreateEstimate` · `useUpdateEstimate` · `useDeleteEstimate` ·
-`useSendEstimate` (status only) · `useEmailEstimate` (real email) ·
-`useApproveEstimate` · `useRejectEstimate` · `useDuplicateEstimate` ·
-`useEstimateVersions` · `useConvertEstimateToInvoice` ·
-`useConvertEstimateToProject` · `useEstimateAnalytics` · `useEstimateTemplates`
-(+ CRUD) · `useProjects` · `useProject` · `useCreateProject` ·
-`useUpdateProject` · `useDeleteProject` · `useMyProjects` ·
-`useCreateProjectTask`/`useUpdateProjectTask`/`useDeleteProjectTask` ·
-`useCreateTimesheetEntry`/`useDeleteTimesheetEntry` ·
-`useCreateCostAllocation`/`useDeleteCostAllocation` · `useProjectBudgetSummary`
-· `useProjectProfitability` · `useProjectBoard` · `useProjectBoardKanban` ·
-`useProjectMembers`/`useAddProjectMember`/`useUpdateProjectMember`/
-`useRemoveProjectMember` · `viewEstimatePdf`/`downloadEstimatePdf` ·
-`usePipelineBoards` (estimatesWorkspace: true) · `useCreatePipelineBoard`
-(personal boards, workspace=estimates, private by default) ·
-`usePipelineKanban` · `filterBoardsForWorkspace`/`boardBelongsToEstimatesWorkspace`/
-`boardUsesTaskTerminology` (task/card language for project + estimates boards) ·
-`useProjectBoard`/`useProjectBoardKanban` (project board via project id) ·
-`isLimitedEstimatesUser`/`getEstimatesModuleDefaultRoute` (board-only users
-land on `/estimates/boards`)
 PUBLISHED TITLE: Right people, right access, one project.
 SHORT-FORM VARIANT: Right people
 PUBLISHED DESCRIPTION: Invite staff to a project as Viewer, Contributor, or Manager, control who edits and who manages the team, and keep the owner locked in. Try free #custosell #estimates #projects #templates #Custosell #SmallBusiness
@@ -11439,7 +11408,38 @@
   - Screen-record clips: the Screen flow steps, trimmed to the script beats
   - Captions / subtitles: full on-screen captions exported as a caption file
   - Brand overlay / watermark: Custosell logo, corner placement
-  - Music: royalty-free background bed, low volume under the voiceover</t>
+  - Music: royalty-free background bed, low volume under the voiceover
+  - ---
+  - ## Technical reference (source of truth)
+  - **Screens:** `/estimates` [M] (list + stat cards + New estimate drawer) ·
+  - `/estimates/{id}` [M] (detail: send/email/approve/reject/convert/PDF/duplicate +
+  - line items, versions, notes) · `/estimates/templates` [M] (template cards) ·
+  - `/estimates/insights` [M] (win rate, margin, trends) ·
+  - `/estimates/projects` [M] (project list with budget vs actual) ·
+  - `/estimates/projects/{id}` [M] (overview/tasks/timesheets/board/documents/
+  - allocations) · `/estimates/boards` [M] (estimates-workspace kanban boards -
+  - "My boards" personal + "Project boards", New personal board drawer)
+  - **User actions (FE hooks):** `useEstimates` · `useEstimate` ·
+  - `useCreateEstimate` · `useUpdateEstimate` · `useDeleteEstimate` ·
+  - `useSendEstimate` (status only) · `useEmailEstimate` (real email) ·
+  - `useApproveEstimate` · `useRejectEstimate` · `useDuplicateEstimate` ·
+  - `useEstimateVersions` · `useConvertEstimateToInvoice` ·
+  - `useConvertEstimateToProject` · `useEstimateAnalytics` · `useEstimateTemplates`
+  - (+ CRUD) · `useProjects` · `useProject` · `useCreateProject` ·
+  - `useUpdateProject` · `useDeleteProject` · `useMyProjects` ·
+  - `useCreateProjectTask`/`useUpdateProjectTask`/`useDeleteProjectTask` ·
+  - `useCreateTimesheetEntry`/`useDeleteTimesheetEntry` ·
+  - `useCreateCostAllocation`/`useDeleteCostAllocation` · `useProjectBudgetSummary`
+  - · `useProjectProfitability` · `useProjectBoard` · `useProjectBoardKanban` ·
+  - `useProjectMembers`/`useAddProjectMember`/`useUpdateProjectMember`/
+  - `useRemoveProjectMember` · `viewEstimatePdf`/`downloadEstimatePdf` ·
+  - `usePipelineBoards` (estimatesWorkspace: true) · `useCreatePipelineBoard`
+  - (personal boards, workspace=estimates, private by default) ·
+  - `usePipelineKanban` · `filterBoardsForWorkspace`/`boardBelongsToEstimatesWorkspace`/
+  - `boardUsesTaskTerminology` (task/card language for project + estimates boards) ·
+  - `useProjectBoard`/`useProjectBoardKanban` (project board via project id) ·
+  - `isLimitedEstimatesUser`/`getEstimatesModuleDefaultRoute` (board-only users
+  - land on `/estimates/boards`)</t>
         </is>
       </c>
       <c r="D183" s="5" t="n"/>
@@ -11551,7 +11551,7 @@
 RELATED: [02-dashboard-reports.md](./02-dashboard-reports.md)
 PUBLISHED TITLE: Chart of accounts, explained for shop owners.
 SHORT-FORM VARIANT: Chart of accounts
-PUBLISHED DESCRIPTION: A plain-English tour of the chart of accounts on Custosell - assets, liabilities, equity, revenue, expenses - in flat view or as a parent- child tree, and how each account feeds your reports. Try free + subscribe #custosell #accounting #bookkeeping #journal #Custosell #SmallBusiness
+PUBLISHED DESCRIPTION: A plain-English tour of the chart of accounts on Custosell - assets, liabilities, equity, revenue, expenses - in flat view or as a parent-child tree, and how each account feeds your reports. Try free + subscribe #custosell #accounting #bookkeeping #journal #Custosell #SmallBusiness
 TAGS: custosell, accounting, bookkeeping, journal, trial balance, income statement, balance sheet, vat, how to, tutorial, walkthrough, tips
 VIDEO ASSETS:
   - Thumbnail: bold text "Assets. Revenue. Expenses. It's that simple." over a bright screenshot of the action
@@ -12196,38 +12196,6 @@
 DEMO DATA: A small Excel file with accounts or entries.
 CTA: Try free
 RELATED: [17-settings.md](./17-settings.md)
----
-## Technical reference (source of truth)
-**Screens:** `/accounting/statements` [M] (5 report cards + PDF export) ·
-`/accounting/chart-of-accounts` [M] (flat/tree, add, import/export) ·
-`/accounting/journal-entries` [M] (list, new entry, post/reverse, import/export)
-· `/accounting/trial-balance` [M] · `/accounting/income-statement` [M] ·
-`/accounting/balance-sheet` [M] · `/accounting/ratios` [M] (trends + download)
-· `/accounting/periods` [M] (close/reopen) · `/accounting/fixed-assets` [M]
-(register, run depreciation, schedule) · `/accounting/settings` [M] (seed COA,
-inventory reconciliation)
-**User actions (FE hooks):** `useChartOfAccounts` · `useChartOfAccountsTree` ·
-`useCreateChartOfAccount` · `useUpdateChartOfAccount` ·
-`useDeleteChartOfAccount` · `useAccountingPeriods` · `useCurrentPeriod` ·
-`useClosePeriod` · `useJournalEntries` · `useJournalEntry` ·
-`useCreateJournalEntry` · `usePostJournalEntry` · `useReverseJournalEntry` ·
-`useDeleteJournalEntry` · `useTrialBalance` · `useIncomeStatement` ·
-`useBalanceSheet` · `useCashFlow` · `useEquity` · `useRatios` ·
-`useRatioTrends` · `useFixedAssets` · `useFixedAsset` · `useCreateFixedAsset` ·
-`useUpdateFixedAsset` · `useRunDepreciation` · `useFixedAssetSchedule` ·
-`useInventoryReconciliation` · `usePostOpeningInventory`
-**API endpoints (BE):** `/chart-of-accounts` CRUD + `/tree` + `/import-template`
-+ `/import` + `/export` · `/accounting-periods` + `/current` + `/{id}/close` +
-`/{id}/reopen` · `/journal-entries` CRUD + `/import-template` + `/import` +
-`/export` + `/{id}/lines` + `/{id}/post` + `/{id}/reverse` ·
-`/general-ledger` + `/trial-balance` + `/profit-loss` + `/balance-sheet` +
-`/cash-flow` + `/equity` · `/fixed-assets` CRUD + `/run-depreciation` +
-`/{id}/schedule` · `/ratios` + `/ratios/trends` · `/inventory/reconciliation` +
-`/inventory/opening-balance` · `/accounting/export/{type}` (PDF/XLSX)
-**Auto-journaling events (BE):** `SaleCreatedForAccounting` ·
-`SaleRefundedForAccounting` · `ExpenseCreatedForAccounting` ·
-`InvoiceSentForAccounting` · `InvoicePaidForAccounting` ·
-`PaymentRecordedForAccounting` · `PayoutCompletedForAccounting`
 PUBLISHED TITLE: Move your books in and out - cleanly.
 SHORT-FORM VARIANT: Move your books in and out
 PUBLISHED DESCRIPTION: Download a template, import your chart of accounts or journal entries from Excel/CSV, and export current data - with per-row validation so you always know what landed. Try free #custosell #accounting #bookkeeping #journal #Custosell #SmallBusiness
@@ -12237,7 +12205,39 @@
   - Screen-record clips: the Screen flow steps, trimmed to the script beats
   - Captions / subtitles: full on-screen captions exported as a caption file
   - Brand overlay / watermark: Custosell logo, corner placement
-  - Music: royalty-free background bed, low volume under the voiceover</t>
+  - Music: royalty-free background bed, low volume under the voiceover
+  - ---
+  - ## Technical reference (source of truth)
+  - **Screens:** `/accounting/statements` [M] (5 report cards + PDF export) ·
+  - `/accounting/chart-of-accounts` [M] (flat/tree, add, import/export) ·
+  - `/accounting/journal-entries` [M] (list, new entry, post/reverse, import/export)
+  - · `/accounting/trial-balance` [M] · `/accounting/income-statement` [M] ·
+  - `/accounting/balance-sheet` [M] · `/accounting/ratios` [M] (trends + download)
+  - · `/accounting/periods` [M] (close/reopen) · `/accounting/fixed-assets` [M]
+  - (register, run depreciation, schedule) · `/accounting/settings` [M] (seed COA,
+  - inventory reconciliation)
+  - **User actions (FE hooks):** `useChartOfAccounts` · `useChartOfAccountsTree` ·
+  - `useCreateChartOfAccount` · `useUpdateChartOfAccount` ·
+  - `useDeleteChartOfAccount` · `useAccountingPeriods` · `useCurrentPeriod` ·
+  - `useClosePeriod` · `useJournalEntries` · `useJournalEntry` ·
+  - `useCreateJournalEntry` · `usePostJournalEntry` · `useReverseJournalEntry` ·
+  - `useDeleteJournalEntry` · `useTrialBalance` · `useIncomeStatement` ·
+  - `useBalanceSheet` · `useCashFlow` · `useEquity` · `useRatios` ·
+  - `useRatioTrends` · `useFixedAssets` · `useFixedAsset` · `useCreateFixedAsset` ·
+  - `useUpdateFixedAsset` · `useRunDepreciation` · `useFixedAssetSchedule` ·
+  - `useInventoryReconciliation` · `usePostOpeningInventory`
+  - **API endpoints (BE):** `/chart-of-accounts` CRUD + `/tree` + `/import-template`
+  - + `/import` + `/export` · `/accounting-periods` + `/current` + `/{id}/close` +
+  - `/{id}/reopen` · `/journal-entries` CRUD + `/import-template` + `/import` +
+  - `/export` + `/{id}/lines` + `/{id}/post` + `/{id}/reverse` ·
+  - `/general-ledger` + `/trial-balance` + `/profit-loss` + `/balance-sheet` +
+  - `/cash-flow` + `/equity` · `/fixed-assets` CRUD + `/run-depreciation` +
+  - `/{id}/schedule` · `/ratios` + `/ratios/trends` · `/inventory/reconciliation` +
+  - `/inventory/opening-balance` · `/accounting/export/{type}` (PDF/XLSX)
+  - **Auto-journaling events (BE):** `SaleCreatedForAccounting` ·
+  - `SaleRefundedForAccounting` · `ExpenseCreatedForAccounting` ·
+  - `InvoiceSentForAccounting` · `InvoicePaidForAccounting` ·
+  - `PaymentRecordedForAccounting` · `PayoutCompletedForAccounting`</t>
         </is>
       </c>
       <c r="D196" s="5" t="n"/>
@@ -12804,33 +12804,6 @@
 DEMO DATA: A few staff members actively filing documents.
 CTA: Try free
 RELATED: [17-settings.md](./17-settings.md)
----
-## Technical reference (source of truth)
-**Screens:** `/documents` [M] (cabinet cards + search + New cabinet) ·
-`/documents/cabinets/{id}` [M] (explorer: folder tree, upload/link/import,
-access, preview/edit, email, export, activity)
-**User actions (FE hooks):** `useDocumentCabinets` · `useDocumentCabinet` ·
-`useCreateDocumentCabinet` · `useUpdateDocumentCabinet` ·
-`useDeleteDocumentCabinet` · `useDocumentFolderTree` ·
-`useDocumentFolderChildren` · `useDocumentFolderContents` ·
-`useCreateDocumentFolder` · `useUpdateDocumentFolder` ·
-`useDeleteDocumentFolder` · `useDocuments` (infinite list) · `useDocument` ·
-`useUploadDocument` · `useCreateDocumentLink` · `useUpdateDocument` ·
-`useDeleteDocument` · `useDocumentContent` · `useUpdateDocumentContent` ·
-`useRecordDocumentView` · `useRecordDocumentDownload` ·
-`useDocumentAccessibleMembers` · `useDocumentActivity` · `useDocumentTags` ·
-`useDocumentsVaultAppearance` · `useUpdateDocumentsVaultAppearance`
-**API endpoints (BE):** `/documents` GET + `/documents/upload` +
-`/documents/link` + `/documents/{id}` GET/PATCH/DELETE + `/{id}/view` +
-`/{id}/download` + `/{id}/email` + `/{id}/content` GET/PUT ·
-`/documents/cabinets` CRUD + `/documents/activity` + `/documents/vault-appearance`
-GET/PATCH + `/documents/accessible-members` + `/documents/tags` GET/POST ·
-`/documents/folders/tree` + `/documents/folders/children` + `/documents/folders`
-POST + `/documents/folders/{id}` GET/PATCH/DELETE + `/{id}/contents` +
-`/{id}/export` (zip) + `/{id}/email`
-**Vault client helpers (FE):** `uploadDocumentWithProgress` ·
-`downloadFileWithProgress` · `downloadFolderExportWithProgress` ·
-`importFolderTree` (recreates a local folder tree in the vault)
 PUBLISHED TITLE: Every upload, move, and email - on record.
 SHORT-FORM VARIANT: Every upload, move, and email
 PUBLISHED DESCRIPTION: Open the vault activity feed to see who uploaded, moved, renamed, emailed, or deleted what - a full audit trail for your documents. Try free #custosell #documents #filestorage #vault #Custosell #SmallBusiness
@@ -12840,7 +12813,34 @@
   - Screen-record clips: the Screen flow steps, trimmed to the script beats
   - Captions / subtitles: full on-screen captions exported as a caption file
   - Brand overlay / watermark: Custosell logo, corner placement
-  - Music: royalty-free background bed, low volume under the voiceover</t>
+  - Music: royalty-free background bed, low volume under the voiceover
+  - ---
+  - ## Technical reference (source of truth)
+  - **Screens:** `/documents` [M] (cabinet cards + search + New cabinet) ·
+  - `/documents/cabinets/{id}` [M] (explorer: folder tree, upload/link/import,
+  - access, preview/edit, email, export, activity)
+  - **User actions (FE hooks):** `useDocumentCabinets` · `useDocumentCabinet` ·
+  - `useCreateDocumentCabinet` · `useUpdateDocumentCabinet` ·
+  - `useDeleteDocumentCabinet` · `useDocumentFolderTree` ·
+  - `useDocumentFolderChildren` · `useDocumentFolderContents` ·
+  - `useCreateDocumentFolder` · `useUpdateDocumentFolder` ·
+  - `useDeleteDocumentFolder` · `useDocuments` (infinite list) · `useDocument` ·
+  - `useUploadDocument` · `useCreateDocumentLink` · `useUpdateDocument` ·
+  - `useDeleteDocument` · `useDocumentContent` · `useUpdateDocumentContent` ·
+  - `useRecordDocumentView` · `useRecordDocumentDownload` ·
+  - `useDocumentAccessibleMembers` · `useDocumentActivity` · `useDocumentTags` ·
+  - `useDocumentsVaultAppearance` · `useUpdateDocumentsVaultAppearance`
+  - **API endpoints (BE):** `/documents` GET + `/documents/upload` +
+  - `/documents/link` + `/documents/{id}` GET/PATCH/DELETE + `/{id}/view` +
+  - `/{id}/download` + `/{id}/email` + `/{id}/content` GET/PUT ·
+  - `/documents/cabinets` CRUD + `/documents/activity` + `/documents/vault-appearance`
+  - GET/PATCH + `/documents/accessible-members` + `/documents/tags` GET/POST ·
+  - `/documents/folders/tree` + `/documents/folders/children` + `/documents/folders`
+  - POST + `/documents/folders/{id}` GET/PATCH/DELETE + `/{id}/contents` +
+  - `/{id}/export` (zip) + `/{id}/email`
+  - **Vault client helpers (FE):** `uploadDocumentWithProgress` ·
+  - `downloadFileWithProgress` · `downloadFolderExportWithProgress` ·
+  - `importFolderTree` (recreates a local folder tree in the vault)</t>
         </is>
       </c>
       <c r="D206" s="5" t="n"/>
@@ -13177,7 +13177,7 @@
 CTA: Try free
 RELATED: [19-notifications-webpush.md](./19-notifications-webpush.md)
 PUBLISHED TITLE: The fortune is in the follow-up.
-SHORT-FORM VARIANT: The fortune is
+SHORT-FORM VARIANT: The follow-up is the fortune
 PUBLISHED DESCRIPTION: Set a reminder on any lead - when and how (in-app, email, or both) - and Custosell nags you so no deal goes cold. Try free #custosell #crm #pipeline #leads #Custosell #SmallBusiness
 TAGS: custosell, crm, pipeline, leads, sales funnel, kanban, deals, how to, tutorial, walkthrough, tips
 VIDEO ASSETS:
@@ -13867,59 +13867,6 @@
 DEMO DATA: A recently won deal.
 CTA: Try free
 RELATED: [11-pipeline-crm.md](./11-pipeline-crm.md)
----
-## Technical reference (source of truth)
-**Screens:** `/pipeline/boards` [M] (board directory + search) ·
-`/pipeline/boards/{boardRef}` [M] (full-screen kanban/calendar/members/progress/
-fame + conversation + collaboration) · `/pipeline/my-work` [M] (my open leads) ·
-`/pipeline/leads` [M] (all leads with filters) · `/pipeline/insights` [M] ·
-`/pipeline/settings` [M] (sources, labels, custom fields, boards directory) ·
-`/pipeline/referrals` · `/book/{token}` + `/book/{token}/check/{reference}`
-[public]
-**User actions (FE hooks):** `usePipelineBoards` · `usePipelineBoard` ·
-`usePipelineKanban` · `useCreatePipelineBoard` · `useUpdatePipelineBoard` ·
-`useDuplicatePipelineBoard` · `useDeletePipelineBoard` ·
-`useCreatePipelineStage` · `useUpdatePipelineStage` · `useDeletePipelineStage`
-· `useReorderPipelineStages` · `usePipelineLeads` · `usePipelineLead` ·
-`useCreatePipelineLead` · `useUpdatePipelineLead` · `useMovePipelineLead` ·
-`useConvertPipelineLead` · `useDeletePipelineLead` · `usePipelineSources`
-(+ CRUD) · `usePipelineLabels` (+ CRUD) · `useCreatePipelineChecklist` +
-items (+ update/delete) · `useAddPipelineActivity`/`useUpdatePipelineActivity`/
-`useDeletePipelineActivity` · `useToggleActivityReaction` ·
-`useLeadReminders`/`useCreateLeadReminder`/`useCancelLeadReminder` ·
-`useBoardAnnouncements`/`useCreateBoardAnnouncement`/`useSetAnnouncementRead` ·
-`useBoardPolls`/`useCreateBoardPoll`/`useVotePoll`/`useRemovePollVote` ·
-`useBoardConversationSummary`/`useBoardConversationMessages`/`usePostBoardMessage`
-(+ update/delete/react/pin/read) · `useBoardAutomations`/`useSyncBoardAutomations`
-· `useBoardResources`(+ CRUD + members) · `useBoardTemplates`/`useApplyBoardTemplate`
-· `usePipelineCalendar`/`useAllBoardsCalendar` · `usePipelineInsights` ·
-`useBoardProgressSummary`/`useMyBoardProgress`/`useBoardTargets`/
-`useCreateBoardTarget`/`useUpdateBoardTarget`/`useArchiveBoardTarget`/
-`useDecomposeTargetPreview`/`useExportBoardProgress` · `useWallFamePosts`(+ CRUD)
-· `useBookingInfo`/`useBookingSlots`/`useCreateBooking`/`useCheckBooking`/
-`useBookingSettings`(+ update/regenerate token)/`useApproveBooking`/
-`useCompleteBooking`/`useRejectBooking`/`useClearBooking` ·
-`useScheduleMeeting`/`useCreateMeeting`/`useUpdateMeeting`/`useDeleteMeeting` ·
-`usePipelineMemberRoster`
-**API endpoints (BE):** `/pipeline/boards` CRUD + `/kanban` + `/calendar` +
-`/duplicate` + `/background` + `/import-template` + `/import` +
-`/team-members` · `/pipeline/boards/{id}/stages` + `/stages/reorder` +
-`/pipeline/stages/{id}` · `/pipeline/leads` CRUD + `/{id}/stage` +
-`/{id}/convert` + `/{id}/activities` + `/{id}/attachments` (+ `/link`) +
-`/{id}/checklists` + items + `/{id}/meta-values` + `/{id}/links` +
-`/{id}/reminders` · `/pipeline/sources` CRUD · `/pipeline/labels` CRUD ·
-`/pipeline/insights` · `/pipeline/boards/{id}/collaboration-summary` +
-`/announcements` + `/polls` (+ vote) + `/conversation/*` + `/automations` +
-`/resources` (+ upload/link/view/download) + `/progress/summary` + `/progress/my`
-+ `/progress/config` + `/progress/export` + `/targets` (+ decompose-preview) ·
-`/pipeline/board-templates` + `/apply-template` · `/pipeline/wall-of-fame` CRUD
-· `/pipeline/boards/{id}/booking-settings` (+ regenerate-token) +
-`/pipeline/leads/{id}/approve-booking|complete-booking|reject-booking|
-clear-booking|schedule-meeting` + `/pipeline/meetings/{id}` ·
-`/public/book/{token}` + `/slots` + `/check/{reference}`
-**Route middleware (BE):** `auth:sanctum` · `business.active` ·
-`subscription.active` · `pipeline.access` (EnsurePipelineModuleAccess) - public
-booking routes unauthenticated
 PUBLISHED TITLE: Closed it? Put it on the wall.
 SHORT-FORM VARIANT: Closed it? Put it on the wall.
 PUBLISHED DESCRIPTION: Post quotes, shoutouts, performers, and milestones to the board's wall of fame - a fun, motivating feed your team sees when they open the board. Try free #custosell #crm #pipeline #leads #Custosell #SmallBusiness
@@ -13929,7 +13876,60 @@
   - Screen-record clips: the Screen flow steps, trimmed to the script beats
   - Captions / subtitles: full on-screen captions exported as a caption file
   - Brand overlay / watermark: Custosell logo, corner placement
-  - Music: royalty-free background bed, low volume under the voiceover</t>
+  - Music: royalty-free background bed, low volume under the voiceover
+  - ---
+  - ## Technical reference (source of truth)
+  - **Screens:** `/pipeline/boards` [M] (board directory + search) ·
+  - `/pipeline/boards/{boardRef}` [M] (full-screen kanban/calendar/members/progress/
+  - fame + conversation + collaboration) · `/pipeline/my-work` [M] (my open leads) ·
+  - `/pipeline/leads` [M] (all leads with filters) · `/pipeline/insights` [M] ·
+  - `/pipeline/settings` [M] (sources, labels, custom fields, boards directory) ·
+  - `/pipeline/referrals` · `/book/{token}` + `/book/{token}/check/{reference}`
+  - [public]
+  - **User actions (FE hooks):** `usePipelineBoards` · `usePipelineBoard` ·
+  - `usePipelineKanban` · `useCreatePipelineBoard` · `useUpdatePipelineBoard` ·
+  - `useDuplicatePipelineBoard` · `useDeletePipelineBoard` ·
+  - `useCreatePipelineStage` · `useUpdatePipelineStage` · `useDeletePipelineStage`
+  - · `useReorderPipelineStages` · `usePipelineLeads` · `usePipelineLead` ·
+  - `useCreatePipelineLead` · `useUpdatePipelineLead` · `useMovePipelineLead` ·
+  - `useConvertPipelineLead` · `useDeletePipelineLead` · `usePipelineSources`
+  - (+ CRUD) · `usePipelineLabels` (+ CRUD) · `useCreatePipelineChecklist` +
+  - items (+ update/delete) · `useAddPipelineActivity`/`useUpdatePipelineActivity`/
+  - `useDeletePipelineActivity` · `useToggleActivityReaction` ·
+  - `useLeadReminders`/`useCreateLeadReminder`/`useCancelLeadReminder` ·
+  - `useBoardAnnouncements`/`useCreateBoardAnnouncement`/`useSetAnnouncementRead` ·
+  - `useBoardPolls`/`useCreateBoardPoll`/`useVotePoll`/`useRemovePollVote` ·
+  - `useBoardConversationSummary`/`useBoardConversationMessages`/`usePostBoardMessage`
+  - (+ update/delete/react/pin/read) · `useBoardAutomations`/`useSyncBoardAutomations`
+  - · `useBoardResources`(+ CRUD + members) · `useBoardTemplates`/`useApplyBoardTemplate`
+  - · `usePipelineCalendar`/`useAllBoardsCalendar` · `usePipelineInsights` ·
+  - `useBoardProgressSummary`/`useMyBoardProgress`/`useBoardTargets`/
+  - `useCreateBoardTarget`/`useUpdateBoardTarget`/`useArchiveBoardTarget`/
+  - `useDecomposeTargetPreview`/`useExportBoardProgress` · `useWallFamePosts`(+ CRUD)
+  - · `useBookingInfo`/`useBookingSlots`/`useCreateBooking`/`useCheckBooking`/
+  - `useBookingSettings`(+ update/regenerate token)/`useApproveBooking`/
+  - `useCompleteBooking`/`useRejectBooking`/`useClearBooking` ·
+  - `useScheduleMeeting`/`useCreateMeeting`/`useUpdateMeeting`/`useDeleteMeeting` ·
+  - `usePipelineMemberRoster`
+  - **API endpoints (BE):** `/pipeline/boards` CRUD + `/kanban` + `/calendar` +
+  - `/duplicate` + `/background` + `/import-template` + `/import` +
+  - `/team-members` · `/pipeline/boards/{id}/stages` + `/stages/reorder` +
+  - `/pipeline/stages/{id}` · `/pipeline/leads` CRUD + `/{id}/stage` +
+  - `/{id}/convert` + `/{id}/activities` + `/{id}/attachments` (+ `/link`) +
+  - `/{id}/checklists` + items + `/{id}/meta-values` + `/{id}/links` +
+  - `/{id}/reminders` · `/pipeline/sources` CRUD · `/pipeline/labels` CRUD ·
+  - `/pipeline/insights` · `/pipeline/boards/{id}/collaboration-summary` +
+  - `/announcements` + `/polls` (+ vote) + `/conversation/*` + `/automations` +
+  - `/resources` (+ upload/link/view/download) + `/progress/summary` + `/progress/my`
+  - + `/progress/config` + `/progress/export` + `/targets` (+ decompose-preview) ·
+  - `/pipeline/board-templates` + `/apply-template` · `/pipeline/wall-of-fame` CRUD
+  - · `/pipeline/boards/{id}/booking-settings` (+ regenerate-token) +
+  - `/pipeline/leads/{id}/approve-booking|complete-booking|reject-booking|
+  - clear-booking|schedule-meeting` + `/pipeline/meetings/{id}` ·
+  - `/public/book/{token}` + `/slots` + `/check/{reference}`
+  - **Route middleware (BE):** `auth:sanctum` · `business.active` ·
+  - `subscription.active` · `pipeline.access` (EnsurePipelineModuleAccess) - public
+  - booking routes unauthenticated</t>
         </is>
       </c>
       <c r="D224" s="5" t="n"/>
@@ -14623,65 +14623,6 @@
 DEMO DATA: A published shop and social link URLs.
 CTA: Try free
 RELATED: [17-settings.md](./17-settings.md)
----
-## Technical reference (source of truth)
-**Screens (buyer):** `/discover` [M] (Businesses / Products tabs, infinite
-catalogs) · `/discover/shop/{slug}` [M] (shop catalog, filters, product modal,
-QR, social) · `/discover/my-orders` [M] (status tabs, cancel/delete, receipt,
-invoice) · `/discover/wishlist` [M] · `/discover/favorites` [M] · `/{@slug}`
-and `/{@slug}/p/{productSlug}` [M] (public share handles that redirect into the
-app). Seller setup lives in Settings -&gt; Sales channels (`BusinessStorefrontCard`,
-`ShopUsernameField`, QR download) and Inventory -&gt; products
-(`ProductStorefrontListingSection`, bulk list/unlist, image upload).
-**User actions (FE hooks):** Catalog: `useStorefrontShopsInfinite` ·
-`useStorefrontDiscoverInfinite` · `useStorefrontFacets` ·
-`useStorefrontCategories` · `useStorefrontShop` ·
-`useStorefrontShopProductsInfinite` · `useStorefrontShopProduct`. Orders:
-`useMyStorefrontOrdersList` (30s poll) · `useMyStorefrontOrdersCount` ·
-`usePlaceStorefrontOrder` · `useCancelMyStorefrontOrder` ·
-`useDeleteMyStorefrontOrder` · `fetchMyStorefrontOrderSale` ·
-`fetchMyStorefrontOrderInvoice`. Wishlist: `useWishlist` · `useWishlistCount` ·
-`useAddToWishlist` · `useRemoveFromWishlist`. Favorites: `useFavorites` ·
-`useFavoritesCount` · `useIsFavorited` · `useAddToFavorites` ·
-`useRemoveFromFavorites`. Ratings: `useRateStorefrontProduct` ·
-`useRateStorefrontShop`. Seller: `useUpdateStorefrontProfile` ·
-`useCheckSlugAvailable` · `useUpdateStorefrontListing` ·
-`useUploadProductImage` · `useBusinessSocialLinks` /
-`useUpsertBusinessSocialLink` / `useDeleteBusinessSocialLink`.
-**API endpoints (BE):** `GET /storefront/discover` · `/storefront/categories`
-· `/storefront/facets` · `/storefront/shops` · `/storefront/{slug}` ·
-`/storefront/{slug}/products` · `/storefront/{slug}/products/{productSlug}` ·
-`POST /storefront/{slug}/ratings` · `POST
-/storefront/{slug}/products/{product}/ratings` · `POST
-/storefront/{slug}/orders` (throttle:storefront-orders) · `GET
-/storefront/my-orders` + `/{order}/sale` + `/{order}/invoice` +
-`/{order}/invoice/pdf` + `POST /{order}/cancel` + `DELETE /{order}` ·
-`/storefront/wishlist` (+ `POST`, `DELETE /by-product/{product}`) ·
-`/storefront/favorites` (+ `POST`, `DELETE /{business}`). Seller-side:
-`PATCH /businesses/storefront-profile` · `GET /businesses/slug-available` ·
-`PATCH /products/{id}/storefront-listing` · `POST /products/{id}/image` ·
-`/business-social-links` CRUD.
-**Route middleware (BE):** public catalog/shop routes have no auth; buyer
-auth-gated routes (orders, wishlist, favorites, ratings, place order) use
-`auth:sanctum`, with `throttle:60,1` on wishlist/favorites/ratings and
-`throttle:storefront-orders` on placing orders.
-**Key types (FE):** `StorefrontShop` (name, slug, description, logo, city,
-country, phone, email, currency, rating_avg/count, my_rating, category,
-social_links) · `StorefrontProduct` (slug, unit_price, compare_at_price,
-sale_price, discount_percent, unit, image_path, type product|service,
-stock_quantity, in_stock, availability, rating_avg/count, business) ·
-`MyStorefrontOrder` (order_number, status open|completed|invoiced|cancelled,
-total_amount, items, customer_name/phone, delivery_address/city, notes,
-shop_name/slug, currency, sale_id, receipt_number, invoice_id) ·
-`StorefrontCartBag` (per-shop bag: shop meta, items, notes, contact) ·
-`WishlistItem` (product) vs `FavoriteItem` (business) · Facets (business
-categories, countries/cities, currencies, product types, price bounds).
-**Notes:** multi-cart = one bag per shop slug, tabbed, submitted one at a time,
-persisted in localStorage (`custosell.storefront.cart.v1`), cleared on logout.
-Wishlist is for products (heart); favorites are for businesses (star); both
-server-backed and sign-in gated. Orders poll every 30s with a status-change
-chime. No theme/branding customization exists - shop look comes from the
-Business record (name, logo, description, contact, currency, social links).
 PUBLISHED TITLE: Facebook, WhatsApp, TikTok - on your shop page.
 SHORT-FORM VARIANT: Facebook, WhatsApp, TikTok
 PUBLISHED DESCRIPTION: Add your social links in settings and they appear on your public shop with brand icons - so customers can follow, message, and find you. Try free #custosell #storefront #onlineshop #ecommerce #Custosell #SmallBusiness
@@ -14691,7 +14632,66 @@
   - Screen-record clips: the Screen flow steps, trimmed to the script beats
   - Captions / subtitles: full on-screen captions exported as a caption file
   - Brand overlay / watermark: Custosell logo, corner placement
-  - Music: royalty-free background bed, low volume under the voiceover</t>
+  - Music: royalty-free background bed, low volume under the voiceover
+  - ---
+  - ## Technical reference (source of truth)
+  - **Screens (buyer):** `/discover` [M] (Businesses / Products tabs, infinite
+  - catalogs) · `/discover/shop/{slug}` [M] (shop catalog, filters, product modal,
+  - QR, social) · `/discover/my-orders` [M] (status tabs, cancel/delete, receipt,
+  - invoice) · `/discover/wishlist` [M] · `/discover/favorites` [M] · `/{@slug}`
+  - and `/{@slug}/p/{productSlug}` [M] (public share handles that redirect into the
+  - app). Seller setup lives in Settings -&gt; Sales channels (`BusinessStorefrontCard`,
+  - `ShopUsernameField`, QR download) and Inventory -&gt; products
+  - (`ProductStorefrontListingSection`, bulk list/unlist, image upload).
+  - **User actions (FE hooks):** Catalog: `useStorefrontShopsInfinite` ·
+  - `useStorefrontDiscoverInfinite` · `useStorefrontFacets` ·
+  - `useStorefrontCategories` · `useStorefrontShop` ·
+  - `useStorefrontShopProductsInfinite` · `useStorefrontShopProduct`. Orders:
+  - `useMyStorefrontOrdersList` (30s poll) · `useMyStorefrontOrdersCount` ·
+  - `usePlaceStorefrontOrder` · `useCancelMyStorefrontOrder` ·
+  - `useDeleteMyStorefrontOrder` · `fetchMyStorefrontOrderSale` ·
+  - `fetchMyStorefrontOrderInvoice`. Wishlist: `useWishlist` · `useWishlistCount` ·
+  - `useAddToWishlist` · `useRemoveFromWishlist`. Favorites: `useFavorites` ·
+  - `useFavoritesCount` · `useIsFavorited` · `useAddToFavorites` ·
+  - `useRemoveFromFavorites`. Ratings: `useRateStorefrontProduct` ·
+  - `useRateStorefrontShop`. Seller: `useUpdateStorefrontProfile` ·
+  - `useCheckSlugAvailable` · `useUpdateStorefrontListing` ·
+  - `useUploadProductImage` · `useBusinessSocialLinks` /
+  - `useUpsertBusinessSocialLink` / `useDeleteBusinessSocialLink`.
+  - **API endpoints (BE):** `GET /storefront/discover` · `/storefront/categories`
+  - · `/storefront/facets` · `/storefront/shops` · `/storefront/{slug}` ·
+  - `/storefront/{slug}/products` · `/storefront/{slug}/products/{productSlug}` ·
+  - `POST /storefront/{slug}/ratings` · `POST
+  - /storefront/{slug}/products/{product}/ratings` · `POST
+  - /storefront/{slug}/orders` (throttle:storefront-orders) · `GET
+  - /storefront/my-orders` + `/{order}/sale` + `/{order}/invoice` +
+  - `/{order}/invoice/pdf` + `POST /{order}/cancel` + `DELETE /{order}` ·
+  - `/storefront/wishlist` (+ `POST`, `DELETE /by-product/{product}`) ·
+  - `/storefront/favorites` (+ `POST`, `DELETE /{business}`). Seller-side:
+  - `PATCH /businesses/storefront-profile` · `GET /businesses/slug-available` ·
+  - `PATCH /products/{id}/storefront-listing` · `POST /products/{id}/image` ·
+  - `/business-social-links` CRUD.
+  - **Route middleware (BE):** public catalog/shop routes have no auth; buyer
+  - auth-gated routes (orders, wishlist, favorites, ratings, place order) use
+  - `auth:sanctum`, with `throttle:60,1` on wishlist/favorites/ratings and
+  - `throttle:storefront-orders` on placing orders.
+  - **Key types (FE):** `StorefrontShop` (name, slug, description, logo, city,
+  - country, phone, email, currency, rating_avg/count, my_rating, category,
+  - social_links) · `StorefrontProduct` (slug, unit_price, compare_at_price,
+  - sale_price, discount_percent, unit, image_path, type product|service,
+  - stock_quantity, in_stock, availability, rating_avg/count, business) ·
+  - `MyStorefrontOrder` (order_number, status open|completed|invoiced|cancelled,
+  - total_amount, items, customer_name/phone, delivery_address/city, notes,
+  - shop_name/slug, currency, sale_id, receipt_number, invoice_id) ·
+  - `StorefrontCartBag` (per-shop bag: shop meta, items, notes, contact) ·
+  - `WishlistItem` (product) vs `FavoriteItem` (business) · Facets (business
+  - categories, countries/cities, currencies, product types, price bounds).
+  - **Notes:** multi-cart = one bag per shop slug, tabbed, submitted one at a time,
+  - persisted in localStorage (`custosell.storefront.cart.v1`), cleared on logout.
+  - Wishlist is for products (heart); favorites are for businesses (star); both
+  - server-backed and sign-in gated. Orders poll every 30s with a status-change
+  - chime. No theme/branding customization exists - shop look comes from the
+  - Business record (name, logo, description, contact, currency, social links).</t>
         </is>
       </c>
       <c r="D236" s="5" t="n"/>
@@ -15619,86 +15619,6 @@
 DEMO DATA: Multiple branches with staff.
 CTA: Try free
 RELATED: [17-settings.md](./17-settings.md)
----
-## Technical reference (source of truth)
-**Screens:** `/hr` (index redirects to overview for full HR, attendance for
-limited HR) · `/hr/overview` [M] · `/hr/people` [M] + `/hr/people/{id}` [M]
-(detail editor incl. login section) · `/hr/departments` [M] ·
-`/hr/company-assets` [M] + `/hr/company-assets/{id}` [M] ·
-`/hr/attendance` [M] · `/hr/leave` [M] · `/hr/payroll` [M] +
-`/hr/payroll/runs/{id}` [M] · `/hr/talent` [M] (tabs: performance / onboarding
-/ reviews) · `/hr/transfers` [M] · `/hr/reports` [M] · `/hr/settings` [M]
-(audit log viewer). Full HR access = owner or staff with `hr_full`; limited HR
-users only get attendance, leave, and talent.
-**User actions (FE hooks):** Org: `useHrDepartments` / CRUD ·
-`useHrPositions` / CRUD. Employees: `useHrEmployees` · `useHrEmployee` ·
-`useCreateHrEmployee` · `useCreateHrEmployeeWithAccount` · `useHrAccountOptions`
-· `useUpdateHrEmployee` · `useDeleteHrEmployee` · `useLinkHrEmployeeUser` ·
-`useUnlinkHrEmployeeUser` · `useCreateHrEmployeeAccount` ·
-`useRemoveHrEmployeeAccount`. Attendance: `useHrAttendance` (register +
-events) · `useHrClock` · `useUpdateHrAttendanceDay` · `useImportHrTimesheets` ·
-`useHrPosShifts`. Leave: `useHrLeaveTypes` / CRUD · `useHrLeaveBalances` ·
-`useHrLeaveRequests` · `useCreateHrLeaveRequest` · `useApproveHrLeaveRequest` ·
-`useRejectHrLeaveRequest` · `useCancelHrLeaveRequest`. Payroll:
-`useHrSalaryStructures` / CRUD · `useHrCompensations` / create/delete ·
-`useHrPayRuns` · `useHrPayRun` · `useCreateHrPayRun` · `useUpdateHrPayRun` ·
-`useDeleteHrPayRun` · `useCalculateHrPayRun` · `useApproveHrPayRun` ·
-`usePostHrPayRun` · `useSettleHrPayRun` · `useRemitHrStatutory` ·
-`useVoidHrPayRun`. Talent: `useHrOnboardingTemplates` / CRUD ·
-`useHrOnboardingTasks` / create/update · `useHrReviews` / create/update ·
-`useHrPerformanceRoster` · `useHrPerformanceEmployee` ·
-`useHrPerformanceByUser` · `useSeedHrPerformanceReview`. Assets:
-`useHrCompanyAssets` · `useHrCompanyAsset` · `useCreateHrCompanyAsset` ·
-`useUpdateHrCompanyAssetCustody` · `useAssignHrCompanyAsset` ·
-`useTransferHrCompanyAsset` · `useReturnHrCompanyAsset` ·
-`useHrCompanyAssetAssignments` · `useHrCompanyAssetMaintenanceExpenses`.
-Reports: `useHrPayeReport` · `useHrNssfReport` · `useHrPayrollAffordability`
-(POST) · `useHrPayrollAffordabilityMutation` · `useHrAuditLogs`.
-**API endpoints (BE):** `/hr/departments` CRUD · `/hr/positions` CRUD ·
-`/hr/employees` + `/hr/employees/sync-staff` + `/hr/employees/with-account` +
-`/hr/account-options` + `/{id}` CRUD + `/{id}/link-user` + `/{id}/unlink-user`
-+ `/{id}/create-account` + `/{id}/remove-account` · `/hr/attendance/clock` +
-`/hr/attendance/events` + `/hr/attendance/register` + `/hr/attendance/days`
-(PUT) + `/hr/attendance/import-timesheets` + `/hr/attendance/pos-shifts` ·
-`/hr/leave/types` CRUD + `/hr/leave/balances` + `/hr/leave/balances/ensure` +
-`/hr/leave/requests` + `/{id}/approve` + `/{id}/reject` + `/{id}/cancel` ·
-`/hr/payroll/structures` CRUD + `/hr/payroll/compensations` + `/hr/payroll/
-pay-runs` CRUD + `/{id}/calculate` + `/{id}/approve` + `/{id}/post` +
-`/{id}/settle` + `/{id}/remit-statutory` + `/{id}/void` ·
-`/hr/talent/onboarding-templates` CRUD + `/hr/talent/onboarding-tasks` +
-`/hr/talent/onboarding/assign` + `/hr/talent/reviews` +
-`/hr/talent/performance` + `/hr/talent/performance/employees/{id}` +
-`/hr/talent/performance/by-user/{id}` + `/hr/talent/performance/employees/
-{id}/seed-review` · `/hr/reports/paye-schedule` + `/hr/reports/nssf-schedule`
-+ `/hr/reports/payroll-affordability` (POST) + `/hr/audit-logs` ·
-`/hr/company-assets` CRUD + `/{id}/assign` + `/{id}/transfer` + `/{id}/return`
-+ `/{id}/assignments` + `/{id}/maintenance-expenses`. Cross-module:
-`/staff-transfers` CRUD (settings module), `/users`, `/locations`.
-**Route middleware (BE):** all HR routes use `auth:sanctum` ·
-`business.active` · `subscription.active` · `module:hr`. Sensitive routes
-(org, employee writes, attendance corrections, leave decisions, all payroll,
-talent templates/reviews, reports, assets) additionally require `hr.full`
-middleware; clock, events, register, leave request/cancel, and onboarding-task
-updates are self-service for limited users. Online-only module.
-**Key statuses (FE):** `EmployeeStatus` = onboarding | active | on_leave |
-terminated · `EmploymentType` = full_time | part_time | contract | casual ·
-`PayRunStatus` = draft | calculated | approved | posted | void ·
-`AttendanceEventType` = clock_in | clock_out | break_start | break_end ·
-`AttendanceDayStatus` = present | absent | leave | holiday · `LeaveRequestStatus`
-= pending | approved | rejected | cancelled · `OnboardingTaskStatus` = pending
-| done | skipped · `ReviewStatus` = draft | submitted | completed ·
-`PerformanceVerdict` = on_track | at_risk | behind | no_data | unlinked ·
-`AssetCategory` = laptop | phone | furniture | vehicle | other · `AssetCondition`
-= new | good | fair | poor | retired.
-**Notes:** pay run lifecycle writes accounting journals (accrual Dr 6101 / Cr
-2110-2112, settlement Dr Salaries Payable / Cr Bank 1102, statutory remit Dr
-PAYE + NSSF payable / Cr Bank) and invalidates HR statutory reports on
-post/void. Company assets share the accounting FixedAsset entity (book value
-synced). Performance is computed from Pipeline leads + Project tasks + board
-goals, and seeded review drafts carry that snapshot. Payroll affordability
-defaults to a 3-month horizon and supports a hire what-if (basic salary,
-allowances, deductions, start month offset). Payslips are embedded on pay-run
-lines (no dedicated endpoint yet).
 PUBLISHED TITLE: Move staff between branches, tracked.
 SHORT-FORM VARIANT: Move staff between branches
 PUBLISHED DESCRIPTION: Transfer a staff member from one branch to another - permanent or temporary - and keep the whole history visible with branch headcount overviews. Try free #custosell #hr #payroll #employees #Custosell #SmallBusiness
@@ -15708,7 +15628,87 @@
   - Screen-record clips: the Screen flow steps, trimmed to the script beats
   - Captions / subtitles: full on-screen captions exported as a caption file
   - Brand overlay / watermark: Custosell logo, corner placement
-  - Music: royalty-free background bed, low volume under the voiceover</t>
+  - Music: royalty-free background bed, low volume under the voiceover
+  - ---
+  - ## Technical reference (source of truth)
+  - **Screens:** `/hr` (index redirects to overview for full HR, attendance for
+  - limited HR) · `/hr/overview` [M] · `/hr/people` [M] + `/hr/people/{id}` [M]
+  - (detail editor incl. login section) · `/hr/departments` [M] ·
+  - `/hr/company-assets` [M] + `/hr/company-assets/{id}` [M] ·
+  - `/hr/attendance` [M] · `/hr/leave` [M] · `/hr/payroll` [M] +
+  - `/hr/payroll/runs/{id}` [M] · `/hr/talent` [M] (tabs: performance / onboarding
+  - / reviews) · `/hr/transfers` [M] · `/hr/reports` [M] · `/hr/settings` [M]
+  - (audit log viewer). Full HR access = owner or staff with `hr_full`; limited HR
+  - users only get attendance, leave, and talent.
+  - **User actions (FE hooks):** Org: `useHrDepartments` / CRUD ·
+  - `useHrPositions` / CRUD. Employees: `useHrEmployees` · `useHrEmployee` ·
+  - `useCreateHrEmployee` · `useCreateHrEmployeeWithAccount` · `useHrAccountOptions`
+  - · `useUpdateHrEmployee` · `useDeleteHrEmployee` · `useLinkHrEmployeeUser` ·
+  - `useUnlinkHrEmployeeUser` · `useCreateHrEmployeeAccount` ·
+  - `useRemoveHrEmployeeAccount`. Attendance: `useHrAttendance` (register +
+  - events) · `useHrClock` · `useUpdateHrAttendanceDay` · `useImportHrTimesheets` ·
+  - `useHrPosShifts`. Leave: `useHrLeaveTypes` / CRUD · `useHrLeaveBalances` ·
+  - `useHrLeaveRequests` · `useCreateHrLeaveRequest` · `useApproveHrLeaveRequest` ·
+  - `useRejectHrLeaveRequest` · `useCancelHrLeaveRequest`. Payroll:
+  - `useHrSalaryStructures` / CRUD · `useHrCompensations` / create/delete ·
+  - `useHrPayRuns` · `useHrPayRun` · `useCreateHrPayRun` · `useUpdateHrPayRun` ·
+  - `useDeleteHrPayRun` · `useCalculateHrPayRun` · `useApproveHrPayRun` ·
+  - `usePostHrPayRun` · `useSettleHrPayRun` · `useRemitHrStatutory` ·
+  - `useVoidHrPayRun`. Talent: `useHrOnboardingTemplates` / CRUD ·
+  - `useHrOnboardingTasks` / create/update · `useHrReviews` / create/update ·
+  - `useHrPerformanceRoster` · `useHrPerformanceEmployee` ·
+  - `useHrPerformanceByUser` · `useSeedHrPerformanceReview`. Assets:
+  - `useHrCompanyAssets` · `useHrCompanyAsset` · `useCreateHrCompanyAsset` ·
+  - `useUpdateHrCompanyAssetCustody` · `useAssignHrCompanyAsset` ·
+  - `useTransferHrCompanyAsset` · `useReturnHrCompanyAsset` ·
+  - `useHrCompanyAssetAssignments` · `useHrCompanyAssetMaintenanceExpenses`.
+  - Reports: `useHrPayeReport` · `useHrNssfReport` · `useHrPayrollAffordability`
+  - (POST) · `useHrPayrollAffordabilityMutation` · `useHrAuditLogs`.
+  - **API endpoints (BE):** `/hr/departments` CRUD · `/hr/positions` CRUD ·
+  - `/hr/employees` + `/hr/employees/sync-staff` + `/hr/employees/with-account` +
+  - `/hr/account-options` + `/{id}` CRUD + `/{id}/link-user` + `/{id}/unlink-user`
+  - + `/{id}/create-account` + `/{id}/remove-account` · `/hr/attendance/clock` +
+  - `/hr/attendance/events` + `/hr/attendance/register` + `/hr/attendance/days`
+  - (PUT) + `/hr/attendance/import-timesheets` + `/hr/attendance/pos-shifts` ·
+  - `/hr/leave/types` CRUD + `/hr/leave/balances` + `/hr/leave/balances/ensure` +
+  - `/hr/leave/requests` + `/{id}/approve` + `/{id}/reject` + `/{id}/cancel` ·
+  - `/hr/payroll/structures` CRUD + `/hr/payroll/compensations` + `/hr/payroll/
+  - pay-runs` CRUD + `/{id}/calculate` + `/{id}/approve` + `/{id}/post` +
+  - `/{id}/settle` + `/{id}/remit-statutory` + `/{id}/void` ·
+  - `/hr/talent/onboarding-templates` CRUD + `/hr/talent/onboarding-tasks` +
+  - `/hr/talent/onboarding/assign` + `/hr/talent/reviews` +
+  - `/hr/talent/performance` + `/hr/talent/performance/employees/{id}` +
+  - `/hr/talent/performance/by-user/{id}` + `/hr/talent/performance/employees/
+  - {id}/seed-review` · `/hr/reports/paye-schedule` + `/hr/reports/nssf-schedule`
+  - + `/hr/reports/payroll-affordability` (POST) + `/hr/audit-logs` ·
+  - `/hr/company-assets` CRUD + `/{id}/assign` + `/{id}/transfer` + `/{id}/return`
+  - + `/{id}/assignments` + `/{id}/maintenance-expenses`. Cross-module:
+  - `/staff-transfers` CRUD (settings module), `/users`, `/locations`.
+  - **Route middleware (BE):** all HR routes use `auth:sanctum` ·
+  - `business.active` · `subscription.active` · `module:hr`. Sensitive routes
+  - (org, employee writes, attendance corrections, leave decisions, all payroll,
+  - talent templates/reviews, reports, assets) additionally require `hr.full`
+  - middleware; clock, events, register, leave request/cancel, and onboarding-task
+  - updates are self-service for limited users. Online-only module.
+  - **Key statuses (FE):** `EmployeeStatus` = onboarding | active | on_leave |
+  - terminated · `EmploymentType` = full_time | part_time | contract | casual ·
+  - `PayRunStatus` = draft | calculated | approved | posted | void ·
+  - `AttendanceEventType` = clock_in | clock_out | break_start | break_end ·
+  - `AttendanceDayStatus` = present | absent | leave | holiday · `LeaveRequestStatus`
+  - = pending | approved | rejected | cancelled · `OnboardingTaskStatus` = pending
+  - | done | skipped · `ReviewStatus` = draft | submitted | completed ·
+  - `PerformanceVerdict` = on_track | at_risk | behind | no_data | unlinked ·
+  - `AssetCategory` = laptop | phone | furniture | vehicle | other · `AssetCondition`
+  - = new | good | fair | poor | retired.
+  - **Notes:** pay run lifecycle writes accounting journals (accrual Dr 6101 / Cr
+  - 2110-2112, settlement Dr Salaries Payable / Cr Bank 1102, statutory remit Dr
+  - PAYE + NSSF payable / Cr Bank) and invalidates HR statutory reports on
+  - post/void. Company assets share the accounting FixedAsset entity (book value
+  - synced). Performance is computed from Pipeline leads + Project tasks + board
+  - goals, and seeded review drafts carry that snapshot. Payroll affordability
+  - defaults to a 3-month horizon and supports a hire what-if (basic salary,
+  - allowances, deductions, start month offset). Payslips are embedded on pay-run
+  - lines (no dedicated endpoint yet).</t>
         </is>
       </c>
       <c r="D252" s="5" t="n"/>
@@ -16161,44 +16161,6 @@
 DEMO DATA: Recurring products/services with prices.
 CTA: Try free
 RELATED: [05-inventory-products.md](./05-inventory-products.md)
----
-## Technical reference (source of truth)
-**Screens:** `/forecasting` [M] (INDEX -&gt; overview: cash ladder, burn breakdown,
-budget vs actual, coverage snapshot, quick links) · `/forecasting/budgets` [M]
-(year budget list + create) · `/forecasting/budgets/{id}` [M] (lines with
-justify/approve/roll + snapshots) · `/forecasting/kpis` [M] (retail + saas) ·
-`/forecasting/scenarios` [M] (what-if create/list/run)
-**User actions (FE hooks):** `useForecastingOverview` · `useCashForecast` ·
-`useBudgetVsActual` · `useForecastKpis` · `useForecastBudgets` ·
-`useForecastBudget` · `useCreateForecastBudget` · `useUpdateForecastBudget` ·
-`useDeleteForecastBudget` · `useCreateForecastBudgetLine` ·
-`useUpdateForecastBudgetLine` · `useDeleteForecastBudgetLine` ·
-`useJustifyForecastBudgetLine` · `useApproveForecastBudgetLine` ·
-`useRollForecastBudget` · `useForecastSnapshots` · `useForecastScenarios` ·
-`useForecastScenario` · `useCreateForecastScenario` ·
-`useUpdateForecastScenario` · `useDeleteForecastScenario` ·
-`useRunForecastScenario`
-**API endpoints (BE):** `GET /forecasting/overview` · `GET
-/forecasting/cash-forecast` · `GET /forecasting/budget-vs-actual` · `GET
-/forecasting/kpis` · `/forecasting/budgets` CRUD + `/{id}/lines` CRUD +
-`/{id}/lines/{lineId}/justify` + `/{id}/lines/{lineId}/approve` + `/{id}/roll`
-· `GET /forecasting/snapshots` · `/forecasting/scenarios` CRUD +
-`/{id}/run`
-**Route middleware (BE):** `auth:sanctum` · `business.active` ·
-`subscription.active` · `module:forecasting` (module must be enabled)
-**Key types (FE):** `ForecastCoverageStatus` = healthy | tight | critical |
-unknown · `ForecastBudgetStatus` = draft | active | archived ·
-`ForecastZbbStatus` = draft | justified | approved · `ForecastBvaStatus` = over
-| under | on_track · `ForecastKpiMode` = auto | retail | saas · `CashForecast`
-(cash, liabilities incl payroll/PAYE/NSSF payable, burn from HR payroll
-affordability + trailing opex, assumed monthly inflow from trailing 30d net
-sales, runway coverage, month cash ladder rows with can_cover) ·
-`BudgetVsActual` (per-category budget/actual/variance/status) · `ForecastBudget`
-+ `ForecastBudgetLine` (label, amount, justification, zbb_status) ·
-`ForecastSnapshot` (budget lines + YTD expense actuals captured on roll) ·
-`ForecastKpis` (retail: pulse/CAC/LTV/churn; saas: MRR/ARR/subscribers) ·
-`ForecastScenario` + `ForecastScenarioRun` (baseline + scenario forecast +
-delta)
 PUBLISHED TITLE: Sell recurring? See MRR and ARR proxies.
 SHORT-FORM VARIANT: Sell recurring? See MRR and ARR proxies.
 PUBLISHED DESCRIPTION: Mark products or services as recurring and the KPIs page shows MRR, ARR, active subscribers, and average recurring price as simple proxies from your own catalog. Try free #custosell #forecasting #budget #cashrunway #Custosell #SmallBusiness
@@ -16208,7 +16170,45 @@
   - Screen-record clips: the Screen flow steps, trimmed to the script beats
   - Captions / subtitles: full on-screen captions exported as a caption file
   - Brand overlay / watermark: Custosell logo, corner placement
-  - Music: royalty-free background bed, low volume under the voiceover</t>
+  - Music: royalty-free background bed, low volume under the voiceover
+  - ---
+  - ## Technical reference (source of truth)
+  - **Screens:** `/forecasting` [M] (INDEX -&gt; overview: cash ladder, burn breakdown,
+  - budget vs actual, coverage snapshot, quick links) · `/forecasting/budgets` [M]
+  - (year budget list + create) · `/forecasting/budgets/{id}` [M] (lines with
+  - justify/approve/roll + snapshots) · `/forecasting/kpis` [M] (retail + saas) ·
+  - `/forecasting/scenarios` [M] (what-if create/list/run)
+  - **User actions (FE hooks):** `useForecastingOverview` · `useCashForecast` ·
+  - `useBudgetVsActual` · `useForecastKpis` · `useForecastBudgets` ·
+  - `useForecastBudget` · `useCreateForecastBudget` · `useUpdateForecastBudget` ·
+  - `useDeleteForecastBudget` · `useCreateForecastBudgetLine` ·
+  - `useUpdateForecastBudgetLine` · `useDeleteForecastBudgetLine` ·
+  - `useJustifyForecastBudgetLine` · `useApproveForecastBudgetLine` ·
+  - `useRollForecastBudget` · `useForecastSnapshots` · `useForecastScenarios` ·
+  - `useForecastScenario` · `useCreateForecastScenario` ·
+  - `useUpdateForecastScenario` · `useDeleteForecastScenario` ·
+  - `useRunForecastScenario`
+  - **API endpoints (BE):** `GET /forecasting/overview` · `GET
+  - /forecasting/cash-forecast` · `GET /forecasting/budget-vs-actual` · `GET
+  - /forecasting/kpis` · `/forecasting/budgets` CRUD + `/{id}/lines` CRUD +
+  - `/{id}/lines/{lineId}/justify` + `/{id}/lines/{lineId}/approve` + `/{id}/roll`
+  - · `GET /forecasting/snapshots` · `/forecasting/scenarios` CRUD +
+  - `/{id}/run`
+  - **Route middleware (BE):** `auth:sanctum` · `business.active` ·
+  - `subscription.active` · `module:forecasting` (module must be enabled)
+  - **Key types (FE):** `ForecastCoverageStatus` = healthy | tight | critical |
+  - unknown · `ForecastBudgetStatus` = draft | active | archived ·
+  - `ForecastZbbStatus` = draft | justified | approved · `ForecastBvaStatus` = over
+  - | under | on_track · `ForecastKpiMode` = auto | retail | saas · `CashForecast`
+  - (cash, liabilities incl payroll/PAYE/NSSF payable, burn from HR payroll
+  - affordability + trailing opex, assumed monthly inflow from trailing 30d net
+  - sales, runway coverage, month cash ladder rows with can_cover) ·
+  - `BudgetVsActual` (per-category budget/actual/variance/status) · `ForecastBudget`
+  - + `ForecastBudgetLine` (label, amount, justification, zbb_status) ·
+  - `ForecastSnapshot` (budget lines + YTD expense actuals captured on roll) ·
+  - `ForecastKpis` (retail: pulse/CAC/LTV/churn; saas: MRR/ARR/subscribers) ·
+  - `ForecastScenario` + `ForecastScenarioRun` (baseline + scenario forecast +
+  - delta)</t>
         </is>
       </c>
       <c r="D260" s="5" t="n"/>
@@ -16663,62 +16663,6 @@
 DEMO DATA: A payment in pending status.
 CTA: Try free
 RELATED: [16-subscriptions-billing.md](./16-subscriptions-billing.md)
----
-## Technical reference (source of truth)
-**Screens:** `/settings/subscription` [M] (Plans + History tabs; shows
-available promo credit banner). Plans tab: current plan banner (status, billing
-cycle, next bill or trial end, setup fee status, payment action message, Renew
-Early), monthly/yearly toggle, plan cards with action buttons, feature
-comparison table, limits table. History tab: payment/change/credit timeline with
-receipt download + email + sync payment. Modals: UpgradeFlowModal,
-SubscriptionPaymentModal, BillingCycleSwitchModal, BillingCyclePaymentModal,
-RenewTopUpModal, EmailReceiptModal. Related UI: PlanCard, PlanUsageSection,
-PendingPaymentNotice, PlansTab in onboarding (ROUTES.ONBOARDING).
-**User actions (FE hooks):** `useActivePlans` (GET /plans/active) ·
-`useSubscribe` (POST /subscriptions/subscribe) · `useUpgradeQuote` (GET
-/subscriptions/{id}/proration-quote) · `useUpgrade` (POST
-/subscriptions/{id}/upgrade, effective immediate) · `useDowngrade` (POST
-/subscriptions/{id}/downgrade, effective end_of_period) ·
-`useSubscriptionChanges` (GET /subscriptions/{id}/changes) ·
-`useCancelScheduledChange` (POST /subscriptions/{id}/cancel-change) ·
-`useChangeBillingCycle` (POST /subscriptions/{id}/billing-cycle) ·
-`useInitiatePayment` (POST /billing/payments/initiate) ·
-`useInitiateOnboardingPayment` · `useConfirmPayment` (POST
-/billing/payments/{id}/confirm) · `useBillingPayment` (GET
-/billing/payments/{id}, 3s poll) · `useBillingHistory` (GET /billing/history) ·
-`downloadReceiptPdf` (GET /billing/payments/{id}/receipt) · `useEmailReceipt`
-(POST /billing/payments/{id}/receipt/email) · `useReferralEarnings`
-(available_credit banner). Also `useProfile` refresh after payment, and the
-platform-side `usePlans`/`useSubscriptions` (admin registry).
-**API endpoints (BE):** `/plans/active` + `/plans` (apiResource) ·
-`/subscriptions/current` · `/subscriptions/subscribe` ·
-`/subscriptions/{id}/cancel` · `/subscriptions/{id}/upgrade` ·
-`/subscriptions/{id}/downgrade` · `/subscriptions/{id}/proration-quote` ·
-`/subscriptions/{id}/changes` · `/subscriptions/{id}/cancel-change` ·
-`/subscriptions/{id}/billing-cycle` · `/subscriptions/access` ·
-`/billing/payments` · `/billing/payments/{id}` ·
-`/billing/payments/{id}/receipt` · `/billing/payments/{id}/receipt/email` ·
-`/billing/history` · `/billing/payments/initiate` ·
-`/billing/payments/{id}/confirm` · gateway webhooks/callback (PesaPal):
-`/billing/gateway/pesapal/webhook` + `/billing/gateway/pesapal/callback` +
-`/billing/gateway/pesapal/ipn`. Scheduled jobs (console): expire-trials,
-renew, suspend-past-due, cancel-at-period-end (02:00-02:45 daily).
-**Route middleware (BE):** business-facing subscription + billing routes use
-`auth:sanctum` + `business.active`; platform-only subscription registry
-(index/show) requires `platform:platform.businesses.view`. Generic plan/status
-mutation by owners is intentionally NOT exposed - changes happen only through
-payment-approved flows (initiate + confirm) or the platform.
-**Key concepts (FE):** `PlanActionType` = subscribe | resubscribe | reactivate
-| upgrade | downgrade | current | pay_onboarding | renew | renew_early |
-subscribe_early, resolved by a matrix over subscription status
-(none/trial_paid/trial_unpaid/active/past_due/suspended/expired/cancelled) x
-plan relation (current/higher/lower). `PaymentType` = subscription | onboarding
-| renewal | upgrade_proration | topup. `SubscriptionInfo` carries plan_id,
-status, billing_cycle, next_billing_date, trial_ends_at, onboarding_fee_paid,
-payment_action. History item types = payment | change | credit with statuses
-applied/pending/cancelled/failed/refunded/completed/successful. Payment
-currency: UGX/KES/TZS via PesaPal, otherwise USD. Billing history lives on the
-profile (auth store) and refreshes after confirmed payments.
 PUBLISHED TITLE: Paid but still pending? Sync it.
 SHORT-FORM VARIANT: Paid but still pending? Sync it.
 PUBLISHED DESCRIPTION: When a payment shows pending, tap Sync payment to re-check with the provider and confirm the real status - so your subscription updates immediately. Try free #custosell #subscription #billing #plans #Custosell #SmallBusiness
@@ -16728,7 +16672,63 @@
   - Screen-record clips: the Screen flow steps, trimmed to the script beats
   - Captions / subtitles: full on-screen captions exported as a caption file
   - Brand overlay / watermark: Custosell logo, corner placement
-  - Music: royalty-free background bed, low volume under the voiceover</t>
+  - Music: royalty-free background bed, low volume under the voiceover
+  - ---
+  - ## Technical reference (source of truth)
+  - **Screens:** `/settings/subscription` [M] (Plans + History tabs; shows
+  - available promo credit banner). Plans tab: current plan banner (status, billing
+  - cycle, next bill or trial end, setup fee status, payment action message, Renew
+  - Early), monthly/yearly toggle, plan cards with action buttons, feature
+  - comparison table, limits table. History tab: payment/change/credit timeline with
+  - receipt download + email + sync payment. Modals: UpgradeFlowModal,
+  - SubscriptionPaymentModal, BillingCycleSwitchModal, BillingCyclePaymentModal,
+  - RenewTopUpModal, EmailReceiptModal. Related UI: PlanCard, PlanUsageSection,
+  - PendingPaymentNotice, PlansTab in onboarding (ROUTES.ONBOARDING).
+  - **User actions (FE hooks):** `useActivePlans` (GET /plans/active) ·
+  - `useSubscribe` (POST /subscriptions/subscribe) · `useUpgradeQuote` (GET
+  - /subscriptions/{id}/proration-quote) · `useUpgrade` (POST
+  - /subscriptions/{id}/upgrade, effective immediate) · `useDowngrade` (POST
+  - /subscriptions/{id}/downgrade, effective end_of_period) ·
+  - `useSubscriptionChanges` (GET /subscriptions/{id}/changes) ·
+  - `useCancelScheduledChange` (POST /subscriptions/{id}/cancel-change) ·
+  - `useChangeBillingCycle` (POST /subscriptions/{id}/billing-cycle) ·
+  - `useInitiatePayment` (POST /billing/payments/initiate) ·
+  - `useInitiateOnboardingPayment` · `useConfirmPayment` (POST
+  - /billing/payments/{id}/confirm) · `useBillingPayment` (GET
+  - /billing/payments/{id}, 3s poll) · `useBillingHistory` (GET /billing/history) ·
+  - `downloadReceiptPdf` (GET /billing/payments/{id}/receipt) · `useEmailReceipt`
+  - (POST /billing/payments/{id}/receipt/email) · `useReferralEarnings`
+  - (available_credit banner). Also `useProfile` refresh after payment, and the
+  - platform-side `usePlans`/`useSubscriptions` (admin registry).
+  - **API endpoints (BE):** `/plans/active` + `/plans` (apiResource) ·
+  - `/subscriptions/current` · `/subscriptions/subscribe` ·
+  - `/subscriptions/{id}/cancel` · `/subscriptions/{id}/upgrade` ·
+  - `/subscriptions/{id}/downgrade` · `/subscriptions/{id}/proration-quote` ·
+  - `/subscriptions/{id}/changes` · `/subscriptions/{id}/cancel-change` ·
+  - `/subscriptions/{id}/billing-cycle` · `/subscriptions/access` ·
+  - `/billing/payments` · `/billing/payments/{id}` ·
+  - `/billing/payments/{id}/receipt` · `/billing/payments/{id}/receipt/email` ·
+  - `/billing/history` · `/billing/payments/initiate` ·
+  - `/billing/payments/{id}/confirm` · gateway webhooks/callback (PesaPal):
+  - `/billing/gateway/pesapal/webhook` + `/billing/gateway/pesapal/callback` +
+  - `/billing/gateway/pesapal/ipn`. Scheduled jobs (console): expire-trials,
+  - renew, suspend-past-due, cancel-at-period-end (02:00-02:45 daily).
+  - **Route middleware (BE):** business-facing subscription + billing routes use
+  - `auth:sanctum` + `business.active`; platform-only subscription registry
+  - (index/show) requires `platform:platform.businesses.view`. Generic plan/status
+  - mutation by owners is intentionally NOT exposed - changes happen only through
+  - payment-approved flows (initiate + confirm) or the platform.
+  - **Key concepts (FE):** `PlanActionType` = subscribe | resubscribe | reactivate
+  - | upgrade | downgrade | current | pay_onboarding | renew | renew_early |
+  - subscribe_early, resolved by a matrix over subscription status
+  - (none/trial_paid/trial_unpaid/active/past_due/suspended/expired/cancelled) x
+  - plan relation (current/higher/lower). `PaymentType` = subscription | onboarding
+  - | renewal | upgrade_proration | topup. `SubscriptionInfo` carries plan_id,
+  - status, billing_cycle, next_billing_date, trial_ends_at, onboarding_fee_paid,
+  - payment_action. History item types = payment | change | credit with statuses
+  - applied/pending/cancelled/failed/refunded/completed/successful. Payment
+  - currency: UGX/KES/TZS via PesaPal, otherwise USD. Billing history lives on the
+  - profile (auth store) and refreshes after confirmed payments.</t>
         </is>
       </c>
       <c r="D268" s="5" t="n"/>
@@ -16893,7 +16893,7 @@
   - Beat 1 (Hook): "Referrals are only fun when you can watch them pay off."
   - Beat 2 (Problem): "Rewards nobody can see feel fake."
   - Beat 3 (Action): Referral Dashboard -&gt; Wins tab -&gt; Referrals / Earned /
-  - Paid / Bal cards -&gt; Referred Businesses list -&gt; Payout History.
+  - Paid / Balance cards -&gt; Referred Businesses list -&gt; Payout History.
   - Beat 4 (Aha): "Every referral shows its status and reward - pending, active,
   - or rewarded."
   - Beat 5 (CTA): "Check your dashboard at custosell.com."
@@ -17091,39 +17091,6 @@
 DEMO DATA: A business with an active referral program.
 CTA: Try free
 RELATED: [20-referrals-credits.md](./20-referrals-credits.md)
----
-## Technical reference (source of truth)
-**Screens:** Navbar `Refer &amp; Earn` dropdown (ReferralDropdown) ·
-`/account/referrals` Referral Dashboard (code card + Wins / Policy / Help tabs)
-· signup `ReferralEntryPage` ("Have a referral code?")
-**User actions (FE hooks):** `useReferralEarnings` (GET `/referrals/earnings/me`)
-· `useGenerateReferralCode` (POST `/referral-codes`, owner business) ·
-`useApplyReferralCode` (POST `/referrals/apply`) ·
-`useValidateReferralCode` (GET `/referral-codes/validate`) ·
-`usePaymentInfo` + `useUpdatePaymentInfo` (GET/PUT `/account/payment-info`) ·
-`usePayoutHistory` (GET `/payouts/my-history`)
-**Referral earnings fields:** `referral_code` · `is_sales_rep` ·
-`commission_rate` / `commission_type` · `total_earned` · `rewards_paid` ·
-`commission_earned` / `commission_paid` · `total_referrals` ·
-`available_credit` / `business_credit` / `user_credit` · `referrals[]`
-(referred business, status pending/active/rewarded, reward_amount,
-commission_earned)
-**API endpoints (BE):** `referrals.php` (auth:sanctum + business.active):
-`GET /referrals` · `GET /referrals/{id}` · `GET /referrals/business/{businessId}`
-· `GET /referrals/code/{codeId}` · `GET /referrals/earnings/me` ·
-`POST /referrals/apply` · `GET|PUT /account/payment-info` ·
-`GET /payouts/my-history` · `referral-codes.php`: `GET /referral-codes/validate`
-(public) + apiResource `referral-codes` · `credits.php`:
-`GET /credits/balance` + `GET /credits/history` (auth:sanctum +
-business.active) · `sales-reps.php` (auth:sanctum + business.active +
-subscription.active): apiResource `sales-reps` · `GET /sales-reps/import-template`
-· `POST /sales-reps/import` · `GET /sales-reps/earnings/all` ·
-`GET /sales-reps/earnings/mine` · `GET /sales-reps/{id}/earnings` ·
-`GET /sales-reps/{id}/payouts` · `POST /sales-reps/{id}/payouts`
-**Platform admin (not end-user):** `/platform/sales-reps` - manage sales reps
-(add/edit with commission rate + type + referee discount + active toggle,
-remove blocked while unpaid commission remains, CSV import from template, record
-payouts now or scheduled with method/notes/attachments).
 PUBLISHED TITLE: How Custosell referrals work - the simple version.
 SHORT-FORM VARIANT: How Custosell referrals work
 PUBLISHED DESCRIPTION: Understand the Custosell referral program in plain language: how rewards are calculated, whether there are limits, when payouts happen, and what is not allowed. One referral code per referred business, rewards based on the plan actually paid. Try free #custosell #referrals #credits #rewards #Custosell #SmallBusiness
@@ -17133,7 +17100,40 @@
   - Screen-record clips: the Screen flow steps, trimmed to the script beats
   - Captions / subtitles: full on-screen captions exported as a caption file
   - Brand overlay / watermark: Custosell logo, corner placement
-  - Music: royalty-free background bed, low volume under the voiceover</t>
+  - Music: royalty-free background bed, low volume under the voiceover
+  - ---
+  - ## Technical reference (source of truth)
+  - **Screens:** Navbar `Refer &amp; Earn` dropdown (ReferralDropdown) ·
+  - `/account/referrals` Referral Dashboard (code card + Wins / Policy / Help tabs)
+  - · signup `ReferralEntryPage` ("Have a referral code?")
+  - **User actions (FE hooks):** `useReferralEarnings` (GET `/referrals/earnings/me`)
+  - · `useGenerateReferralCode` (POST `/referral-codes`, owner business) ·
+  - `useApplyReferralCode` (POST `/referrals/apply`) ·
+  - `useValidateReferralCode` (GET `/referral-codes/validate`) ·
+  - `usePaymentInfo` + `useUpdatePaymentInfo` (GET/PUT `/account/payment-info`) ·
+  - `usePayoutHistory` (GET `/payouts/my-history`)
+  - **Referral earnings fields:** `referral_code` · `is_sales_rep` ·
+  - `commission_rate` / `commission_type` · `total_earned` · `rewards_paid` ·
+  - `commission_earned` / `commission_paid` · `total_referrals` ·
+  - `available_credit` / `business_credit` / `user_credit` · `referrals[]`
+  - (referred business, status pending/active/rewarded, reward_amount,
+  - commission_earned)
+  - **API endpoints (BE):** `referrals.php` (auth:sanctum + business.active):
+  - `GET /referrals` · `GET /referrals/{id}` · `GET /referrals/business/{businessId}`
+  - · `GET /referrals/code/{codeId}` · `GET /referrals/earnings/me` ·
+  - `POST /referrals/apply` · `GET|PUT /account/payment-info` ·
+  - `GET /payouts/my-history` · `referral-codes.php`: `GET /referral-codes/validate`
+  - (public) + apiResource `referral-codes` · `credits.php`:
+  - `GET /credits/balance` + `GET /credits/history` (auth:sanctum +
+  - business.active) · `sales-reps.php` (auth:sanctum + business.active +
+  - subscription.active): apiResource `sales-reps` · `GET /sales-reps/import-template`
+  - · `POST /sales-reps/import` · `GET /sales-reps/earnings/all` ·
+  - `GET /sales-reps/earnings/mine` · `GET /sales-reps/{id}/earnings` ·
+  - `GET /sales-reps/{id}/payouts` · `POST /sales-reps/{id}/payouts`
+  - **Platform admin (not end-user):** `/platform/sales-reps` - manage sales reps
+  - (add/edit with commission rate + type + referee discount + active toggle,
+  - remove blocked while unpaid commission remains, CSV import from template, record
+  - payouts now or scheduled with method/notes/attachments).</t>
         </is>
       </c>
       <c r="D274" s="5" t="n"/>
@@ -17351,35 +17351,6 @@
 DEMO DATA: A business account.
 CTA: Try free
 RELATED: [03-sales-pos.md](./03-sales-pos.md)
----
-## Technical reference (source of truth)
-**Screens:** `/notifications` [M] (modules/notifications/NotificationsPage) -
-inbox with All/Unread filters, open/read, mark-all-read, delete
-single/selected/all; the navbar bell (HeaderNotifications) shows the unread
-count; PushNotificationsCard and OrderSoundCard live at the top of the inbox.
-**User actions (FE hooks):** `useNotifications` (paginated, `per_page`,
-`unread_only`) · `useNotificationUnreadCount` · `useMarkNotificationRead` ·
-`useMarkAllNotificationsRead` · `useDeleteNotification` ·
-`useBulkDeleteNotifications` · `useDeleteAllNotifications` · `useWebPush`
-(toggle + status via `fetchWebPushStatus` / `storePushSubscription` /
-`removePushSubscription`) · `useSoundPreferences` (`orderSound`,
-`bigOrderThreshold`).
-**API endpoints (BE):** `GET /notifications` · `GET /notifications/unread-count`
-· `PATCH /notifications/read-all` · `PATCH /notifications/{id}/read` ·
-`DELETE /notifications/{id}` · `POST /notifications/bulk-delete` ·
-`DELETE /notifications/delete-all` · `GET /webpush/status` ·
-`POST /webpush/subscribe` · `DELETE /webpush/unsubscribe`.
-**Middleware:** notifications routes use `auth:sanctum` + `business.active`;
-web-push routes use `auth:sanctum` only.
-**Notable behavior:** notification types are `business_status`,
-`platform_message`, `user_status`, and pipeline events
-(`pipeline.assignment`, `pipeline.comment`, `pipeline.announcement`,
-`pipeline.poll`, `pipeline.reminder`, `pipeline.board_message`) - the inbox is
-for team messages and pipeline activity, not stock/payment alerts. Opening a
-message auto-marks it read; unread bubbles show on the bell. Web Push is
-browser-only (hidden in Electron) and delivers new orders, sales, and account
-updates as system notifications even while the app is closed. The order sound
-and big-order threshold are device-local preferences for business accounts.
 PUBLISHED TITLE: A chime when the order comes in.
 SHORT-FORM VARIANT: A chime when the order comes in.
 PUBLISHED DESCRIPTION: Set the order sound on Custosell so your device chimes when a new open order arrives - and set a big-order threshold so large orders get an urgent chime and a highlighted alert. Try free #custosell #notifications #webpush #alerts #Custosell #SmallBusiness
@@ -17389,7 +17360,36 @@
   - Screen-record clips: the Screen flow steps, trimmed to the script beats
   - Captions / subtitles: full on-screen captions exported as a caption file
   - Brand overlay / watermark: Custosell logo, corner placement
-  - Music: royalty-free background bed, low volume under the voiceover</t>
+  - Music: royalty-free background bed, low volume under the voiceover
+  - ---
+  - ## Technical reference (source of truth)
+  - **Screens:** `/notifications` [M] (modules/notifications/NotificationsPage) -
+  - inbox with All/Unread filters, open/read, mark-all-read, delete
+  - single/selected/all; the navbar bell (HeaderNotifications) shows the unread
+  - count; PushNotificationsCard and OrderSoundCard live at the top of the inbox.
+  - **User actions (FE hooks):** `useNotifications` (paginated, `per_page`,
+  - `unread_only`) · `useNotificationUnreadCount` · `useMarkNotificationRead` ·
+  - `useMarkAllNotificationsRead` · `useDeleteNotification` ·
+  - `useBulkDeleteNotifications` · `useDeleteAllNotifications` · `useWebPush`
+  - (toggle + status via `fetchWebPushStatus` / `storePushSubscription` /
+  - `removePushSubscription`) · `useSoundPreferences` (`orderSound`,
+  - `bigOrderThreshold`).
+  - **API endpoints (BE):** `GET /notifications` · `GET /notifications/unread-count`
+  - · `PATCH /notifications/read-all` · `PATCH /notifications/{id}/read` ·
+  - `DELETE /notifications/{id}` · `POST /notifications/bulk-delete` ·
+  - `DELETE /notifications/delete-all` · `GET /webpush/status` ·
+  - `POST /webpush/subscribe` · `DELETE /webpush/unsubscribe`.
+  - **Middleware:** notifications routes use `auth:sanctum` + `business.active`;
+  - web-push routes use `auth:sanctum` only.
+  - **Notable behavior:** notification types are `business_status`,
+  - `platform_message`, `user_status`, and pipeline events
+  - (`pipeline.assignment`, `pipeline.comment`, `pipeline.announcement`,
+  - `pipeline.poll`, `pipeline.reminder`, `pipeline.board_message`) - the inbox is
+  - for team messages and pipeline activity, not stock/payment alerts. Opening a
+  - message auto-marks it read; unread bubbles show on the bell. Web Push is
+  - browser-only (hidden in Electron) and delivers new orders, sales, and account
+  - updates as system notifications even while the app is closed. The order sound
+  - and big-order threshold are device-local preferences for business accounts.</t>
         </is>
       </c>
       <c r="D278" s="5" t="n"/>
@@ -17663,27 +17663,6 @@
 DEMO DATA: A notes board with a few notes.
 CTA: Try free
 RELATED: [18-quick-notes.md](./18-quick-notes.md)
----
-## Technical reference (source of truth)
-**Screens:** `/notes` [M] (modules/notes/QuickNotesPage) - sticky-note board with
-search bar, tag chips, New note modal, pin/drag, Background picker, Full screen
-toggle; notes are also reachable from the navbar Quick Notes dropdown.
-**User actions (FE hooks):** `useQuickNotes` · `useCreateQuickNote` ·
-`useUpdateQuickNote` · `useDeleteQuickNote` · `useReorderQuickNotes` ·
-`useRenameQuickNoteTag` · `useRemoveQuickNoteTag` · `useSaveNotesBackground` ·
-`canShareQuickNotes` (business accounts only - personal accounts keep notes
-private).
-**API endpoints (BE):** `GET|POST /quick-notes` · `PUT|PATCH|DELETE
-/quick-notes/{note_id}` · `POST /quick-notes/reorder` ·
-`POST /quick-notes/background` · `POST /quick-notes/tags/rename` ·
-`POST /quick-notes/tags/remove`.
-**Middleware:** `auth:sanctum` + `business.active` + `subscription.active`.
-**Notable behavior:** search and tag filtering are client-side (no search
-endpoint) - the search box filters notes by title/body and tag chips filter the
-board; tag rename/remove are the only tag endpoints. Offline-first: creates,
-updates, and deletes complete locally and sync later (dedupe by `client_uuid`,
-pending-sync badges on notes); `is_shared` notes show a Shared badge plus the
-author's name and are visible to the whole organization.
 PUBLISHED TITLE: Your notes, your style.
 SHORT-FORM VARIANT: Your notes
 PUBLISHED DESCRIPTION: Change the look of your quick notes board on Custosell - pick a background, use full-screen mode to hide navigation, and color-code notes the way you like. Try free #custosell #quicknotes #notes #memo #Custosell #SmallBusiness
@@ -17693,7 +17672,28 @@
   - Screen-record clips: the Screen flow steps, trimmed to the script beats
   - Captions / subtitles: full on-screen captions exported as a caption file
   - Brand overlay / watermark: Custosell logo, corner placement
-  - Music: royalty-free background bed, low volume under the voiceover</t>
+  - Music: royalty-free background bed, low volume under the voiceover
+  - ---
+  - ## Technical reference (source of truth)
+  - **Screens:** `/notes` [M] (modules/notes/QuickNotesPage) - sticky-note board with
+  - search bar, tag chips, New note modal, pin/drag, Background picker, Full screen
+  - toggle; notes are also reachable from the navbar Quick Notes dropdown.
+  - **User actions (FE hooks):** `useQuickNotes` · `useCreateQuickNote` ·
+  - `useUpdateQuickNote` · `useDeleteQuickNote` · `useReorderQuickNotes` ·
+  - `useRenameQuickNoteTag` · `useRemoveQuickNoteTag` · `useSaveNotesBackground` ·
+  - `canShareQuickNotes` (business accounts only - personal accounts keep notes
+  - private).
+  - **API endpoints (BE):** `GET|POST /quick-notes` · `PUT|PATCH|DELETE
+  - /quick-notes/{note_id}` · `POST /quick-notes/reorder` ·
+  - `POST /quick-notes/background` · `POST /quick-notes/tags/rename` ·
+  - `POST /quick-notes/tags/remove`.
+  - **Middleware:** `auth:sanctum` + `business.active` + `subscription.active`.
+  - **Notable behavior:** search and tag filtering are client-side (no search
+  - endpoint) - the search box filters notes by title/body and tag chips filter the
+  - board; tag rename/remove are the only tag endpoints. Offline-first: creates,
+  - updates, and deletes complete locally and sync later (dedupe by `client_uuid`,
+  - pending-sync badges on notes); `is_shared` notes show a Shared badge plus the
+  - author's name and are visible to the whole organization.</t>
         </is>
       </c>
       <c r="D283" s="5" t="n"/>
@@ -17988,35 +17988,6 @@
 contact details.
 CTA: Try free
 RELATED: [22-guide.md](./22-guide.md)
----
-## Technical reference (source of truth)
-**Screens:** `/guide/tutorials` (search + category filter + video cards) ·
-`/guide/faqs` (category accordion + search) · `/guide/feedback` (compose +
-Your submissions with status badges and team replies) · `/guide/contact`
-(support email + phone lines with copy buttons). All under
-`ModuleAccessMiddleware module="guide"`.
-**User actions (FE hooks):** `useGuideTutorials` (GET `/guide/tutorials`) ·
-`useGuideFaqs` (GET `/guide/faqs`) · `usePublicFaqs` (GET `/public/faqs`) ·
-`useMyGuideFeedback` (GET `/guide/feedback/mine`, merged with local pending
-via `readWithOfflineStrategy`) · `useCreateGuideFeedback` (POST
-`/guide/feedback`; offline-first via `completeOfflineGuideFeedbackInstant` -
-queues a mutation and returns a local pending record) ·
-`useDeleteMyGuideFeedback` + `useBulkDeleteMyGuideFeedback` (DELETE
-`/guide/feedback/{id}` / POST `/guide/feedback/bulk-delete`, removing local
-queue entries for unsent items)
-**Feedback status lifecycle:** `submitted` -&gt; `acknowledged` -&gt;
-`in_progress` -&gt; `resolved` / `closed`; staff replies surface on the user's
-submission card; local records carry `_pendingSync` / `_syncFailed` / `_localId`
-markers.
-**API endpoints (BE):** `guide.php` (auth:sanctum + business.active):
-`GET /guide/tutorials` · `GET /guide/faqs` · `GET /guide/feedback/mine` ·
-`POST /guide/feedback` · `POST /guide/feedback/bulk-delete` ·
-`DELETE /guide/feedback/{guideFeedback}` · `public.php`: `GET /public/faqs`
-(no auth)
-**Platform admin (not end-user):** `/platform/guide/*` - manage tutorials
-(create/edit/publish, thumbnail upload + preview) with
-`platform.guide.manage`, manage FAQs, and triage feedback (status updates,
-staff replies, bulk actions) with `platform.guide.feedback.manage`.
 PUBLISHED TITLE: A human, one tap away.
 SHORT-FORM VARIANT: A human
 PUBLISHED DESCRIPTION: Reach the Custosell team when you need a person - support email and phone lines with one-tap copy, plus business hours. Works offline too: the details stay copyable so you can contact the team after you reconnect. Try free #custosell #guide #tutorials #faq #Custosell #SmallBusiness
@@ -18026,7 +17997,36 @@
   - Screen-record clips: the Screen flow steps, trimmed to the script beats
   - Captions / subtitles: full on-screen captions exported as a caption file
   - Brand overlay / watermark: Custosell logo, corner placement
-  - Music: royalty-free background bed, low volume under the voiceover</t>
+  - Music: royalty-free background bed, low volume under the voiceover
+  - ---
+  - ## Technical reference (source of truth)
+  - **Screens:** `/guide/tutorials` (search + category filter + video cards) ·
+  - `/guide/faqs` (category accordion + search) · `/guide/feedback` (compose +
+  - Your submissions with status badges and team replies) · `/guide/contact`
+  - (support email + phone lines with copy buttons). All under
+  - `ModuleAccessMiddleware module="guide"`.
+  - **User actions (FE hooks):** `useGuideTutorials` (GET `/guide/tutorials`) ·
+  - `useGuideFaqs` (GET `/guide/faqs`) · `usePublicFaqs` (GET `/public/faqs`) ·
+  - `useMyGuideFeedback` (GET `/guide/feedback/mine`, merged with local pending
+  - via `readWithOfflineStrategy`) · `useCreateGuideFeedback` (POST
+  - `/guide/feedback`; offline-first via `completeOfflineGuideFeedbackInstant` -
+  - queues a mutation and returns a local pending record) ·
+  - `useDeleteMyGuideFeedback` + `useBulkDeleteMyGuideFeedback` (DELETE
+  - `/guide/feedback/{id}` / POST `/guide/feedback/bulk-delete`, removing local
+  - queue entries for unsent items)
+  - **Feedback status lifecycle:** `submitted` -&gt; `acknowledged` -&gt;
+  - `in_progress` -&gt; `resolved` / `closed`; staff replies surface on the user's
+  - submission card; local records carry `_pendingSync` / `_syncFailed` / `_localId`
+  - markers.
+  - **API endpoints (BE):** `guide.php` (auth:sanctum + business.active):
+  - `GET /guide/tutorials` · `GET /guide/faqs` · `GET /guide/feedback/mine` ·
+  - `POST /guide/feedback` · `POST /guide/feedback/bulk-delete` ·
+  - `DELETE /guide/feedback/{guideFeedback}` · `public.php`: `GET /public/faqs`
+  - (no auth)
+  - **Platform admin (not end-user):** `/platform/guide/*` - manage tutorials
+  - (create/edit/publish, thumbnail upload + preview) with
+  - `platform.guide.manage`, manage FAQs, and triage feedback (status updates,
+  - staff replies, bulk actions) with `platform.guide.feedback.manage`.</t>
         </is>
       </c>
       <c r="D288" s="5" t="n"/>
